--- a/building_tenants_test_data.xlsx
+++ b/building_tenants_test_data.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J401"/>
+  <dimension ref="A1:J402"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="14.83203125" customWidth="1"/>
@@ -416,7 +416,7 @@
         <v>Unit</v>
       </c>
       <c r="B1" t="str">
-        <v>Tenant ID</v>
+        <v>T-Code</v>
       </c>
       <c r="C1" t="str">
         <v>Name</v>
@@ -463,7 +463,7 @@
         <v>1998</v>
       </c>
       <c r="G2">
-        <v>940</v>
+        <v>942</v>
       </c>
       <c r="H2" t="str">
         <v>2025-05-01</v>
@@ -472,7 +472,7 @@
         <v>2026-05-31</v>
       </c>
       <c r="J2" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="3">
@@ -495,7 +495,7 @@
         <v>2000</v>
       </c>
       <c r="G3">
-        <v>970</v>
+        <v>972.75</v>
       </c>
       <c r="H3" t="str">
         <v>2025-06-01</v>
@@ -504,7 +504,7 @@
         <v>2026-06-31</v>
       </c>
       <c r="J3" t="str">
-        <v>Occupied</v>
+        <v>Notice</v>
       </c>
     </row>
     <row r="4">
@@ -527,7 +527,7 @@
         <v>2002</v>
       </c>
       <c r="G4">
-        <v>1000</v>
+        <v>1003.5</v>
       </c>
       <c r="H4" t="str">
         <v>2025-07-01</v>
@@ -536,7 +536,7 @@
         <v>2026-07-31</v>
       </c>
       <c r="J4" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="5">
@@ -559,7 +559,7 @@
         <v>2004</v>
       </c>
       <c r="G5">
-        <v>1030</v>
+        <v>1034.25</v>
       </c>
       <c r="H5" t="str">
         <v>2025-08-01</v>
@@ -568,7 +568,7 @@
         <v>2026-08-31</v>
       </c>
       <c r="J5" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="6">
@@ -591,7 +591,7 @@
         <v>1994</v>
       </c>
       <c r="G6">
-        <v>1060</v>
+        <v>1065</v>
       </c>
       <c r="H6" t="str">
         <v>2025-09-01</v>
@@ -600,7 +600,7 @@
         <v>2026-09-31</v>
       </c>
       <c r="J6" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="7">
@@ -623,7 +623,7 @@
         <v>1998</v>
       </c>
       <c r="G7">
-        <v>940</v>
+        <v>942</v>
       </c>
       <c r="H7" t="str">
         <v>2025-05-01</v>
@@ -632,7 +632,7 @@
         <v>2026-05-31</v>
       </c>
       <c r="J7" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="8">
@@ -655,7 +655,7 @@
         <v>2000</v>
       </c>
       <c r="G8">
-        <v>970</v>
+        <v>972.75</v>
       </c>
       <c r="H8" t="str">
         <v>2025-06-01</v>
@@ -664,7 +664,7 @@
         <v>2026-06-31</v>
       </c>
       <c r="J8" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         <v>2002</v>
       </c>
       <c r="G9">
-        <v>1000</v>
+        <v>1003.5</v>
       </c>
       <c r="H9" t="str">
         <v>2025-07-01</v>
@@ -696,7 +696,7 @@
         <v>2026-07-31</v>
       </c>
       <c r="J9" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="10">
@@ -719,7 +719,7 @@
         <v>2004</v>
       </c>
       <c r="G10">
-        <v>1030</v>
+        <v>1034.25</v>
       </c>
       <c r="H10" t="str">
         <v>2025-08-01</v>
@@ -728,7 +728,7 @@
         <v>2026-08-31</v>
       </c>
       <c r="J10" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="11">
@@ -751,7 +751,7 @@
         <v>1998</v>
       </c>
       <c r="G11">
-        <v>940</v>
+        <v>942</v>
       </c>
       <c r="H11" t="str">
         <v>2025-05-01</v>
@@ -760,7 +760,7 @@
         <v>2026-05-31</v>
       </c>
       <c r="J11" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="12">
@@ -783,7 +783,7 @@
         <v>2000</v>
       </c>
       <c r="G12">
-        <v>970</v>
+        <v>972.75</v>
       </c>
       <c r="H12" t="str">
         <v>2025-06-01</v>
@@ -792,7 +792,7 @@
         <v>2026-06-31</v>
       </c>
       <c r="J12" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="13">
@@ -815,7 +815,7 @@
         <v>1998</v>
       </c>
       <c r="G13">
-        <v>940</v>
+        <v>942</v>
       </c>
       <c r="H13" t="str">
         <v>2025-05-01</v>
@@ -824,7 +824,7 @@
         <v>2026-05-31</v>
       </c>
       <c r="J13" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="14">
@@ -847,7 +847,7 @@
         <v>2000</v>
       </c>
       <c r="G14">
-        <v>970</v>
+        <v>972.75</v>
       </c>
       <c r="H14" t="str">
         <v>2025-06-01</v>
@@ -856,7 +856,7 @@
         <v>2026-06-31</v>
       </c>
       <c r="J14" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="15">
@@ -879,7 +879,7 @@
         <v>2002</v>
       </c>
       <c r="G15">
-        <v>1000</v>
+        <v>1003.5</v>
       </c>
       <c r="H15" t="str">
         <v>2025-07-01</v>
@@ -888,7 +888,7 @@
         <v>2026-07-31</v>
       </c>
       <c r="J15" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="16">
@@ -911,7 +911,7 @@
         <v>1998</v>
       </c>
       <c r="G16">
-        <v>940</v>
+        <v>942</v>
       </c>
       <c r="H16" t="str">
         <v>2025-05-01</v>
@@ -920,7 +920,7 @@
         <v>2026-05-31</v>
       </c>
       <c r="J16" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="17">
@@ -943,7 +943,7 @@
         <v>2000</v>
       </c>
       <c r="G17">
-        <v>970</v>
+        <v>972.75</v>
       </c>
       <c r="H17" t="str">
         <v>2025-06-01</v>
@@ -952,7 +952,7 @@
         <v>2026-06-31</v>
       </c>
       <c r="J17" t="str">
-        <v>Occupied</v>
+        <v>Notice</v>
       </c>
     </row>
     <row r="18">
@@ -975,7 +975,7 @@
         <v>2002</v>
       </c>
       <c r="G18">
-        <v>1000</v>
+        <v>1003.5</v>
       </c>
       <c r="H18" t="str">
         <v>2025-07-01</v>
@@ -984,7 +984,7 @@
         <v>2026-07-31</v>
       </c>
       <c r="J18" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="19">
@@ -1007,7 +1007,7 @@
         <v>2004</v>
       </c>
       <c r="G19">
-        <v>1030</v>
+        <v>1034.25</v>
       </c>
       <c r="H19" t="str">
         <v>2025-08-01</v>
@@ -1016,7 +1016,7 @@
         <v>2026-08-31</v>
       </c>
       <c r="J19" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="20">
@@ -1039,7 +1039,7 @@
         <v>1998</v>
       </c>
       <c r="G20">
-        <v>940</v>
+        <v>942</v>
       </c>
       <c r="H20" t="str">
         <v>2025-05-01</v>
@@ -1048,7 +1048,7 @@
         <v>2026-05-31</v>
       </c>
       <c r="J20" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="21">
@@ -1071,7 +1071,7 @@
         <v>2000</v>
       </c>
       <c r="G21">
-        <v>970</v>
+        <v>972.75</v>
       </c>
       <c r="H21" t="str">
         <v>2025-06-01</v>
@@ -1080,7 +1080,7 @@
         <v>2026-06-31</v>
       </c>
       <c r="J21" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="22">
@@ -1103,7 +1103,7 @@
         <v>2004</v>
       </c>
       <c r="G22">
-        <v>1030</v>
+        <v>1034.25</v>
       </c>
       <c r="H22" t="str">
         <v>2025-08-01</v>
@@ -1112,7 +1112,7 @@
         <v>2026-08-31</v>
       </c>
       <c r="J22" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="23">
@@ -1135,7 +1135,7 @@
         <v>1994</v>
       </c>
       <c r="G23">
-        <v>1060</v>
+        <v>1065</v>
       </c>
       <c r="H23" t="str">
         <v>2025-09-01</v>
@@ -1144,7 +1144,7 @@
         <v>2026-09-31</v>
       </c>
       <c r="J23" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="24">
@@ -1167,7 +1167,7 @@
         <v>1999</v>
       </c>
       <c r="G24">
-        <v>960</v>
+        <v>962.25</v>
       </c>
       <c r="H24" t="str">
         <v>2025-06-01</v>
@@ -1176,7 +1176,7 @@
         <v>2026-06-31</v>
       </c>
       <c r="J24" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="25">
@@ -1199,7 +1199,7 @@
         <v>2001</v>
       </c>
       <c r="G25">
-        <v>990</v>
+        <v>993</v>
       </c>
       <c r="H25" t="str">
         <v>2025-07-01</v>
@@ -1208,7 +1208,7 @@
         <v>2026-07-31</v>
       </c>
       <c r="J25" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="26">
@@ -1231,7 +1231,7 @@
         <v>2003</v>
       </c>
       <c r="G26">
-        <v>1020</v>
+        <v>1023.75</v>
       </c>
       <c r="H26" t="str">
         <v>2025-08-01</v>
@@ -1240,7 +1240,7 @@
         <v>2026-08-31</v>
       </c>
       <c r="J26" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="27">
@@ -1263,7 +1263,7 @@
         <v>1993</v>
       </c>
       <c r="G27">
-        <v>1050</v>
+        <v>1054.5</v>
       </c>
       <c r="H27" t="str">
         <v>2025-09-01</v>
@@ -1272,7 +1272,7 @@
         <v>2026-09-31</v>
       </c>
       <c r="J27" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="28">
@@ -1295,7 +1295,7 @@
         <v>1995</v>
       </c>
       <c r="G28">
-        <v>1080</v>
+        <v>1085.25</v>
       </c>
       <c r="H28" t="str">
         <v>2025-10-01</v>
@@ -1304,7 +1304,7 @@
         <v>2026-10-31</v>
       </c>
       <c r="J28" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="29">
@@ -1327,7 +1327,7 @@
         <v>1999</v>
       </c>
       <c r="G29">
-        <v>960</v>
+        <v>962.25</v>
       </c>
       <c r="H29" t="str">
         <v>2025-06-01</v>
@@ -1336,7 +1336,7 @@
         <v>2026-06-31</v>
       </c>
       <c r="J29" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="30">
@@ -1359,7 +1359,7 @@
         <v>2001</v>
       </c>
       <c r="G30">
-        <v>990</v>
+        <v>993</v>
       </c>
       <c r="H30" t="str">
         <v>2025-07-01</v>
@@ -1368,7 +1368,7 @@
         <v>2026-07-31</v>
       </c>
       <c r="J30" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="31">
@@ -1391,7 +1391,7 @@
         <v>1993</v>
       </c>
       <c r="G31">
-        <v>1050</v>
+        <v>1054.5</v>
       </c>
       <c r="H31" t="str">
         <v>2025-09-01</v>
@@ -1400,7 +1400,7 @@
         <v>2026-09-31</v>
       </c>
       <c r="J31" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="32">
@@ -1423,7 +1423,7 @@
         <v>1999</v>
       </c>
       <c r="G32">
-        <v>960</v>
+        <v>962.25</v>
       </c>
       <c r="H32" t="str">
         <v>2025-06-01</v>
@@ -1432,7 +1432,7 @@
         <v>2026-06-31</v>
       </c>
       <c r="J32" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="33">
@@ -1455,7 +1455,7 @@
         <v>2001</v>
       </c>
       <c r="G33">
-        <v>990</v>
+        <v>993</v>
       </c>
       <c r="H33" t="str">
         <v>2025-07-01</v>
@@ -1464,7 +1464,7 @@
         <v>2026-07-31</v>
       </c>
       <c r="J33" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="34">
@@ -1487,7 +1487,7 @@
         <v>2003</v>
       </c>
       <c r="G34">
-        <v>1020</v>
+        <v>1023.75</v>
       </c>
       <c r="H34" t="str">
         <v>2025-08-01</v>
@@ -1496,7 +1496,7 @@
         <v>2026-08-31</v>
       </c>
       <c r="J34" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="35">
@@ -1519,7 +1519,7 @@
         <v>1999</v>
       </c>
       <c r="G35">
-        <v>960</v>
+        <v>962.25</v>
       </c>
       <c r="H35" t="str">
         <v>2025-06-01</v>
@@ -1528,7 +1528,7 @@
         <v>2026-06-31</v>
       </c>
       <c r="J35" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="36">
@@ -1551,7 +1551,7 @@
         <v>2001</v>
       </c>
       <c r="G36">
-        <v>990</v>
+        <v>993</v>
       </c>
       <c r="H36" t="str">
         <v>2025-07-01</v>
@@ -1560,7 +1560,7 @@
         <v>2026-07-31</v>
       </c>
       <c r="J36" t="str">
-        <v>Occupied</v>
+        <v>Notice</v>
       </c>
     </row>
     <row r="37">
@@ -1583,7 +1583,7 @@
         <v>2003</v>
       </c>
       <c r="G37">
-        <v>1020</v>
+        <v>1023.75</v>
       </c>
       <c r="H37" t="str">
         <v>2025-08-01</v>
@@ -1592,7 +1592,7 @@
         <v>2026-08-31</v>
       </c>
       <c r="J37" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="38">
@@ -1615,7 +1615,7 @@
         <v>1999</v>
       </c>
       <c r="G38">
-        <v>960</v>
+        <v>962.25</v>
       </c>
       <c r="H38" t="str">
         <v>2025-06-01</v>
@@ -1624,7 +1624,7 @@
         <v>2026-06-31</v>
       </c>
       <c r="J38" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="39">
@@ -1647,7 +1647,7 @@
         <v>2001</v>
       </c>
       <c r="G39">
-        <v>990</v>
+        <v>993</v>
       </c>
       <c r="H39" t="str">
         <v>2025-07-01</v>
@@ -1656,7 +1656,7 @@
         <v>2026-07-31</v>
       </c>
       <c r="J39" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="40">
@@ -1679,7 +1679,7 @@
         <v>1993</v>
       </c>
       <c r="G40">
-        <v>1050</v>
+        <v>1054.5</v>
       </c>
       <c r="H40" t="str">
         <v>2025-09-01</v>
@@ -1688,7 +1688,7 @@
         <v>2026-09-31</v>
       </c>
       <c r="J40" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="41">
@@ -1711,7 +1711,7 @@
         <v>1999</v>
       </c>
       <c r="G41">
-        <v>960</v>
+        <v>962.25</v>
       </c>
       <c r="H41" t="str">
         <v>2025-06-01</v>
@@ -1720,7 +1720,7 @@
         <v>2026-06-31</v>
       </c>
       <c r="J41" t="str">
-        <v>Secured</v>
+        <v>Future</v>
       </c>
     </row>
     <row r="42">
@@ -1743,7 +1743,7 @@
         <v>2001</v>
       </c>
       <c r="G42">
-        <v>990</v>
+        <v>993</v>
       </c>
       <c r="H42" t="str">
         <v>2025-07-01</v>
@@ -1752,7 +1752,7 @@
         <v>2026-07-31</v>
       </c>
       <c r="J42" t="str">
-        <v>Secured</v>
+        <v>Future</v>
       </c>
     </row>
     <row r="43">
@@ -1775,7 +1775,7 @@
         <v>2003</v>
       </c>
       <c r="G43">
-        <v>1020</v>
+        <v>1023.75</v>
       </c>
       <c r="H43" t="str">
         <v>2025-08-01</v>
@@ -1784,7 +1784,7 @@
         <v>2026-08-31</v>
       </c>
       <c r="J43" t="str">
-        <v>Secured</v>
+        <v>Future</v>
       </c>
     </row>
     <row r="44">
@@ -1807,7 +1807,7 @@
         <v>1993</v>
       </c>
       <c r="G44">
-        <v>1050</v>
+        <v>1054.5</v>
       </c>
       <c r="H44" t="str">
         <v>2025-09-01</v>
@@ -1816,7 +1816,7 @@
         <v>2026-09-31</v>
       </c>
       <c r="J44" t="str">
-        <v>Secured</v>
+        <v>Future</v>
       </c>
     </row>
     <row r="45">
@@ -1839,7 +1839,7 @@
         <v>1995</v>
       </c>
       <c r="G45">
-        <v>1080</v>
+        <v>1085.25</v>
       </c>
       <c r="H45" t="str">
         <v>2025-10-01</v>
@@ -1848,7 +1848,7 @@
         <v>2026-10-31</v>
       </c>
       <c r="J45" t="str">
-        <v>Secured</v>
+        <v>Future</v>
       </c>
     </row>
     <row r="46">
@@ -1871,7 +1871,7 @@
         <v>2000</v>
       </c>
       <c r="G46">
-        <v>980</v>
+        <v>982.5</v>
       </c>
       <c r="H46" t="str">
         <v>2025-07-01</v>
@@ -1880,7 +1880,7 @@
         <v>2026-07-31</v>
       </c>
       <c r="J46" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="47">
@@ -1903,7 +1903,7 @@
         <v>2002</v>
       </c>
       <c r="G47">
-        <v>1010</v>
+        <v>1013.25</v>
       </c>
       <c r="H47" t="str">
         <v>2025-08-01</v>
@@ -1912,7 +1912,7 @@
         <v>2026-08-31</v>
       </c>
       <c r="J47" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="48">
@@ -1935,7 +1935,7 @@
         <v>1994</v>
       </c>
       <c r="G48">
-        <v>1070</v>
+        <v>1074.75</v>
       </c>
       <c r="H48" t="str">
         <v>2025-10-01</v>
@@ -1944,7 +1944,7 @@
         <v>2026-10-31</v>
       </c>
       <c r="J48" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="49">
@@ -1967,7 +1967,7 @@
         <v>1996</v>
       </c>
       <c r="G49">
-        <v>1100</v>
+        <v>1105.5</v>
       </c>
       <c r="H49" t="str">
         <v>2025-11-01</v>
@@ -1976,7 +1976,7 @@
         <v>2026-11-31</v>
       </c>
       <c r="J49" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="50">
@@ -1999,7 +1999,7 @@
         <v>2000</v>
       </c>
       <c r="G50">
-        <v>980</v>
+        <v>982.5</v>
       </c>
       <c r="H50" t="str">
         <v>2025-07-01</v>
@@ -2008,7 +2008,7 @@
         <v>2026-07-31</v>
       </c>
       <c r="J50" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="51">
@@ -2031,7 +2031,7 @@
         <v>2002</v>
       </c>
       <c r="G51">
-        <v>1010</v>
+        <v>1013.25</v>
       </c>
       <c r="H51" t="str">
         <v>2025-08-01</v>
@@ -2040,7 +2040,7 @@
         <v>2026-08-31</v>
       </c>
       <c r="J51" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="52">
@@ -2063,7 +2063,7 @@
         <v>2004</v>
       </c>
       <c r="G52">
-        <v>1040</v>
+        <v>1044</v>
       </c>
       <c r="H52" t="str">
         <v>2025-09-01</v>
@@ -2072,7 +2072,7 @@
         <v>2026-09-31</v>
       </c>
       <c r="J52" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="53">
@@ -2095,7 +2095,7 @@
         <v>1994</v>
       </c>
       <c r="G53">
-        <v>1070</v>
+        <v>1074.75</v>
       </c>
       <c r="H53" t="str">
         <v>2025-10-01</v>
@@ -2104,7 +2104,7 @@
         <v>2026-10-31</v>
       </c>
       <c r="J53" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="54">
@@ -2127,7 +2127,7 @@
         <v>2000</v>
       </c>
       <c r="G54">
-        <v>980</v>
+        <v>982.5</v>
       </c>
       <c r="H54" t="str">
         <v>2025-07-01</v>
@@ -2136,7 +2136,7 @@
         <v>2026-07-31</v>
       </c>
       <c r="J54" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="55">
@@ -2159,7 +2159,7 @@
         <v>2002</v>
       </c>
       <c r="G55">
-        <v>1010</v>
+        <v>1013.25</v>
       </c>
       <c r="H55" t="str">
         <v>2025-08-01</v>
@@ -2168,7 +2168,7 @@
         <v>2026-08-31</v>
       </c>
       <c r="J55" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="56">
@@ -2191,7 +2191,7 @@
         <v>2000</v>
       </c>
       <c r="G56">
-        <v>980</v>
+        <v>982.5</v>
       </c>
       <c r="H56" t="str">
         <v>2025-07-01</v>
@@ -2200,7 +2200,7 @@
         <v>2026-07-31</v>
       </c>
       <c r="J56" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="57">
@@ -2223,7 +2223,7 @@
         <v>2002</v>
       </c>
       <c r="G57">
-        <v>1010</v>
+        <v>1013.25</v>
       </c>
       <c r="H57" t="str">
         <v>2025-08-01</v>
@@ -2232,7 +2232,7 @@
         <v>2026-08-31</v>
       </c>
       <c r="J57" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="58">
@@ -2255,7 +2255,7 @@
         <v>2004</v>
       </c>
       <c r="G58">
-        <v>1040</v>
+        <v>1044</v>
       </c>
       <c r="H58" t="str">
         <v>2025-09-01</v>
@@ -2264,7 +2264,7 @@
         <v>2026-09-31</v>
       </c>
       <c r="J58" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="59">
@@ -2287,7 +2287,7 @@
         <v>1994</v>
       </c>
       <c r="G59">
-        <v>1070</v>
+        <v>1074.75</v>
       </c>
       <c r="H59" t="str">
         <v>2025-10-01</v>
@@ -2296,7 +2296,7 @@
         <v>2026-10-31</v>
       </c>
       <c r="J59" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="60">
@@ -2319,7 +2319,7 @@
         <v>2000</v>
       </c>
       <c r="G60">
-        <v>980</v>
+        <v>982.5</v>
       </c>
       <c r="H60" t="str">
         <v>2025-07-01</v>
@@ -2328,7 +2328,7 @@
         <v>2026-07-31</v>
       </c>
       <c r="J60" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="61">
@@ -2351,7 +2351,7 @@
         <v>2002</v>
       </c>
       <c r="G61">
-        <v>1010</v>
+        <v>1013.25</v>
       </c>
       <c r="H61" t="str">
         <v>2025-08-01</v>
@@ -2360,7 +2360,7 @@
         <v>2026-08-31</v>
       </c>
       <c r="J61" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="62">
@@ -2383,7 +2383,7 @@
         <v>2004</v>
       </c>
       <c r="G62">
-        <v>1040</v>
+        <v>1044</v>
       </c>
       <c r="H62" t="str">
         <v>2025-09-01</v>
@@ -2392,7 +2392,7 @@
         <v>2026-09-31</v>
       </c>
       <c r="J62" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="63">
@@ -2415,7 +2415,7 @@
         <v>1994</v>
       </c>
       <c r="G63">
-        <v>1070</v>
+        <v>1074.75</v>
       </c>
       <c r="H63" t="str">
         <v>2025-10-01</v>
@@ -2424,7 +2424,7 @@
         <v>2026-10-31</v>
       </c>
       <c r="J63" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="64">
@@ -2447,7 +2447,7 @@
         <v>1996</v>
       </c>
       <c r="G64">
-        <v>1100</v>
+        <v>1105.5</v>
       </c>
       <c r="H64" t="str">
         <v>2025-11-01</v>
@@ -2456,7 +2456,7 @@
         <v>2026-11-31</v>
       </c>
       <c r="J64" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="65">
@@ -2479,7 +2479,7 @@
         <v>2001</v>
       </c>
       <c r="G65">
-        <v>1000</v>
+        <v>1002.75</v>
       </c>
       <c r="H65" t="str">
         <v>2025-08-01</v>
@@ -2488,7 +2488,7 @@
         <v>2026-08-31</v>
       </c>
       <c r="J65" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="66">
@@ -2511,7 +2511,7 @@
         <v>2003</v>
       </c>
       <c r="G66">
-        <v>1030</v>
+        <v>1033.5</v>
       </c>
       <c r="H66" t="str">
         <v>2025-09-01</v>
@@ -2520,7 +2520,7 @@
         <v>2026-09-31</v>
       </c>
       <c r="J66" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="67">
@@ -2543,7 +2543,7 @@
         <v>1993</v>
       </c>
       <c r="G67">
-        <v>1060</v>
+        <v>1064.25</v>
       </c>
       <c r="H67" t="str">
         <v>2025-10-01</v>
@@ -2552,7 +2552,7 @@
         <v>2026-10-31</v>
       </c>
       <c r="J67" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="68">
@@ -2575,7 +2575,7 @@
         <v>1995</v>
       </c>
       <c r="G68">
-        <v>1090</v>
+        <v>1095</v>
       </c>
       <c r="H68" t="str">
         <v>2025-11-01</v>
@@ -2584,7 +2584,7 @@
         <v>2026-11-31</v>
       </c>
       <c r="J68" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="69">
@@ -2607,7 +2607,7 @@
         <v>1997</v>
       </c>
       <c r="G69">
-        <v>1120</v>
+        <v>1125.75</v>
       </c>
       <c r="H69" t="str">
         <v>2025-12-01</v>
@@ -2616,7 +2616,7 @@
         <v>2026-12-31</v>
       </c>
       <c r="J69" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="70">
@@ -2639,7 +2639,7 @@
         <v>2001</v>
       </c>
       <c r="G70">
-        <v>1000</v>
+        <v>1002.75</v>
       </c>
       <c r="H70" t="str">
         <v>2025-08-01</v>
@@ -2648,7 +2648,7 @@
         <v>2026-08-31</v>
       </c>
       <c r="J70" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="71">
@@ -2671,7 +2671,7 @@
         <v>2003</v>
       </c>
       <c r="G71">
-        <v>1030</v>
+        <v>1033.5</v>
       </c>
       <c r="H71" t="str">
         <v>2025-09-01</v>
@@ -2680,7 +2680,7 @@
         <v>2026-09-31</v>
       </c>
       <c r="J71" t="str">
-        <v>Occupied</v>
+        <v>Notice</v>
       </c>
     </row>
     <row r="72">
@@ -2703,7 +2703,7 @@
         <v>1993</v>
       </c>
       <c r="G72">
-        <v>1060</v>
+        <v>1064.25</v>
       </c>
       <c r="H72" t="str">
         <v>2025-10-01</v>
@@ -2712,7 +2712,7 @@
         <v>2026-10-31</v>
       </c>
       <c r="J72" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="73">
@@ -2735,7 +2735,7 @@
         <v>1995</v>
       </c>
       <c r="G73">
-        <v>1090</v>
+        <v>1095</v>
       </c>
       <c r="H73" t="str">
         <v>2025-11-01</v>
@@ -2744,7 +2744,7 @@
         <v>2026-11-31</v>
       </c>
       <c r="J73" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="74">
@@ -2767,7 +2767,7 @@
         <v>2001</v>
       </c>
       <c r="G74">
-        <v>1000</v>
+        <v>1002.75</v>
       </c>
       <c r="H74" t="str">
         <v>2025-08-01</v>
@@ -2776,7 +2776,7 @@
         <v>2026-08-31</v>
       </c>
       <c r="J74" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="75">
@@ -2799,7 +2799,7 @@
         <v>2003</v>
       </c>
       <c r="G75">
-        <v>1030</v>
+        <v>1033.5</v>
       </c>
       <c r="H75" t="str">
         <v>2025-09-01</v>
@@ -2808,7 +2808,7 @@
         <v>2026-09-31</v>
       </c>
       <c r="J75" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="76">
@@ -2831,7 +2831,7 @@
         <v>2001</v>
       </c>
       <c r="G76">
-        <v>1000</v>
+        <v>1002.75</v>
       </c>
       <c r="H76" t="str">
         <v>2025-08-01</v>
@@ -2840,7 +2840,7 @@
         <v>2026-08-31</v>
       </c>
       <c r="J76" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="77">
@@ -2863,7 +2863,7 @@
         <v>2003</v>
       </c>
       <c r="G77">
-        <v>1030</v>
+        <v>1033.5</v>
       </c>
       <c r="H77" t="str">
         <v>2025-09-01</v>
@@ -2872,7 +2872,7 @@
         <v>2026-09-31</v>
       </c>
       <c r="J77" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="78">
@@ -2895,7 +2895,7 @@
         <v>1993</v>
       </c>
       <c r="G78">
-        <v>1060</v>
+        <v>1064.25</v>
       </c>
       <c r="H78" t="str">
         <v>2025-10-01</v>
@@ -2904,7 +2904,7 @@
         <v>2026-10-31</v>
       </c>
       <c r="J78" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="79">
@@ -2927,7 +2927,7 @@
         <v>2001</v>
       </c>
       <c r="G79">
-        <v>1000</v>
+        <v>1002.75</v>
       </c>
       <c r="H79" t="str">
         <v>2025-08-01</v>
@@ -2936,7 +2936,7 @@
         <v>2026-08-31</v>
       </c>
       <c r="J79" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="80">
@@ -2959,7 +2959,7 @@
         <v>2003</v>
       </c>
       <c r="G80">
-        <v>1030</v>
+        <v>1033.5</v>
       </c>
       <c r="H80" t="str">
         <v>2025-09-01</v>
@@ -2968,7 +2968,7 @@
         <v>2026-09-31</v>
       </c>
       <c r="J80" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="81">
@@ -2991,7 +2991,7 @@
         <v>1993</v>
       </c>
       <c r="G81">
-        <v>1060</v>
+        <v>1064.25</v>
       </c>
       <c r="H81" t="str">
         <v>2025-10-01</v>
@@ -3000,7 +3000,7 @@
         <v>2026-10-31</v>
       </c>
       <c r="J81" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="82">
@@ -3023,7 +3023,7 @@
         <v>1995</v>
       </c>
       <c r="G82">
-        <v>1090</v>
+        <v>1095</v>
       </c>
       <c r="H82" t="str">
         <v>2025-11-01</v>
@@ -3032,7 +3032,7 @@
         <v>2026-11-31</v>
       </c>
       <c r="J82" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="83">
@@ -3055,7 +3055,7 @@
         <v>2001</v>
       </c>
       <c r="G83">
-        <v>1000</v>
+        <v>1002.75</v>
       </c>
       <c r="H83" t="str">
         <v>2025-08-01</v>
@@ -3064,7 +3064,7 @@
         <v>2026-08-31</v>
       </c>
       <c r="J83" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="84">
@@ -3087,7 +3087,7 @@
         <v>2003</v>
       </c>
       <c r="G84">
-        <v>1030</v>
+        <v>1033.5</v>
       </c>
       <c r="H84" t="str">
         <v>2025-09-01</v>
@@ -3096,7 +3096,7 @@
         <v>2026-09-31</v>
       </c>
       <c r="J84" t="str">
-        <v>Occupied</v>
+        <v>Notice</v>
       </c>
     </row>
     <row r="85">
@@ -3119,7 +3119,7 @@
         <v>1995</v>
       </c>
       <c r="G85">
-        <v>1090</v>
+        <v>1095</v>
       </c>
       <c r="H85" t="str">
         <v>2025-11-01</v>
@@ -3128,7 +3128,7 @@
         <v>2026-11-31</v>
       </c>
       <c r="J85" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="86">
@@ -3151,7 +3151,7 @@
         <v>1997</v>
       </c>
       <c r="G86">
-        <v>1120</v>
+        <v>1125.75</v>
       </c>
       <c r="H86" t="str">
         <v>2025-12-01</v>
@@ -3160,7 +3160,7 @@
         <v>2026-12-31</v>
       </c>
       <c r="J86" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="87">
@@ -3183,7 +3183,7 @@
         <v>2002</v>
       </c>
       <c r="G87">
-        <v>1020</v>
+        <v>1023</v>
       </c>
       <c r="H87" t="str">
         <v>2025-09-01</v>
@@ -3192,7 +3192,7 @@
         <v>2026-09-31</v>
       </c>
       <c r="J87" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="88">
@@ -3215,7 +3215,7 @@
         <v>2004</v>
       </c>
       <c r="G88">
-        <v>1050</v>
+        <v>1053.75</v>
       </c>
       <c r="H88" t="str">
         <v>2025-10-01</v>
@@ -3224,7 +3224,7 @@
         <v>2026-10-31</v>
       </c>
       <c r="J88" t="str">
-        <v>Occupied</v>
+        <v>Notice</v>
       </c>
     </row>
     <row r="89">
@@ -3247,7 +3247,7 @@
         <v>1994</v>
       </c>
       <c r="G89">
-        <v>1080</v>
+        <v>1084.5</v>
       </c>
       <c r="H89" t="str">
         <v>2025-11-01</v>
@@ -3256,7 +3256,7 @@
         <v>2026-11-31</v>
       </c>
       <c r="J89" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="90">
@@ -3279,7 +3279,7 @@
         <v>1996</v>
       </c>
       <c r="G90">
-        <v>1110</v>
+        <v>1115.25</v>
       </c>
       <c r="H90" t="str">
         <v>2025-12-01</v>
@@ -3288,7 +3288,7 @@
         <v>2026-12-31</v>
       </c>
       <c r="J90" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="91">
@@ -3311,7 +3311,7 @@
         <v>1998</v>
       </c>
       <c r="G91">
-        <v>1140</v>
+        <v>1146</v>
       </c>
       <c r="H91" t="str">
         <v>2025-01-01</v>
@@ -3320,7 +3320,7 @@
         <v>2026-01-31</v>
       </c>
       <c r="J91" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="92">
@@ -3343,7 +3343,7 @@
         <v>2002</v>
       </c>
       <c r="G92">
-        <v>1020</v>
+        <v>1023</v>
       </c>
       <c r="H92" t="str">
         <v>2025-09-01</v>
@@ -3352,7 +3352,7 @@
         <v>2026-09-31</v>
       </c>
       <c r="J92" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="93">
@@ -3375,7 +3375,7 @@
         <v>2004</v>
       </c>
       <c r="G93">
-        <v>1050</v>
+        <v>1053.75</v>
       </c>
       <c r="H93" t="str">
         <v>2025-10-01</v>
@@ -3384,7 +3384,7 @@
         <v>2026-10-31</v>
       </c>
       <c r="J93" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="94">
@@ -3407,7 +3407,7 @@
         <v>1996</v>
       </c>
       <c r="G94">
-        <v>1110</v>
+        <v>1115.25</v>
       </c>
       <c r="H94" t="str">
         <v>2025-12-01</v>
@@ -3416,7 +3416,7 @@
         <v>2026-12-31</v>
       </c>
       <c r="J94" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="95">
@@ -3439,7 +3439,7 @@
         <v>2002</v>
       </c>
       <c r="G95">
-        <v>1020</v>
+        <v>1023</v>
       </c>
       <c r="H95" t="str">
         <v>2025-09-01</v>
@@ -3448,7 +3448,7 @@
         <v>2026-09-31</v>
       </c>
       <c r="J95" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="96">
@@ -3471,7 +3471,7 @@
         <v>2004</v>
       </c>
       <c r="G96">
-        <v>1050</v>
+        <v>1053.75</v>
       </c>
       <c r="H96" t="str">
         <v>2025-10-01</v>
@@ -3480,7 +3480,7 @@
         <v>2026-10-31</v>
       </c>
       <c r="J96" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="97">
@@ -3503,7 +3503,7 @@
         <v>1994</v>
       </c>
       <c r="G97">
-        <v>1080</v>
+        <v>1084.5</v>
       </c>
       <c r="H97" t="str">
         <v>2025-11-01</v>
@@ -3512,7 +3512,7 @@
         <v>2026-11-31</v>
       </c>
       <c r="J97" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="98">
@@ -3535,7 +3535,7 @@
         <v>2002</v>
       </c>
       <c r="G98">
-        <v>1020</v>
+        <v>1023</v>
       </c>
       <c r="H98" t="str">
         <v>2025-09-01</v>
@@ -3544,7 +3544,7 @@
         <v>2026-09-31</v>
       </c>
       <c r="J98" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="99">
@@ -3567,7 +3567,7 @@
         <v>2004</v>
       </c>
       <c r="G99">
-        <v>1050</v>
+        <v>1053.75</v>
       </c>
       <c r="H99" t="str">
         <v>2025-10-01</v>
@@ -3576,7 +3576,7 @@
         <v>2026-10-31</v>
       </c>
       <c r="J99" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="100">
@@ -3599,7 +3599,7 @@
         <v>1994</v>
       </c>
       <c r="G100">
-        <v>1080</v>
+        <v>1084.5</v>
       </c>
       <c r="H100" t="str">
         <v>2025-11-01</v>
@@ -3608,7 +3608,7 @@
         <v>2026-11-31</v>
       </c>
       <c r="J100" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="101">
@@ -3631,7 +3631,7 @@
         <v>2002</v>
       </c>
       <c r="G101">
-        <v>1020</v>
+        <v>1023</v>
       </c>
       <c r="H101" t="str">
         <v>2025-09-01</v>
@@ -3640,7 +3640,7 @@
         <v>2026-09-31</v>
       </c>
       <c r="J101" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="102">
@@ -3663,7 +3663,7 @@
         <v>2004</v>
       </c>
       <c r="G102">
-        <v>1050</v>
+        <v>1053.75</v>
       </c>
       <c r="H102" t="str">
         <v>2025-10-01</v>
@@ -3672,7 +3672,7 @@
         <v>2026-10-31</v>
       </c>
       <c r="J102" t="str">
-        <v>Occupied</v>
+        <v>Notice</v>
       </c>
     </row>
     <row r="103">
@@ -3695,7 +3695,7 @@
         <v>1996</v>
       </c>
       <c r="G103">
-        <v>1110</v>
+        <v>1115.25</v>
       </c>
       <c r="H103" t="str">
         <v>2025-12-01</v>
@@ -3704,7 +3704,7 @@
         <v>2026-12-31</v>
       </c>
       <c r="J103" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="104">
@@ -3727,7 +3727,7 @@
         <v>2002</v>
       </c>
       <c r="G104">
-        <v>1020</v>
+        <v>1023</v>
       </c>
       <c r="H104" t="str">
         <v>2025-09-01</v>
@@ -3736,7 +3736,7 @@
         <v>2026-09-31</v>
       </c>
       <c r="J104" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="105">
@@ -3759,7 +3759,7 @@
         <v>2004</v>
       </c>
       <c r="G105">
-        <v>1050</v>
+        <v>1053.75</v>
       </c>
       <c r="H105" t="str">
         <v>2025-10-01</v>
@@ -3768,7 +3768,7 @@
         <v>2026-10-31</v>
       </c>
       <c r="J105" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="106">
@@ -3791,7 +3791,7 @@
         <v>1994</v>
       </c>
       <c r="G106">
-        <v>1080</v>
+        <v>1084.5</v>
       </c>
       <c r="H106" t="str">
         <v>2025-11-01</v>
@@ -3800,7 +3800,7 @@
         <v>2026-11-31</v>
       </c>
       <c r="J106" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="107">
@@ -3823,7 +3823,7 @@
         <v>1996</v>
       </c>
       <c r="G107">
-        <v>1110</v>
+        <v>1115.25</v>
       </c>
       <c r="H107" t="str">
         <v>2025-12-01</v>
@@ -3832,7 +3832,7 @@
         <v>2026-12-31</v>
       </c>
       <c r="J107" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="108">
@@ -3855,7 +3855,7 @@
         <v>1998</v>
       </c>
       <c r="G108">
-        <v>1140</v>
+        <v>1146</v>
       </c>
       <c r="H108" t="str">
         <v>2025-01-01</v>
@@ -3864,7 +3864,7 @@
         <v>2026-01-31</v>
       </c>
       <c r="J108" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="109">
@@ -3887,7 +3887,7 @@
         <v>2003</v>
       </c>
       <c r="G109">
-        <v>1040</v>
+        <v>1043.25</v>
       </c>
       <c r="H109" t="str">
         <v>2025-10-01</v>
@@ -3896,7 +3896,7 @@
         <v>2026-10-31</v>
       </c>
       <c r="J109" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="110">
@@ -3919,7 +3919,7 @@
         <v>1993</v>
       </c>
       <c r="G110">
-        <v>1070</v>
+        <v>1074</v>
       </c>
       <c r="H110" t="str">
         <v>2025-11-01</v>
@@ -3928,7 +3928,7 @@
         <v>2026-11-31</v>
       </c>
       <c r="J110" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="111">
@@ -3951,7 +3951,7 @@
         <v>1995</v>
       </c>
       <c r="G111">
-        <v>1100</v>
+        <v>1104.75</v>
       </c>
       <c r="H111" t="str">
         <v>2025-12-01</v>
@@ -3960,7 +3960,7 @@
         <v>2026-12-31</v>
       </c>
       <c r="J111" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="112">
@@ -3983,7 +3983,7 @@
         <v>1997</v>
       </c>
       <c r="G112">
-        <v>1130</v>
+        <v>1135.5</v>
       </c>
       <c r="H112" t="str">
         <v>2025-01-01</v>
@@ -3992,7 +3992,7 @@
         <v>2026-01-31</v>
       </c>
       <c r="J112" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="113">
@@ -4015,7 +4015,7 @@
         <v>2003</v>
       </c>
       <c r="G113">
-        <v>1040</v>
+        <v>1043.25</v>
       </c>
       <c r="H113" t="str">
         <v>2025-10-01</v>
@@ -4024,7 +4024,7 @@
         <v>2026-10-31</v>
       </c>
       <c r="J113" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="114">
@@ -4047,7 +4047,7 @@
         <v>1993</v>
       </c>
       <c r="G114">
-        <v>1070</v>
+        <v>1074</v>
       </c>
       <c r="H114" t="str">
         <v>2025-11-01</v>
@@ -4056,7 +4056,7 @@
         <v>2026-11-31</v>
       </c>
       <c r="J114" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="115">
@@ -4079,7 +4079,7 @@
         <v>1995</v>
       </c>
       <c r="G115">
-        <v>1100</v>
+        <v>1104.75</v>
       </c>
       <c r="H115" t="str">
         <v>2025-12-01</v>
@@ -4088,7 +4088,7 @@
         <v>2026-12-31</v>
       </c>
       <c r="J115" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="116">
@@ -4111,7 +4111,7 @@
         <v>2003</v>
       </c>
       <c r="G116">
-        <v>1040</v>
+        <v>1043.25</v>
       </c>
       <c r="H116" t="str">
         <v>2025-10-01</v>
@@ -4120,7 +4120,7 @@
         <v>2026-10-31</v>
       </c>
       <c r="J116" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="117">
@@ -4143,7 +4143,7 @@
         <v>1993</v>
       </c>
       <c r="G117">
-        <v>1070</v>
+        <v>1074</v>
       </c>
       <c r="H117" t="str">
         <v>2025-11-01</v>
@@ -4152,7 +4152,7 @@
         <v>2026-11-31</v>
       </c>
       <c r="J117" t="str">
-        <v>Occupied</v>
+        <v>Notice</v>
       </c>
     </row>
     <row r="118">
@@ -4175,7 +4175,7 @@
         <v>2003</v>
       </c>
       <c r="G118">
-        <v>1040</v>
+        <v>1043.25</v>
       </c>
       <c r="H118" t="str">
         <v>2025-10-01</v>
@@ -4184,7 +4184,7 @@
         <v>2026-10-31</v>
       </c>
       <c r="J118" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="119">
@@ -4207,7 +4207,7 @@
         <v>1993</v>
       </c>
       <c r="G119">
-        <v>1070</v>
+        <v>1074</v>
       </c>
       <c r="H119" t="str">
         <v>2025-11-01</v>
@@ -4216,7 +4216,7 @@
         <v>2026-11-31</v>
       </c>
       <c r="J119" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="120">
@@ -4239,7 +4239,7 @@
         <v>1995</v>
       </c>
       <c r="G120">
-        <v>1100</v>
+        <v>1104.75</v>
       </c>
       <c r="H120" t="str">
         <v>2025-12-01</v>
@@ -4248,7 +4248,7 @@
         <v>2026-12-31</v>
       </c>
       <c r="J120" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="121">
@@ -4271,7 +4271,7 @@
         <v>1997</v>
       </c>
       <c r="G121">
-        <v>1130</v>
+        <v>1135.5</v>
       </c>
       <c r="H121" t="str">
         <v>2025-01-01</v>
@@ -4280,7 +4280,7 @@
         <v>2026-01-31</v>
       </c>
       <c r="J121" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="122">
@@ -4303,7 +4303,7 @@
         <v>2003</v>
       </c>
       <c r="G122">
-        <v>1040</v>
+        <v>1043.25</v>
       </c>
       <c r="H122" t="str">
         <v>2025-10-01</v>
@@ -4312,7 +4312,7 @@
         <v>2026-10-31</v>
       </c>
       <c r="J122" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="123">
@@ -4335,7 +4335,7 @@
         <v>1993</v>
       </c>
       <c r="G123">
-        <v>1070</v>
+        <v>1074</v>
       </c>
       <c r="H123" t="str">
         <v>2025-11-01</v>
@@ -4344,7 +4344,7 @@
         <v>2026-11-31</v>
       </c>
       <c r="J123" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="124">
@@ -4367,7 +4367,7 @@
         <v>1995</v>
       </c>
       <c r="G124">
-        <v>1100</v>
+        <v>1104.75</v>
       </c>
       <c r="H124" t="str">
         <v>2025-12-01</v>
@@ -4376,7 +4376,7 @@
         <v>2026-12-31</v>
       </c>
       <c r="J124" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="125">
@@ -4399,7 +4399,7 @@
         <v>1997</v>
       </c>
       <c r="G125">
-        <v>1130</v>
+        <v>1135.5</v>
       </c>
       <c r="H125" t="str">
         <v>2025-01-01</v>
@@ -4408,7 +4408,7 @@
         <v>2026-01-31</v>
       </c>
       <c r="J125" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="126">
@@ -4431,7 +4431,7 @@
         <v>1999</v>
       </c>
       <c r="G126">
-        <v>1160</v>
+        <v>1166.25</v>
       </c>
       <c r="H126" t="str">
         <v>2025-02-01</v>
@@ -4440,7 +4440,7 @@
         <v>2026-02-31</v>
       </c>
       <c r="J126" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="127">
@@ -4463,7 +4463,7 @@
         <v>2004</v>
       </c>
       <c r="G127">
-        <v>1060</v>
+        <v>1063.5</v>
       </c>
       <c r="H127" t="str">
         <v>2025-11-01</v>
@@ -4472,7 +4472,7 @@
         <v>2026-11-31</v>
       </c>
       <c r="J127" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="128">
@@ -4495,7 +4495,7 @@
         <v>1994</v>
       </c>
       <c r="G128">
-        <v>1090</v>
+        <v>1094.25</v>
       </c>
       <c r="H128" t="str">
         <v>2025-12-01</v>
@@ -4504,7 +4504,7 @@
         <v>2026-12-31</v>
       </c>
       <c r="J128" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="129">
@@ -4527,7 +4527,7 @@
         <v>1996</v>
       </c>
       <c r="G129">
-        <v>1120</v>
+        <v>1125</v>
       </c>
       <c r="H129" t="str">
         <v>2025-01-01</v>
@@ -4536,7 +4536,7 @@
         <v>2026-01-31</v>
       </c>
       <c r="J129" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="130">
@@ -4559,7 +4559,7 @@
         <v>1998</v>
       </c>
       <c r="G130">
-        <v>1150</v>
+        <v>1155.75</v>
       </c>
       <c r="H130" t="str">
         <v>2025-02-01</v>
@@ -4568,7 +4568,7 @@
         <v>2026-02-31</v>
       </c>
       <c r="J130" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="131">
@@ -4591,7 +4591,7 @@
         <v>2000</v>
       </c>
       <c r="G131">
-        <v>1180</v>
+        <v>1186.5</v>
       </c>
       <c r="H131" t="str">
         <v>2025-03-01</v>
@@ -4600,7 +4600,7 @@
         <v>2026-03-31</v>
       </c>
       <c r="J131" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="132">
@@ -4623,7 +4623,7 @@
         <v>2004</v>
       </c>
       <c r="G132">
-        <v>1060</v>
+        <v>1063.5</v>
       </c>
       <c r="H132" t="str">
         <v>2025-11-01</v>
@@ -4632,7 +4632,7 @@
         <v>2026-11-31</v>
       </c>
       <c r="J132" t="str">
-        <v>Secured</v>
+        <v>Future</v>
       </c>
     </row>
     <row r="133">
@@ -4655,7 +4655,7 @@
         <v>1994</v>
       </c>
       <c r="G133">
-        <v>1090</v>
+        <v>1094.25</v>
       </c>
       <c r="H133" t="str">
         <v>2025-12-01</v>
@@ -4664,7 +4664,7 @@
         <v>2026-12-31</v>
       </c>
       <c r="J133" t="str">
-        <v>Secured</v>
+        <v>Future</v>
       </c>
     </row>
     <row r="134">
@@ -4687,7 +4687,7 @@
         <v>1996</v>
       </c>
       <c r="G134">
-        <v>1120</v>
+        <v>1125</v>
       </c>
       <c r="H134" t="str">
         <v>2025-01-01</v>
@@ -4696,7 +4696,7 @@
         <v>2026-01-31</v>
       </c>
       <c r="J134" t="str">
-        <v>Secured</v>
+        <v>Future</v>
       </c>
     </row>
     <row r="135">
@@ -4719,7 +4719,7 @@
         <v>1998</v>
       </c>
       <c r="G135">
-        <v>1150</v>
+        <v>1155.75</v>
       </c>
       <c r="H135" t="str">
         <v>2025-02-01</v>
@@ -4728,7 +4728,7 @@
         <v>2026-02-31</v>
       </c>
       <c r="J135" t="str">
-        <v>Secured</v>
+        <v>Future</v>
       </c>
     </row>
     <row r="136">
@@ -4751,7 +4751,7 @@
         <v>2004</v>
       </c>
       <c r="G136">
-        <v>1060</v>
+        <v>1063.5</v>
       </c>
       <c r="H136" t="str">
         <v>2025-11-01</v>
@@ -4760,7 +4760,7 @@
         <v>2026-11-31</v>
       </c>
       <c r="J136" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="137">
@@ -4783,7 +4783,7 @@
         <v>1994</v>
       </c>
       <c r="G137">
-        <v>1090</v>
+        <v>1094.25</v>
       </c>
       <c r="H137" t="str">
         <v>2025-12-01</v>
@@ -4792,7 +4792,7 @@
         <v>2026-12-31</v>
       </c>
       <c r="J137" t="str">
-        <v>Occupied</v>
+        <v>Notice</v>
       </c>
     </row>
     <row r="138">
@@ -4815,7 +4815,7 @@
         <v>2004</v>
       </c>
       <c r="G138">
-        <v>1060</v>
+        <v>1063.5</v>
       </c>
       <c r="H138" t="str">
         <v>2025-11-01</v>
@@ -4824,7 +4824,7 @@
         <v>2026-11-31</v>
       </c>
       <c r="J138" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="139">
@@ -4847,7 +4847,7 @@
         <v>1994</v>
       </c>
       <c r="G139">
-        <v>1090</v>
+        <v>1094.25</v>
       </c>
       <c r="H139" t="str">
         <v>2025-12-01</v>
@@ -4856,7 +4856,7 @@
         <v>2026-12-31</v>
       </c>
       <c r="J139" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="140">
@@ -4879,7 +4879,7 @@
         <v>1996</v>
       </c>
       <c r="G140">
-        <v>1120</v>
+        <v>1125</v>
       </c>
       <c r="H140" t="str">
         <v>2025-01-01</v>
@@ -4888,7 +4888,7 @@
         <v>2026-01-31</v>
       </c>
       <c r="J140" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="141">
@@ -4911,7 +4911,7 @@
         <v>2004</v>
       </c>
       <c r="G141">
-        <v>1060</v>
+        <v>1063.5</v>
       </c>
       <c r="H141" t="str">
         <v>2025-11-01</v>
@@ -4920,7 +4920,7 @@
         <v>2026-11-31</v>
       </c>
       <c r="J141" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="142">
@@ -4943,7 +4943,7 @@
         <v>1994</v>
       </c>
       <c r="G142">
-        <v>1090</v>
+        <v>1094.25</v>
       </c>
       <c r="H142" t="str">
         <v>2025-12-01</v>
@@ -4952,7 +4952,7 @@
         <v>2026-12-31</v>
       </c>
       <c r="J142" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="143">
@@ -4975,7 +4975,7 @@
         <v>1996</v>
       </c>
       <c r="G143">
-        <v>1120</v>
+        <v>1125</v>
       </c>
       <c r="H143" t="str">
         <v>2025-01-01</v>
@@ -4984,7 +4984,7 @@
         <v>2026-01-31</v>
       </c>
       <c r="J143" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="144">
@@ -5007,7 +5007,7 @@
         <v>1998</v>
       </c>
       <c r="G144">
-        <v>1150</v>
+        <v>1155.75</v>
       </c>
       <c r="H144" t="str">
         <v>2025-02-01</v>
@@ -5016,7 +5016,7 @@
         <v>2026-02-31</v>
       </c>
       <c r="J144" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="145">
@@ -5039,7 +5039,7 @@
         <v>2004</v>
       </c>
       <c r="G145">
-        <v>1060</v>
+        <v>1063.5</v>
       </c>
       <c r="H145" t="str">
         <v>2025-11-01</v>
@@ -5048,7 +5048,7 @@
         <v>2026-11-31</v>
       </c>
       <c r="J145" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="146">
@@ -5071,7 +5071,7 @@
         <v>1994</v>
       </c>
       <c r="G146">
-        <v>1090</v>
+        <v>1094.25</v>
       </c>
       <c r="H146" t="str">
         <v>2025-12-01</v>
@@ -5080,7 +5080,7 @@
         <v>2026-12-31</v>
       </c>
       <c r="J146" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="147">
@@ -5103,7 +5103,7 @@
         <v>1998</v>
       </c>
       <c r="G147">
-        <v>1150</v>
+        <v>1155.75</v>
       </c>
       <c r="H147" t="str">
         <v>2025-02-01</v>
@@ -5112,7 +5112,7 @@
         <v>2026-02-31</v>
       </c>
       <c r="J147" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="148">
@@ -5135,7 +5135,7 @@
         <v>2000</v>
       </c>
       <c r="G148">
-        <v>1180</v>
+        <v>1186.5</v>
       </c>
       <c r="H148" t="str">
         <v>2025-03-01</v>
@@ -5144,7 +5144,7 @@
         <v>2026-03-31</v>
       </c>
       <c r="J148" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="149">
@@ -5167,7 +5167,7 @@
         <v>1993</v>
       </c>
       <c r="G149">
-        <v>1080</v>
+        <v>1083.75</v>
       </c>
       <c r="H149" t="str">
         <v>2025-12-01</v>
@@ -5176,7 +5176,7 @@
         <v>2026-12-31</v>
       </c>
       <c r="J149" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="150">
@@ -5199,7 +5199,7 @@
         <v>1995</v>
       </c>
       <c r="G150">
-        <v>1110</v>
+        <v>1114.5</v>
       </c>
       <c r="H150" t="str">
         <v>2025-01-01</v>
@@ -5208,7 +5208,7 @@
         <v>2026-01-31</v>
       </c>
       <c r="J150" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="151">
@@ -5231,7 +5231,7 @@
         <v>1997</v>
       </c>
       <c r="G151">
-        <v>1140</v>
+        <v>1145.25</v>
       </c>
       <c r="H151" t="str">
         <v>2025-02-01</v>
@@ -5240,7 +5240,7 @@
         <v>2026-02-31</v>
       </c>
       <c r="J151" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="152">
@@ -5263,7 +5263,7 @@
         <v>1999</v>
       </c>
       <c r="G152">
-        <v>1170</v>
+        <v>1176</v>
       </c>
       <c r="H152" t="str">
         <v>2025-03-01</v>
@@ -5272,7 +5272,7 @@
         <v>2026-03-31</v>
       </c>
       <c r="J152" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="153">
@@ -5295,7 +5295,7 @@
         <v>2001</v>
       </c>
       <c r="G153">
-        <v>1200</v>
+        <v>1206.75</v>
       </c>
       <c r="H153" t="str">
         <v>2025-04-01</v>
@@ -5304,7 +5304,7 @@
         <v>2026-04-31</v>
       </c>
       <c r="J153" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="154">
@@ -5327,7 +5327,7 @@
         <v>1993</v>
       </c>
       <c r="G154">
-        <v>1080</v>
+        <v>1083.75</v>
       </c>
       <c r="H154" t="str">
         <v>2025-12-01</v>
@@ -5336,7 +5336,7 @@
         <v>2026-12-31</v>
       </c>
       <c r="J154" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="155">
@@ -5359,7 +5359,7 @@
         <v>1995</v>
       </c>
       <c r="G155">
-        <v>1110</v>
+        <v>1114.5</v>
       </c>
       <c r="H155" t="str">
         <v>2025-01-01</v>
@@ -5368,7 +5368,7 @@
         <v>2026-01-31</v>
       </c>
       <c r="J155" t="str">
-        <v>Occupied</v>
+        <v>Notice</v>
       </c>
     </row>
     <row r="156">
@@ -5391,7 +5391,7 @@
         <v>1999</v>
       </c>
       <c r="G156">
-        <v>1170</v>
+        <v>1176</v>
       </c>
       <c r="H156" t="str">
         <v>2025-03-01</v>
@@ -5400,7 +5400,7 @@
         <v>2026-03-31</v>
       </c>
       <c r="J156" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="157">
@@ -5423,7 +5423,7 @@
         <v>1993</v>
       </c>
       <c r="G157">
-        <v>1080</v>
+        <v>1083.75</v>
       </c>
       <c r="H157" t="str">
         <v>2025-12-01</v>
@@ -5432,7 +5432,7 @@
         <v>2026-12-31</v>
       </c>
       <c r="J157" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="158">
@@ -5455,7 +5455,7 @@
         <v>1995</v>
       </c>
       <c r="G158">
-        <v>1110</v>
+        <v>1114.5</v>
       </c>
       <c r="H158" t="str">
         <v>2025-01-01</v>
@@ -5464,7 +5464,7 @@
         <v>2026-01-31</v>
       </c>
       <c r="J158" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="159">
@@ -5487,7 +5487,7 @@
         <v>1997</v>
       </c>
       <c r="G159">
-        <v>1140</v>
+        <v>1145.25</v>
       </c>
       <c r="H159" t="str">
         <v>2025-02-01</v>
@@ -5496,7 +5496,7 @@
         <v>2026-02-31</v>
       </c>
       <c r="J159" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="160">
@@ -5519,7 +5519,7 @@
         <v>1993</v>
       </c>
       <c r="G160">
-        <v>1080</v>
+        <v>1083.75</v>
       </c>
       <c r="H160" t="str">
         <v>2025-12-01</v>
@@ -5528,7 +5528,7 @@
         <v>2026-12-31</v>
       </c>
       <c r="J160" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="161">
@@ -5551,7 +5551,7 @@
         <v>1995</v>
       </c>
       <c r="G161">
-        <v>1110</v>
+        <v>1114.5</v>
       </c>
       <c r="H161" t="str">
         <v>2025-01-01</v>
@@ -5560,7 +5560,7 @@
         <v>2026-01-31</v>
       </c>
       <c r="J161" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="162">
@@ -5583,7 +5583,7 @@
         <v>1997</v>
       </c>
       <c r="G162">
-        <v>1140</v>
+        <v>1145.25</v>
       </c>
       <c r="H162" t="str">
         <v>2025-02-01</v>
@@ -5592,7 +5592,7 @@
         <v>2026-02-31</v>
       </c>
       <c r="J162" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="163">
@@ -5615,7 +5615,7 @@
         <v>1993</v>
       </c>
       <c r="G163">
-        <v>1080</v>
+        <v>1083.75</v>
       </c>
       <c r="H163" t="str">
         <v>2025-12-01</v>
@@ -5624,7 +5624,7 @@
         <v>2026-12-31</v>
       </c>
       <c r="J163" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="164">
@@ -5647,7 +5647,7 @@
         <v>1995</v>
       </c>
       <c r="G164">
-        <v>1110</v>
+        <v>1114.5</v>
       </c>
       <c r="H164" t="str">
         <v>2025-01-01</v>
@@ -5656,7 +5656,7 @@
         <v>2026-01-31</v>
       </c>
       <c r="J164" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="165">
@@ -5679,7 +5679,7 @@
         <v>1999</v>
       </c>
       <c r="G165">
-        <v>1170</v>
+        <v>1176</v>
       </c>
       <c r="H165" t="str">
         <v>2025-03-01</v>
@@ -5688,7 +5688,7 @@
         <v>2026-03-31</v>
       </c>
       <c r="J165" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="166">
@@ -5711,7 +5711,7 @@
         <v>1993</v>
       </c>
       <c r="G166">
-        <v>1080</v>
+        <v>1083.75</v>
       </c>
       <c r="H166" t="str">
         <v>2025-12-01</v>
@@ -5720,7 +5720,7 @@
         <v>2026-12-31</v>
       </c>
       <c r="J166" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="167">
@@ -5743,7 +5743,7 @@
         <v>1995</v>
       </c>
       <c r="G167">
-        <v>1110</v>
+        <v>1114.5</v>
       </c>
       <c r="H167" t="str">
         <v>2025-01-01</v>
@@ -5752,7 +5752,7 @@
         <v>2026-01-31</v>
       </c>
       <c r="J167" t="str">
-        <v>Occupied</v>
+        <v>Notice</v>
       </c>
     </row>
     <row r="168">
@@ -5775,7 +5775,7 @@
         <v>1997</v>
       </c>
       <c r="G168">
-        <v>1140</v>
+        <v>1145.25</v>
       </c>
       <c r="H168" t="str">
         <v>2025-02-01</v>
@@ -5784,7 +5784,7 @@
         <v>2026-02-31</v>
       </c>
       <c r="J168" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="169">
@@ -5807,7 +5807,7 @@
         <v>1999</v>
       </c>
       <c r="G169">
-        <v>1170</v>
+        <v>1176</v>
       </c>
       <c r="H169" t="str">
         <v>2025-03-01</v>
@@ -5816,7 +5816,7 @@
         <v>2026-03-31</v>
       </c>
       <c r="J169" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="170">
@@ -5839,7 +5839,7 @@
         <v>2001</v>
       </c>
       <c r="G170">
-        <v>1200</v>
+        <v>1206.75</v>
       </c>
       <c r="H170" t="str">
         <v>2025-04-01</v>
@@ -5848,7 +5848,7 @@
         <v>2026-04-31</v>
       </c>
       <c r="J170" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="171">
@@ -5871,7 +5871,7 @@
         <v>1994</v>
       </c>
       <c r="G171">
-        <v>1100</v>
+        <v>1104</v>
       </c>
       <c r="H171" t="str">
         <v>2025-01-01</v>
@@ -5880,7 +5880,7 @@
         <v>2026-01-31</v>
       </c>
       <c r="J171" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="172">
@@ -5903,7 +5903,7 @@
         <v>1996</v>
       </c>
       <c r="G172">
-        <v>1130</v>
+        <v>1134.75</v>
       </c>
       <c r="H172" t="str">
         <v>2025-02-01</v>
@@ -5912,7 +5912,7 @@
         <v>2026-02-31</v>
       </c>
       <c r="J172" t="str">
-        <v>Occupied</v>
+        <v>Notice</v>
       </c>
     </row>
     <row r="173">
@@ -5935,7 +5935,7 @@
         <v>2000</v>
       </c>
       <c r="G173">
-        <v>1190</v>
+        <v>1196.25</v>
       </c>
       <c r="H173" t="str">
         <v>2025-04-01</v>
@@ -5944,7 +5944,7 @@
         <v>2026-04-31</v>
       </c>
       <c r="J173" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="174">
@@ -5967,7 +5967,7 @@
         <v>2002</v>
       </c>
       <c r="G174">
-        <v>1220</v>
+        <v>1227</v>
       </c>
       <c r="H174" t="str">
         <v>2025-05-01</v>
@@ -5976,7 +5976,7 @@
         <v>2026-05-31</v>
       </c>
       <c r="J174" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="175">
@@ -5999,7 +5999,7 @@
         <v>1994</v>
       </c>
       <c r="G175">
-        <v>1100</v>
+        <v>1104</v>
       </c>
       <c r="H175" t="str">
         <v>2025-01-01</v>
@@ -6008,7 +6008,7 @@
         <v>2026-01-31</v>
       </c>
       <c r="J175" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="176">
@@ -6031,7 +6031,7 @@
         <v>1996</v>
       </c>
       <c r="G176">
-        <v>1130</v>
+        <v>1134.75</v>
       </c>
       <c r="H176" t="str">
         <v>2025-02-01</v>
@@ -6040,7 +6040,7 @@
         <v>2026-02-31</v>
       </c>
       <c r="J176" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="177">
@@ -6063,7 +6063,7 @@
         <v>1998</v>
       </c>
       <c r="G177">
-        <v>1160</v>
+        <v>1165.5</v>
       </c>
       <c r="H177" t="str">
         <v>2025-03-01</v>
@@ -6072,7 +6072,7 @@
         <v>2026-03-31</v>
       </c>
       <c r="J177" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="178">
@@ -6095,7 +6095,7 @@
         <v>2000</v>
       </c>
       <c r="G178">
-        <v>1190</v>
+        <v>1196.25</v>
       </c>
       <c r="H178" t="str">
         <v>2025-04-01</v>
@@ -6104,7 +6104,7 @@
         <v>2026-04-31</v>
       </c>
       <c r="J178" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="179">
@@ -6127,7 +6127,7 @@
         <v>1994</v>
       </c>
       <c r="G179">
-        <v>1100</v>
+        <v>1104</v>
       </c>
       <c r="H179" t="str">
         <v>2025-01-01</v>
@@ -6136,7 +6136,7 @@
         <v>2026-01-31</v>
       </c>
       <c r="J179" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="180">
@@ -6159,7 +6159,7 @@
         <v>1996</v>
       </c>
       <c r="G180">
-        <v>1130</v>
+        <v>1134.75</v>
       </c>
       <c r="H180" t="str">
         <v>2025-02-01</v>
@@ -6168,7 +6168,7 @@
         <v>2026-02-31</v>
       </c>
       <c r="J180" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="181">
@@ -6191,7 +6191,7 @@
         <v>1998</v>
       </c>
       <c r="G181">
-        <v>1160</v>
+        <v>1165.5</v>
       </c>
       <c r="H181" t="str">
         <v>2025-03-01</v>
@@ -6200,7 +6200,7 @@
         <v>2026-03-31</v>
       </c>
       <c r="J181" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="182">
@@ -6223,7 +6223,7 @@
         <v>1994</v>
       </c>
       <c r="G182">
-        <v>1100</v>
+        <v>1104</v>
       </c>
       <c r="H182" t="str">
         <v>2025-01-01</v>
@@ -6232,7 +6232,7 @@
         <v>2026-01-31</v>
       </c>
       <c r="J182" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="183">
@@ -6255,7 +6255,7 @@
         <v>1996</v>
       </c>
       <c r="G183">
-        <v>1130</v>
+        <v>1134.75</v>
       </c>
       <c r="H183" t="str">
         <v>2025-02-01</v>
@@ -6264,7 +6264,7 @@
         <v>2026-02-31</v>
       </c>
       <c r="J183" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="184">
@@ -6287,7 +6287,7 @@
         <v>1994</v>
       </c>
       <c r="G184">
-        <v>1100</v>
+        <v>1104</v>
       </c>
       <c r="H184" t="str">
         <v>2025-01-01</v>
@@ -6296,7 +6296,7 @@
         <v>2026-01-31</v>
       </c>
       <c r="J184" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="185">
@@ -6319,7 +6319,7 @@
         <v>1996</v>
       </c>
       <c r="G185">
-        <v>1130</v>
+        <v>1134.75</v>
       </c>
       <c r="H185" t="str">
         <v>2025-02-01</v>
@@ -6328,7 +6328,7 @@
         <v>2026-02-31</v>
       </c>
       <c r="J185" t="str">
-        <v>Occupied</v>
+        <v>Notice</v>
       </c>
     </row>
     <row r="186">
@@ -6351,7 +6351,7 @@
         <v>1998</v>
       </c>
       <c r="G186">
-        <v>1160</v>
+        <v>1165.5</v>
       </c>
       <c r="H186" t="str">
         <v>2025-03-01</v>
@@ -6360,7 +6360,7 @@
         <v>2026-03-31</v>
       </c>
       <c r="J186" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="187">
@@ -6383,7 +6383,7 @@
         <v>2000</v>
       </c>
       <c r="G187">
-        <v>1190</v>
+        <v>1196.25</v>
       </c>
       <c r="H187" t="str">
         <v>2025-04-01</v>
@@ -6392,7 +6392,7 @@
         <v>2026-04-31</v>
       </c>
       <c r="J187" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="188">
@@ -6415,7 +6415,7 @@
         <v>1994</v>
       </c>
       <c r="G188">
-        <v>1100</v>
+        <v>1104</v>
       </c>
       <c r="H188" t="str">
         <v>2025-01-01</v>
@@ -6424,7 +6424,7 @@
         <v>2026-01-31</v>
       </c>
       <c r="J188" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="189">
@@ -6447,7 +6447,7 @@
         <v>1996</v>
       </c>
       <c r="G189">
-        <v>1130</v>
+        <v>1134.75</v>
       </c>
       <c r="H189" t="str">
         <v>2025-02-01</v>
@@ -6456,7 +6456,7 @@
         <v>2026-02-31</v>
       </c>
       <c r="J189" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="190">
@@ -6479,7 +6479,7 @@
         <v>1998</v>
       </c>
       <c r="G190">
-        <v>1160</v>
+        <v>1165.5</v>
       </c>
       <c r="H190" t="str">
         <v>2025-03-01</v>
@@ -6488,7 +6488,7 @@
         <v>2026-03-31</v>
       </c>
       <c r="J190" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="191">
@@ -6511,7 +6511,7 @@
         <v>2000</v>
       </c>
       <c r="G191">
-        <v>1190</v>
+        <v>1196.25</v>
       </c>
       <c r="H191" t="str">
         <v>2025-04-01</v>
@@ -6520,7 +6520,7 @@
         <v>2026-04-31</v>
       </c>
       <c r="J191" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="192">
@@ -6543,7 +6543,7 @@
         <v>2002</v>
       </c>
       <c r="G192">
-        <v>1220</v>
+        <v>1227</v>
       </c>
       <c r="H192" t="str">
         <v>2025-05-01</v>
@@ -6552,7 +6552,7 @@
         <v>2026-05-31</v>
       </c>
       <c r="J192" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="193">
@@ -6575,7 +6575,7 @@
         <v>1995</v>
       </c>
       <c r="G193">
-        <v>1120</v>
+        <v>1124.25</v>
       </c>
       <c r="H193" t="str">
         <v>2025-02-01</v>
@@ -6584,7 +6584,7 @@
         <v>2026-02-31</v>
       </c>
       <c r="J193" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="194">
@@ -6607,7 +6607,7 @@
         <v>1997</v>
       </c>
       <c r="G194">
-        <v>1150</v>
+        <v>1155</v>
       </c>
       <c r="H194" t="str">
         <v>2025-03-01</v>
@@ -6616,7 +6616,7 @@
         <v>2026-03-31</v>
       </c>
       <c r="J194" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="195">
@@ -6639,7 +6639,7 @@
         <v>1999</v>
       </c>
       <c r="G195">
-        <v>1180</v>
+        <v>1185.75</v>
       </c>
       <c r="H195" t="str">
         <v>2025-04-01</v>
@@ -6648,7 +6648,7 @@
         <v>2026-04-31</v>
       </c>
       <c r="J195" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="196">
@@ -6671,7 +6671,7 @@
         <v>2001</v>
       </c>
       <c r="G196">
-        <v>1210</v>
+        <v>1216.5</v>
       </c>
       <c r="H196" t="str">
         <v>2025-05-01</v>
@@ -6680,7 +6680,7 @@
         <v>2026-05-31</v>
       </c>
       <c r="J196" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="197">
@@ -6703,7 +6703,7 @@
         <v>2003</v>
       </c>
       <c r="G197">
-        <v>1240</v>
+        <v>1247.25</v>
       </c>
       <c r="H197" t="str">
         <v>2025-06-01</v>
@@ -6712,7 +6712,7 @@
         <v>2026-06-31</v>
       </c>
       <c r="J197" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="198">
@@ -6735,7 +6735,7 @@
         <v>1995</v>
       </c>
       <c r="G198">
-        <v>1120</v>
+        <v>1124.25</v>
       </c>
       <c r="H198" t="str">
         <v>2025-02-01</v>
@@ -6744,7 +6744,7 @@
         <v>2026-02-31</v>
       </c>
       <c r="J198" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="199">
@@ -6767,7 +6767,7 @@
         <v>1997</v>
       </c>
       <c r="G199">
-        <v>1150</v>
+        <v>1155</v>
       </c>
       <c r="H199" t="str">
         <v>2025-03-01</v>
@@ -6776,7 +6776,7 @@
         <v>2026-03-31</v>
       </c>
       <c r="J199" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="200">
@@ -6799,7 +6799,7 @@
         <v>1999</v>
       </c>
       <c r="G200">
-        <v>1180</v>
+        <v>1185.75</v>
       </c>
       <c r="H200" t="str">
         <v>2025-04-01</v>
@@ -6808,7 +6808,7 @@
         <v>2026-04-31</v>
       </c>
       <c r="J200" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="201">
@@ -6831,7 +6831,7 @@
         <v>2001</v>
       </c>
       <c r="G201">
-        <v>1210</v>
+        <v>1216.5</v>
       </c>
       <c r="H201" t="str">
         <v>2025-05-01</v>
@@ -6840,7 +6840,7 @@
         <v>2026-05-31</v>
       </c>
       <c r="J201" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="202">
@@ -6863,7 +6863,7 @@
         <v>1995</v>
       </c>
       <c r="G202">
-        <v>1120</v>
+        <v>1124.25</v>
       </c>
       <c r="H202" t="str">
         <v>2025-02-01</v>
@@ -6872,7 +6872,7 @@
         <v>2026-02-31</v>
       </c>
       <c r="J202" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="203">
@@ -6895,7 +6895,7 @@
         <v>1997</v>
       </c>
       <c r="G203">
-        <v>1150</v>
+        <v>1155</v>
       </c>
       <c r="H203" t="str">
         <v>2025-03-01</v>
@@ -6904,7 +6904,7 @@
         <v>2026-03-31</v>
       </c>
       <c r="J203" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="204">
@@ -6927,7 +6927,7 @@
         <v>1995</v>
       </c>
       <c r="G204">
-        <v>1120</v>
+        <v>1124.25</v>
       </c>
       <c r="H204" t="str">
         <v>2025-02-01</v>
@@ -6936,7 +6936,7 @@
         <v>2026-02-31</v>
       </c>
       <c r="J204" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="205">
@@ -6959,7 +6959,7 @@
         <v>1997</v>
       </c>
       <c r="G205">
-        <v>1150</v>
+        <v>1155</v>
       </c>
       <c r="H205" t="str">
         <v>2025-03-01</v>
@@ -6968,7 +6968,7 @@
         <v>2026-03-31</v>
       </c>
       <c r="J205" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="206">
@@ -6991,7 +6991,7 @@
         <v>1999</v>
       </c>
       <c r="G206">
-        <v>1180</v>
+        <v>1185.75</v>
       </c>
       <c r="H206" t="str">
         <v>2025-04-01</v>
@@ -7000,7 +7000,7 @@
         <v>2026-04-31</v>
       </c>
       <c r="J206" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="207">
@@ -7023,7 +7023,7 @@
         <v>2001</v>
       </c>
       <c r="G207">
-        <v>1210</v>
+        <v>1216.5</v>
       </c>
       <c r="H207" t="str">
         <v>2025-05-01</v>
@@ -7032,7 +7032,7 @@
         <v>2026-05-31</v>
       </c>
       <c r="J207" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="208">
@@ -7055,7 +7055,7 @@
         <v>1995</v>
       </c>
       <c r="G208">
-        <v>1120</v>
+        <v>1124.25</v>
       </c>
       <c r="H208" t="str">
         <v>2025-02-01</v>
@@ -7064,7 +7064,7 @@
         <v>2026-02-31</v>
       </c>
       <c r="J208" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="209">
@@ -7087,7 +7087,7 @@
         <v>1997</v>
       </c>
       <c r="G209">
-        <v>1150</v>
+        <v>1155</v>
       </c>
       <c r="H209" t="str">
         <v>2025-03-01</v>
@@ -7096,7 +7096,7 @@
         <v>2026-03-31</v>
       </c>
       <c r="J209" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="210">
@@ -7119,7 +7119,7 @@
         <v>2001</v>
       </c>
       <c r="G210">
-        <v>1210</v>
+        <v>1216.5</v>
       </c>
       <c r="H210" t="str">
         <v>2025-05-01</v>
@@ -7128,7 +7128,7 @@
         <v>2026-05-31</v>
       </c>
       <c r="J210" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="211">
@@ -7151,7 +7151,7 @@
         <v>2003</v>
       </c>
       <c r="G211">
-        <v>1240</v>
+        <v>1247.25</v>
       </c>
       <c r="H211" t="str">
         <v>2025-06-01</v>
@@ -7160,7 +7160,7 @@
         <v>2026-06-31</v>
       </c>
       <c r="J211" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="212">
@@ -7183,7 +7183,7 @@
         <v>1996</v>
       </c>
       <c r="G212">
-        <v>1140</v>
+        <v>1144.5</v>
       </c>
       <c r="H212" t="str">
         <v>2025-03-01</v>
@@ -7192,7 +7192,7 @@
         <v>2026-03-31</v>
       </c>
       <c r="J212" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="213">
@@ -7215,7 +7215,7 @@
         <v>1998</v>
       </c>
       <c r="G213">
-        <v>1170</v>
+        <v>1175.25</v>
       </c>
       <c r="H213" t="str">
         <v>2025-04-01</v>
@@ -7224,7 +7224,7 @@
         <v>2026-04-31</v>
       </c>
       <c r="J213" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="214">
@@ -7247,7 +7247,7 @@
         <v>2000</v>
       </c>
       <c r="G214">
-        <v>1200</v>
+        <v>1206</v>
       </c>
       <c r="H214" t="str">
         <v>2025-05-01</v>
@@ -7256,7 +7256,7 @@
         <v>2026-05-31</v>
       </c>
       <c r="J214" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="215">
@@ -7279,7 +7279,7 @@
         <v>2002</v>
       </c>
       <c r="G215">
-        <v>1230</v>
+        <v>1236.75</v>
       </c>
       <c r="H215" t="str">
         <v>2025-06-01</v>
@@ -7288,7 +7288,7 @@
         <v>2026-06-31</v>
       </c>
       <c r="J215" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="216">
@@ -7311,7 +7311,7 @@
         <v>2004</v>
       </c>
       <c r="G216">
-        <v>1260</v>
+        <v>1267.5</v>
       </c>
       <c r="H216" t="str">
         <v>2025-07-01</v>
@@ -7320,7 +7320,7 @@
         <v>2026-07-31</v>
       </c>
       <c r="J216" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="217">
@@ -7343,7 +7343,7 @@
         <v>1996</v>
       </c>
       <c r="G217">
-        <v>1140</v>
+        <v>1144.5</v>
       </c>
       <c r="H217" t="str">
         <v>2025-03-01</v>
@@ -7352,7 +7352,7 @@
         <v>2026-03-31</v>
       </c>
       <c r="J217" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="218">
@@ -7375,7 +7375,7 @@
         <v>1998</v>
       </c>
       <c r="G218">
-        <v>1170</v>
+        <v>1175.25</v>
       </c>
       <c r="H218" t="str">
         <v>2025-04-01</v>
@@ -7384,7 +7384,7 @@
         <v>2026-04-31</v>
       </c>
       <c r="J218" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="219">
@@ -7407,7 +7407,7 @@
         <v>2002</v>
       </c>
       <c r="G219">
-        <v>1230</v>
+        <v>1236.75</v>
       </c>
       <c r="H219" t="str">
         <v>2025-06-01</v>
@@ -7416,7 +7416,7 @@
         <v>2026-06-31</v>
       </c>
       <c r="J219" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="220">
@@ -7439,7 +7439,7 @@
         <v>1996</v>
       </c>
       <c r="G220">
-        <v>1140</v>
+        <v>1144.5</v>
       </c>
       <c r="H220" t="str">
         <v>2025-03-01</v>
@@ -7448,7 +7448,7 @@
         <v>2026-03-31</v>
       </c>
       <c r="J220" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="221">
@@ -7471,7 +7471,7 @@
         <v>1998</v>
       </c>
       <c r="G221">
-        <v>1170</v>
+        <v>1175.25</v>
       </c>
       <c r="H221" t="str">
         <v>2025-04-01</v>
@@ -7480,7 +7480,7 @@
         <v>2026-04-31</v>
       </c>
       <c r="J221" t="str">
-        <v>Occupied</v>
+        <v>Notice</v>
       </c>
     </row>
     <row r="222">
@@ -7503,7 +7503,7 @@
         <v>2000</v>
       </c>
       <c r="G222">
-        <v>1200</v>
+        <v>1206</v>
       </c>
       <c r="H222" t="str">
         <v>2025-05-01</v>
@@ -7512,7 +7512,7 @@
         <v>2026-05-31</v>
       </c>
       <c r="J222" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="223">
@@ -7535,7 +7535,7 @@
         <v>1996</v>
       </c>
       <c r="G223">
-        <v>1140</v>
+        <v>1144.5</v>
       </c>
       <c r="H223" t="str">
         <v>2025-03-01</v>
@@ -7544,7 +7544,7 @@
         <v>2026-03-31</v>
       </c>
       <c r="J223" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="224">
@@ -7567,7 +7567,7 @@
         <v>1998</v>
       </c>
       <c r="G224">
-        <v>1170</v>
+        <v>1175.25</v>
       </c>
       <c r="H224" t="str">
         <v>2025-04-01</v>
@@ -7576,7 +7576,7 @@
         <v>2026-04-31</v>
       </c>
       <c r="J224" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="225">
@@ -7599,7 +7599,7 @@
         <v>2000</v>
       </c>
       <c r="G225">
-        <v>1200</v>
+        <v>1206</v>
       </c>
       <c r="H225" t="str">
         <v>2025-05-01</v>
@@ -7608,7 +7608,7 @@
         <v>2026-05-31</v>
       </c>
       <c r="J225" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="226">
@@ -7631,7 +7631,7 @@
         <v>1996</v>
       </c>
       <c r="G226">
-        <v>1140</v>
+        <v>1144.5</v>
       </c>
       <c r="H226" t="str">
         <v>2025-03-01</v>
@@ -7640,7 +7640,7 @@
         <v>2026-03-31</v>
       </c>
       <c r="J226" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="227">
@@ -7663,7 +7663,7 @@
         <v>1998</v>
       </c>
       <c r="G227">
-        <v>1170</v>
+        <v>1175.25</v>
       </c>
       <c r="H227" t="str">
         <v>2025-04-01</v>
@@ -7672,7 +7672,7 @@
         <v>2026-04-31</v>
       </c>
       <c r="J227" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="228">
@@ -7695,7 +7695,7 @@
         <v>2002</v>
       </c>
       <c r="G228">
-        <v>1230</v>
+        <v>1236.75</v>
       </c>
       <c r="H228" t="str">
         <v>2025-06-01</v>
@@ -7704,7 +7704,7 @@
         <v>2026-06-31</v>
       </c>
       <c r="J228" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="229">
@@ -7727,7 +7727,7 @@
         <v>1996</v>
       </c>
       <c r="G229">
-        <v>1140</v>
+        <v>1144.5</v>
       </c>
       <c r="H229" t="str">
         <v>2025-03-01</v>
@@ -7736,7 +7736,7 @@
         <v>2026-03-31</v>
       </c>
       <c r="J229" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="230">
@@ -7759,7 +7759,7 @@
         <v>1998</v>
       </c>
       <c r="G230">
-        <v>1170</v>
+        <v>1175.25</v>
       </c>
       <c r="H230" t="str">
         <v>2025-04-01</v>
@@ -7768,7 +7768,7 @@
         <v>2026-04-31</v>
       </c>
       <c r="J230" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="231">
@@ -7791,7 +7791,7 @@
         <v>2000</v>
       </c>
       <c r="G231">
-        <v>1200</v>
+        <v>1206</v>
       </c>
       <c r="H231" t="str">
         <v>2025-05-01</v>
@@ -7800,7 +7800,7 @@
         <v>2026-05-31</v>
       </c>
       <c r="J231" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="232">
@@ -7823,7 +7823,7 @@
         <v>2002</v>
       </c>
       <c r="G232">
-        <v>1230</v>
+        <v>1236.75</v>
       </c>
       <c r="H232" t="str">
         <v>2025-06-01</v>
@@ -7832,7 +7832,7 @@
         <v>2026-06-31</v>
       </c>
       <c r="J232" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="233">
@@ -7855,7 +7855,7 @@
         <v>2004</v>
       </c>
       <c r="G233">
-        <v>1260</v>
+        <v>1267.5</v>
       </c>
       <c r="H233" t="str">
         <v>2025-07-01</v>
@@ -7864,7 +7864,7 @@
         <v>2026-07-31</v>
       </c>
       <c r="J233" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="234">
@@ -7887,7 +7887,7 @@
         <v>1997</v>
       </c>
       <c r="G234">
-        <v>1160</v>
+        <v>1164.75</v>
       </c>
       <c r="H234" t="str">
         <v>2025-04-01</v>
@@ -7896,7 +7896,7 @@
         <v>2026-04-31</v>
       </c>
       <c r="J234" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="235">
@@ -7919,7 +7919,7 @@
         <v>1999</v>
       </c>
       <c r="G235">
-        <v>1190</v>
+        <v>1195.5</v>
       </c>
       <c r="H235" t="str">
         <v>2025-05-01</v>
@@ -7928,7 +7928,7 @@
         <v>2026-05-31</v>
       </c>
       <c r="J235" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="236">
@@ -7951,7 +7951,7 @@
         <v>2003</v>
       </c>
       <c r="G236">
-        <v>1250</v>
+        <v>1257</v>
       </c>
       <c r="H236" t="str">
         <v>2025-07-01</v>
@@ -7960,7 +7960,7 @@
         <v>2026-07-31</v>
       </c>
       <c r="J236" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="237">
@@ -7983,7 +7983,7 @@
         <v>1993</v>
       </c>
       <c r="G237">
-        <v>1280</v>
+        <v>1287.75</v>
       </c>
       <c r="H237" t="str">
         <v>2025-08-01</v>
@@ -7992,7 +7992,7 @@
         <v>2026-08-31</v>
       </c>
       <c r="J237" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="238">
@@ -8015,7 +8015,7 @@
         <v>1997</v>
       </c>
       <c r="G238">
-        <v>1160</v>
+        <v>1164.75</v>
       </c>
       <c r="H238" t="str">
         <v>2025-04-01</v>
@@ -8024,7 +8024,7 @@
         <v>2026-04-31</v>
       </c>
       <c r="J238" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="239">
@@ -8047,7 +8047,7 @@
         <v>1999</v>
       </c>
       <c r="G239">
-        <v>1190</v>
+        <v>1195.5</v>
       </c>
       <c r="H239" t="str">
         <v>2025-05-01</v>
@@ -8056,7 +8056,7 @@
         <v>2026-05-31</v>
       </c>
       <c r="J239" t="str">
-        <v>Occupied</v>
+        <v>Notice</v>
       </c>
     </row>
     <row r="240">
@@ -8079,7 +8079,7 @@
         <v>2001</v>
       </c>
       <c r="G240">
-        <v>1220</v>
+        <v>1226.25</v>
       </c>
       <c r="H240" t="str">
         <v>2025-06-01</v>
@@ -8088,7 +8088,7 @@
         <v>2026-06-31</v>
       </c>
       <c r="J240" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="241">
@@ -8111,7 +8111,7 @@
         <v>2003</v>
       </c>
       <c r="G241">
-        <v>1250</v>
+        <v>1257</v>
       </c>
       <c r="H241" t="str">
         <v>2025-07-01</v>
@@ -8120,7 +8120,7 @@
         <v>2026-07-31</v>
       </c>
       <c r="J241" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="242">
@@ -8143,7 +8143,7 @@
         <v>1997</v>
       </c>
       <c r="G242">
-        <v>1160</v>
+        <v>1164.75</v>
       </c>
       <c r="H242" t="str">
         <v>2025-04-01</v>
@@ -8152,7 +8152,7 @@
         <v>2026-04-31</v>
       </c>
       <c r="J242" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="243">
@@ -8175,7 +8175,7 @@
         <v>1999</v>
       </c>
       <c r="G243">
-        <v>1190</v>
+        <v>1195.5</v>
       </c>
       <c r="H243" t="str">
         <v>2025-05-01</v>
@@ -8184,7 +8184,7 @@
         <v>2026-05-31</v>
       </c>
       <c r="J243" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="244">
@@ -8207,7 +8207,7 @@
         <v>2001</v>
       </c>
       <c r="G244">
-        <v>1220</v>
+        <v>1226.25</v>
       </c>
       <c r="H244" t="str">
         <v>2025-06-01</v>
@@ -8216,7 +8216,7 @@
         <v>2026-06-31</v>
       </c>
       <c r="J244" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="245">
@@ -8239,7 +8239,7 @@
         <v>1997</v>
       </c>
       <c r="G245">
-        <v>1160</v>
+        <v>1164.75</v>
       </c>
       <c r="H245" t="str">
         <v>2025-04-01</v>
@@ -8248,7 +8248,7 @@
         <v>2026-04-31</v>
       </c>
       <c r="J245" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="246">
@@ -8271,7 +8271,7 @@
         <v>1999</v>
       </c>
       <c r="G246">
-        <v>1190</v>
+        <v>1195.5</v>
       </c>
       <c r="H246" t="str">
         <v>2025-05-01</v>
@@ -8280,7 +8280,7 @@
         <v>2026-05-31</v>
       </c>
       <c r="J246" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="247">
@@ -8303,7 +8303,7 @@
         <v>1997</v>
       </c>
       <c r="G247">
-        <v>1160</v>
+        <v>1164.75</v>
       </c>
       <c r="H247" t="str">
         <v>2025-04-01</v>
@@ -8312,7 +8312,7 @@
         <v>2026-04-31</v>
       </c>
       <c r="J247" t="str">
-        <v>Secured</v>
+        <v>Future</v>
       </c>
     </row>
     <row r="248">
@@ -8335,7 +8335,7 @@
         <v>1999</v>
       </c>
       <c r="G248">
-        <v>1190</v>
+        <v>1195.5</v>
       </c>
       <c r="H248" t="str">
         <v>2025-05-01</v>
@@ -8344,7 +8344,7 @@
         <v>2026-05-31</v>
       </c>
       <c r="J248" t="str">
-        <v>Secured</v>
+        <v>Future</v>
       </c>
     </row>
     <row r="249">
@@ -8367,7 +8367,7 @@
         <v>2001</v>
       </c>
       <c r="G249">
-        <v>1220</v>
+        <v>1226.25</v>
       </c>
       <c r="H249" t="str">
         <v>2025-06-01</v>
@@ -8376,7 +8376,7 @@
         <v>2026-06-31</v>
       </c>
       <c r="J249" t="str">
-        <v>Secured</v>
+        <v>Future</v>
       </c>
     </row>
     <row r="250">
@@ -8399,7 +8399,7 @@
         <v>2003</v>
       </c>
       <c r="G250">
-        <v>1250</v>
+        <v>1257</v>
       </c>
       <c r="H250" t="str">
         <v>2025-07-01</v>
@@ -8408,7 +8408,7 @@
         <v>2026-07-31</v>
       </c>
       <c r="J250" t="str">
-        <v>Secured</v>
+        <v>Future</v>
       </c>
     </row>
     <row r="251">
@@ -8431,7 +8431,7 @@
         <v>1997</v>
       </c>
       <c r="G251">
-        <v>1160</v>
+        <v>1164.75</v>
       </c>
       <c r="H251" t="str">
         <v>2025-04-01</v>
@@ -8440,7 +8440,7 @@
         <v>2026-04-31</v>
       </c>
       <c r="J251" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="252">
@@ -8463,7 +8463,7 @@
         <v>1999</v>
       </c>
       <c r="G252">
-        <v>1190</v>
+        <v>1195.5</v>
       </c>
       <c r="H252" t="str">
         <v>2025-05-01</v>
@@ -8472,7 +8472,7 @@
         <v>2026-05-31</v>
       </c>
       <c r="J252" t="str">
-        <v>Occupied</v>
+        <v>Notice</v>
       </c>
     </row>
     <row r="253">
@@ -8495,7 +8495,7 @@
         <v>2001</v>
       </c>
       <c r="G253">
-        <v>1220</v>
+        <v>1226.25</v>
       </c>
       <c r="H253" t="str">
         <v>2025-06-01</v>
@@ -8504,7 +8504,7 @@
         <v>2026-06-31</v>
       </c>
       <c r="J253" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="254">
@@ -8527,7 +8527,7 @@
         <v>2003</v>
       </c>
       <c r="G254">
-        <v>1250</v>
+        <v>1257</v>
       </c>
       <c r="H254" t="str">
         <v>2025-07-01</v>
@@ -8536,7 +8536,7 @@
         <v>2026-07-31</v>
       </c>
       <c r="J254" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="255">
@@ -8559,7 +8559,7 @@
         <v>1993</v>
       </c>
       <c r="G255">
-        <v>1280</v>
+        <v>1287.75</v>
       </c>
       <c r="H255" t="str">
         <v>2025-08-01</v>
@@ -8568,7 +8568,7 @@
         <v>2026-08-31</v>
       </c>
       <c r="J255" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="256">
@@ -8591,7 +8591,7 @@
         <v>1998</v>
       </c>
       <c r="G256">
-        <v>1180</v>
+        <v>1185</v>
       </c>
       <c r="H256" t="str">
         <v>2025-05-01</v>
@@ -8600,7 +8600,7 @@
         <v>2026-05-31</v>
       </c>
       <c r="J256" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="257">
@@ -8623,7 +8623,7 @@
         <v>2000</v>
       </c>
       <c r="G257">
-        <v>1210</v>
+        <v>1215.75</v>
       </c>
       <c r="H257" t="str">
         <v>2025-06-01</v>
@@ -8632,7 +8632,7 @@
         <v>2026-06-31</v>
       </c>
       <c r="J257" t="str">
-        <v>Occupied</v>
+        <v>Notice</v>
       </c>
     </row>
     <row r="258">
@@ -8655,7 +8655,7 @@
         <v>2002</v>
       </c>
       <c r="G258">
-        <v>1240</v>
+        <v>1246.5</v>
       </c>
       <c r="H258" t="str">
         <v>2025-07-01</v>
@@ -8664,7 +8664,7 @@
         <v>2026-07-31</v>
       </c>
       <c r="J258" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="259">
@@ -8687,7 +8687,7 @@
         <v>2004</v>
       </c>
       <c r="G259">
-        <v>1270</v>
+        <v>1277.25</v>
       </c>
       <c r="H259" t="str">
         <v>2025-08-01</v>
@@ -8696,7 +8696,7 @@
         <v>2026-08-31</v>
       </c>
       <c r="J259" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="260">
@@ -8719,7 +8719,7 @@
         <v>1994</v>
       </c>
       <c r="G260">
-        <v>1300</v>
+        <v>1308</v>
       </c>
       <c r="H260" t="str">
         <v>2025-09-01</v>
@@ -8728,7 +8728,7 @@
         <v>2026-09-31</v>
       </c>
       <c r="J260" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="261">
@@ -8751,7 +8751,7 @@
         <v>1998</v>
       </c>
       <c r="G261">
-        <v>1180</v>
+        <v>1185</v>
       </c>
       <c r="H261" t="str">
         <v>2025-05-01</v>
@@ -8760,7 +8760,7 @@
         <v>2026-05-31</v>
       </c>
       <c r="J261" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="262">
@@ -8783,7 +8783,7 @@
         <v>2000</v>
       </c>
       <c r="G262">
-        <v>1210</v>
+        <v>1215.75</v>
       </c>
       <c r="H262" t="str">
         <v>2025-06-01</v>
@@ -8792,7 +8792,7 @@
         <v>2026-06-31</v>
       </c>
       <c r="J262" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="263">
@@ -8815,7 +8815,7 @@
         <v>2002</v>
       </c>
       <c r="G263">
-        <v>1240</v>
+        <v>1246.5</v>
       </c>
       <c r="H263" t="str">
         <v>2025-07-01</v>
@@ -8824,7 +8824,7 @@
         <v>2026-07-31</v>
       </c>
       <c r="J263" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="264">
@@ -8847,7 +8847,7 @@
         <v>2004</v>
       </c>
       <c r="G264">
-        <v>1270</v>
+        <v>1277.25</v>
       </c>
       <c r="H264" t="str">
         <v>2025-08-01</v>
@@ -8856,7 +8856,7 @@
         <v>2026-08-31</v>
       </c>
       <c r="J264" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="265">
@@ -8879,7 +8879,7 @@
         <v>1998</v>
       </c>
       <c r="G265">
-        <v>1180</v>
+        <v>1185</v>
       </c>
       <c r="H265" t="str">
         <v>2025-05-01</v>
@@ -8888,7 +8888,7 @@
         <v>2026-05-31</v>
       </c>
       <c r="J265" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="266">
@@ -8911,7 +8911,7 @@
         <v>2000</v>
       </c>
       <c r="G266">
-        <v>1210</v>
+        <v>1215.75</v>
       </c>
       <c r="H266" t="str">
         <v>2025-06-01</v>
@@ -8920,7 +8920,7 @@
         <v>2026-06-31</v>
       </c>
       <c r="J266" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="267">
@@ -8943,7 +8943,7 @@
         <v>1998</v>
       </c>
       <c r="G267">
-        <v>1180</v>
+        <v>1185</v>
       </c>
       <c r="H267" t="str">
         <v>2025-05-01</v>
@@ -8952,7 +8952,7 @@
         <v>2026-05-31</v>
       </c>
       <c r="J267" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="268">
@@ -8975,7 +8975,7 @@
         <v>2000</v>
       </c>
       <c r="G268">
-        <v>1210</v>
+        <v>1215.75</v>
       </c>
       <c r="H268" t="str">
         <v>2025-06-01</v>
@@ -8984,7 +8984,7 @@
         <v>2026-06-31</v>
       </c>
       <c r="J268" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="269">
@@ -9007,7 +9007,7 @@
         <v>2002</v>
       </c>
       <c r="G269">
-        <v>1240</v>
+        <v>1246.5</v>
       </c>
       <c r="H269" t="str">
         <v>2025-07-01</v>
@@ -9016,7 +9016,7 @@
         <v>2026-07-31</v>
       </c>
       <c r="J269" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="270">
@@ -9039,7 +9039,7 @@
         <v>1998</v>
       </c>
       <c r="G270">
-        <v>1180</v>
+        <v>1185</v>
       </c>
       <c r="H270" t="str">
         <v>2025-05-01</v>
@@ -9048,7 +9048,7 @@
         <v>2026-05-31</v>
       </c>
       <c r="J270" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="271">
@@ -9071,7 +9071,7 @@
         <v>2000</v>
       </c>
       <c r="G271">
-        <v>1210</v>
+        <v>1215.75</v>
       </c>
       <c r="H271" t="str">
         <v>2025-06-01</v>
@@ -9080,7 +9080,7 @@
         <v>2026-06-31</v>
       </c>
       <c r="J271" t="str">
-        <v>Occupied</v>
+        <v>Notice</v>
       </c>
     </row>
     <row r="272">
@@ -9103,7 +9103,7 @@
         <v>2002</v>
       </c>
       <c r="G272">
-        <v>1240</v>
+        <v>1246.5</v>
       </c>
       <c r="H272" t="str">
         <v>2025-07-01</v>
@@ -9112,7 +9112,7 @@
         <v>2026-07-31</v>
       </c>
       <c r="J272" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="273">
@@ -9135,7 +9135,7 @@
         <v>2004</v>
       </c>
       <c r="G273">
-        <v>1270</v>
+        <v>1277.25</v>
       </c>
       <c r="H273" t="str">
         <v>2025-08-01</v>
@@ -9144,7 +9144,7 @@
         <v>2026-08-31</v>
       </c>
       <c r="J273" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="274">
@@ -9167,7 +9167,7 @@
         <v>1998</v>
       </c>
       <c r="G274">
-        <v>1180</v>
+        <v>1185</v>
       </c>
       <c r="H274" t="str">
         <v>2025-05-01</v>
@@ -9176,7 +9176,7 @@
         <v>2026-05-31</v>
       </c>
       <c r="J274" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="275">
@@ -9199,7 +9199,7 @@
         <v>2000</v>
       </c>
       <c r="G275">
-        <v>1210</v>
+        <v>1215.75</v>
       </c>
       <c r="H275" t="str">
         <v>2025-06-01</v>
@@ -9208,7 +9208,7 @@
         <v>2026-06-31</v>
       </c>
       <c r="J275" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="276">
@@ -9231,7 +9231,7 @@
         <v>2004</v>
       </c>
       <c r="G276">
-        <v>1270</v>
+        <v>1277.25</v>
       </c>
       <c r="H276" t="str">
         <v>2025-08-01</v>
@@ -9240,7 +9240,7 @@
         <v>2026-08-31</v>
       </c>
       <c r="J276" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="277">
@@ -9263,7 +9263,7 @@
         <v>1994</v>
       </c>
       <c r="G277">
-        <v>1300</v>
+        <v>1308</v>
       </c>
       <c r="H277" t="str">
         <v>2025-09-01</v>
@@ -9272,7 +9272,7 @@
         <v>2026-09-31</v>
       </c>
       <c r="J277" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="278">
@@ -9295,7 +9295,7 @@
         <v>1999</v>
       </c>
       <c r="G278">
-        <v>1200</v>
+        <v>1205.25</v>
       </c>
       <c r="H278" t="str">
         <v>2025-06-01</v>
@@ -9304,7 +9304,7 @@
         <v>2026-06-31</v>
       </c>
       <c r="J278" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="279">
@@ -9327,7 +9327,7 @@
         <v>2001</v>
       </c>
       <c r="G279">
-        <v>1230</v>
+        <v>1236</v>
       </c>
       <c r="H279" t="str">
         <v>2025-07-01</v>
@@ -9336,7 +9336,7 @@
         <v>2026-07-31</v>
       </c>
       <c r="J279" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="280">
@@ -9359,7 +9359,7 @@
         <v>2003</v>
       </c>
       <c r="G280">
-        <v>1260</v>
+        <v>1266.75</v>
       </c>
       <c r="H280" t="str">
         <v>2025-08-01</v>
@@ -9368,7 +9368,7 @@
         <v>2026-08-31</v>
       </c>
       <c r="J280" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="281">
@@ -9391,7 +9391,7 @@
         <v>1993</v>
       </c>
       <c r="G281">
-        <v>1290</v>
+        <v>1297.5</v>
       </c>
       <c r="H281" t="str">
         <v>2025-09-01</v>
@@ -9400,7 +9400,7 @@
         <v>2026-09-31</v>
       </c>
       <c r="J281" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="282">
@@ -9423,7 +9423,7 @@
         <v>1995</v>
       </c>
       <c r="G282">
-        <v>1320</v>
+        <v>1328.25</v>
       </c>
       <c r="H282" t="str">
         <v>2025-10-01</v>
@@ -9432,7 +9432,7 @@
         <v>2026-10-31</v>
       </c>
       <c r="J282" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="283">
@@ -9455,7 +9455,7 @@
         <v>1999</v>
       </c>
       <c r="G283">
-        <v>1200</v>
+        <v>1205.25</v>
       </c>
       <c r="H283" t="str">
         <v>2025-06-01</v>
@@ -9464,7 +9464,7 @@
         <v>2026-06-31</v>
       </c>
       <c r="J283" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="284">
@@ -9487,7 +9487,7 @@
         <v>2001</v>
       </c>
       <c r="G284">
-        <v>1230</v>
+        <v>1236</v>
       </c>
       <c r="H284" t="str">
         <v>2025-07-01</v>
@@ -9496,7 +9496,7 @@
         <v>2026-07-31</v>
       </c>
       <c r="J284" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="285">
@@ -9519,7 +9519,7 @@
         <v>1993</v>
       </c>
       <c r="G285">
-        <v>1290</v>
+        <v>1297.5</v>
       </c>
       <c r="H285" t="str">
         <v>2025-09-01</v>
@@ -9528,7 +9528,7 @@
         <v>2026-09-31</v>
       </c>
       <c r="J285" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="286">
@@ -9551,7 +9551,7 @@
         <v>1999</v>
       </c>
       <c r="G286">
-        <v>1200</v>
+        <v>1205.25</v>
       </c>
       <c r="H286" t="str">
         <v>2025-06-01</v>
@@ -9560,7 +9560,7 @@
         <v>2026-06-31</v>
       </c>
       <c r="J286" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="287">
@@ -9583,7 +9583,7 @@
         <v>2001</v>
       </c>
       <c r="G287">
-        <v>1230</v>
+        <v>1236</v>
       </c>
       <c r="H287" t="str">
         <v>2025-07-01</v>
@@ -9592,7 +9592,7 @@
         <v>2026-07-31</v>
       </c>
       <c r="J287" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="288">
@@ -9615,7 +9615,7 @@
         <v>2003</v>
       </c>
       <c r="G288">
-        <v>1260</v>
+        <v>1266.75</v>
       </c>
       <c r="H288" t="str">
         <v>2025-08-01</v>
@@ -9624,7 +9624,7 @@
         <v>2026-08-31</v>
       </c>
       <c r="J288" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="289">
@@ -9647,7 +9647,7 @@
         <v>1999</v>
       </c>
       <c r="G289">
-        <v>1200</v>
+        <v>1205.25</v>
       </c>
       <c r="H289" t="str">
         <v>2025-06-01</v>
@@ -9656,7 +9656,7 @@
         <v>2026-06-31</v>
       </c>
       <c r="J289" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="290">
@@ -9679,7 +9679,7 @@
         <v>2001</v>
       </c>
       <c r="G290">
-        <v>1230</v>
+        <v>1236</v>
       </c>
       <c r="H290" t="str">
         <v>2025-07-01</v>
@@ -9688,7 +9688,7 @@
         <v>2026-07-31</v>
       </c>
       <c r="J290" t="str">
-        <v>Occupied</v>
+        <v>Notice</v>
       </c>
     </row>
     <row r="291">
@@ -9711,7 +9711,7 @@
         <v>2003</v>
       </c>
       <c r="G291">
-        <v>1260</v>
+        <v>1266.75</v>
       </c>
       <c r="H291" t="str">
         <v>2025-08-01</v>
@@ -9720,7 +9720,7 @@
         <v>2026-08-31</v>
       </c>
       <c r="J291" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="292">
@@ -9743,7 +9743,7 @@
         <v>1999</v>
       </c>
       <c r="G292">
-        <v>1200</v>
+        <v>1205.25</v>
       </c>
       <c r="H292" t="str">
         <v>2025-06-01</v>
@@ -9752,7 +9752,7 @@
         <v>2026-06-31</v>
       </c>
       <c r="J292" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="293">
@@ -9775,7 +9775,7 @@
         <v>2001</v>
       </c>
       <c r="G293">
-        <v>1230</v>
+        <v>1236</v>
       </c>
       <c r="H293" t="str">
         <v>2025-07-01</v>
@@ -9784,7 +9784,7 @@
         <v>2026-07-31</v>
       </c>
       <c r="J293" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="294">
@@ -9807,7 +9807,7 @@
         <v>1993</v>
       </c>
       <c r="G294">
-        <v>1290</v>
+        <v>1297.5</v>
       </c>
       <c r="H294" t="str">
         <v>2025-09-01</v>
@@ -9816,7 +9816,7 @@
         <v>2026-09-31</v>
       </c>
       <c r="J294" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="295">
@@ -9839,7 +9839,7 @@
         <v>1999</v>
       </c>
       <c r="G295">
-        <v>1200</v>
+        <v>1205.25</v>
       </c>
       <c r="H295" t="str">
         <v>2025-06-01</v>
@@ -9848,7 +9848,7 @@
         <v>2026-06-31</v>
       </c>
       <c r="J295" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="296">
@@ -9871,7 +9871,7 @@
         <v>2001</v>
       </c>
       <c r="G296">
-        <v>1230</v>
+        <v>1236</v>
       </c>
       <c r="H296" t="str">
         <v>2025-07-01</v>
@@ -9880,7 +9880,7 @@
         <v>2026-07-31</v>
       </c>
       <c r="J296" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="297">
@@ -9903,7 +9903,7 @@
         <v>2003</v>
       </c>
       <c r="G297">
-        <v>1260</v>
+        <v>1266.75</v>
       </c>
       <c r="H297" t="str">
         <v>2025-08-01</v>
@@ -9912,7 +9912,7 @@
         <v>2026-08-31</v>
       </c>
       <c r="J297" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="298">
@@ -9935,7 +9935,7 @@
         <v>1993</v>
       </c>
       <c r="G298">
-        <v>1290</v>
+        <v>1297.5</v>
       </c>
       <c r="H298" t="str">
         <v>2025-09-01</v>
@@ -9944,7 +9944,7 @@
         <v>2026-09-31</v>
       </c>
       <c r="J298" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="299">
@@ -9967,7 +9967,7 @@
         <v>1995</v>
       </c>
       <c r="G299">
-        <v>1320</v>
+        <v>1328.25</v>
       </c>
       <c r="H299" t="str">
         <v>2025-10-01</v>
@@ -9976,7 +9976,7 @@
         <v>2026-10-31</v>
       </c>
       <c r="J299" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="300">
@@ -9999,7 +9999,7 @@
         <v>2000</v>
       </c>
       <c r="G300">
-        <v>1220</v>
+        <v>1225.5</v>
       </c>
       <c r="H300" t="str">
         <v>2025-07-01</v>
@@ -10008,7 +10008,7 @@
         <v>2026-07-31</v>
       </c>
       <c r="J300" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="301">
@@ -10031,7 +10031,7 @@
         <v>2002</v>
       </c>
       <c r="G301">
-        <v>1250</v>
+        <v>1256.25</v>
       </c>
       <c r="H301" t="str">
         <v>2025-08-01</v>
@@ -10040,7 +10040,7 @@
         <v>2026-08-31</v>
       </c>
       <c r="J301" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="302">
@@ -10063,7 +10063,7 @@
         <v>1994</v>
       </c>
       <c r="G302">
-        <v>1310</v>
+        <v>1317.75</v>
       </c>
       <c r="H302" t="str">
         <v>2025-10-01</v>
@@ -10072,7 +10072,7 @@
         <v>2026-10-31</v>
       </c>
       <c r="J302" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="303">
@@ -10095,7 +10095,7 @@
         <v>1996</v>
       </c>
       <c r="G303">
-        <v>1340</v>
+        <v>1348.5</v>
       </c>
       <c r="H303" t="str">
         <v>2025-11-01</v>
@@ -10104,7 +10104,7 @@
         <v>2026-11-31</v>
       </c>
       <c r="J303" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="304">
@@ -10127,7 +10127,7 @@
         <v>2000</v>
       </c>
       <c r="G304">
-        <v>1220</v>
+        <v>1225.5</v>
       </c>
       <c r="H304" t="str">
         <v>2025-07-01</v>
@@ -10136,7 +10136,7 @@
         <v>2026-07-31</v>
       </c>
       <c r="J304" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="305">
@@ -10159,7 +10159,7 @@
         <v>2002</v>
       </c>
       <c r="G305">
-        <v>1250</v>
+        <v>1256.25</v>
       </c>
       <c r="H305" t="str">
         <v>2025-08-01</v>
@@ -10168,7 +10168,7 @@
         <v>2026-08-31</v>
       </c>
       <c r="J305" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="306">
@@ -10191,7 +10191,7 @@
         <v>2004</v>
       </c>
       <c r="G306">
-        <v>1280</v>
+        <v>1287</v>
       </c>
       <c r="H306" t="str">
         <v>2025-09-01</v>
@@ -10200,7 +10200,7 @@
         <v>2026-09-31</v>
       </c>
       <c r="J306" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="307">
@@ -10223,7 +10223,7 @@
         <v>1994</v>
       </c>
       <c r="G307">
-        <v>1310</v>
+        <v>1317.75</v>
       </c>
       <c r="H307" t="str">
         <v>2025-10-01</v>
@@ -10232,7 +10232,7 @@
         <v>2026-10-31</v>
       </c>
       <c r="J307" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="308">
@@ -10255,7 +10255,7 @@
         <v>2000</v>
       </c>
       <c r="G308">
-        <v>1220</v>
+        <v>1225.5</v>
       </c>
       <c r="H308" t="str">
         <v>2025-07-01</v>
@@ -10264,7 +10264,7 @@
         <v>2026-07-31</v>
       </c>
       <c r="J308" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="309">
@@ -10287,7 +10287,7 @@
         <v>2002</v>
       </c>
       <c r="G309">
-        <v>1250</v>
+        <v>1256.25</v>
       </c>
       <c r="H309" t="str">
         <v>2025-08-01</v>
@@ -10296,7 +10296,7 @@
         <v>2026-08-31</v>
       </c>
       <c r="J309" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="310">
@@ -10319,7 +10319,7 @@
         <v>2000</v>
       </c>
       <c r="G310">
-        <v>1220</v>
+        <v>1225.5</v>
       </c>
       <c r="H310" t="str">
         <v>2025-07-01</v>
@@ -10328,7 +10328,7 @@
         <v>2026-07-31</v>
       </c>
       <c r="J310" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="311">
@@ -10351,7 +10351,7 @@
         <v>2002</v>
       </c>
       <c r="G311">
-        <v>1250</v>
+        <v>1256.25</v>
       </c>
       <c r="H311" t="str">
         <v>2025-08-01</v>
@@ -10360,7 +10360,7 @@
         <v>2026-08-31</v>
       </c>
       <c r="J311" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="312">
@@ -10383,7 +10383,7 @@
         <v>2004</v>
       </c>
       <c r="G312">
-        <v>1280</v>
+        <v>1287</v>
       </c>
       <c r="H312" t="str">
         <v>2025-09-01</v>
@@ -10392,7 +10392,7 @@
         <v>2026-09-31</v>
       </c>
       <c r="J312" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="313">
@@ -10415,7 +10415,7 @@
         <v>1994</v>
       </c>
       <c r="G313">
-        <v>1310</v>
+        <v>1317.75</v>
       </c>
       <c r="H313" t="str">
         <v>2025-10-01</v>
@@ -10424,7 +10424,7 @@
         <v>2026-10-31</v>
       </c>
       <c r="J313" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="314">
@@ -10447,7 +10447,7 @@
         <v>2000</v>
       </c>
       <c r="G314">
-        <v>1220</v>
+        <v>1225.5</v>
       </c>
       <c r="H314" t="str">
         <v>2025-07-01</v>
@@ -10456,7 +10456,7 @@
         <v>2026-07-31</v>
       </c>
       <c r="J314" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="315">
@@ -10479,7 +10479,7 @@
         <v>2002</v>
       </c>
       <c r="G315">
-        <v>1250</v>
+        <v>1256.25</v>
       </c>
       <c r="H315" t="str">
         <v>2025-08-01</v>
@@ -10488,7 +10488,7 @@
         <v>2026-08-31</v>
       </c>
       <c r="J315" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="316">
@@ -10511,7 +10511,7 @@
         <v>2004</v>
       </c>
       <c r="G316">
-        <v>1280</v>
+        <v>1287</v>
       </c>
       <c r="H316" t="str">
         <v>2025-09-01</v>
@@ -10520,7 +10520,7 @@
         <v>2026-09-31</v>
       </c>
       <c r="J316" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="317">
@@ -10543,7 +10543,7 @@
         <v>1994</v>
       </c>
       <c r="G317">
-        <v>1310</v>
+        <v>1317.75</v>
       </c>
       <c r="H317" t="str">
         <v>2025-10-01</v>
@@ -10552,7 +10552,7 @@
         <v>2026-10-31</v>
       </c>
       <c r="J317" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="318">
@@ -10575,7 +10575,7 @@
         <v>1996</v>
       </c>
       <c r="G318">
-        <v>1340</v>
+        <v>1348.5</v>
       </c>
       <c r="H318" t="str">
         <v>2025-11-01</v>
@@ -10584,7 +10584,7 @@
         <v>2026-11-31</v>
       </c>
       <c r="J318" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="319">
@@ -10607,7 +10607,7 @@
         <v>2001</v>
       </c>
       <c r="G319">
-        <v>1240</v>
+        <v>1245.75</v>
       </c>
       <c r="H319" t="str">
         <v>2025-08-01</v>
@@ -10616,7 +10616,7 @@
         <v>2026-08-31</v>
       </c>
       <c r="J319" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="320">
@@ -10639,7 +10639,7 @@
         <v>2003</v>
       </c>
       <c r="G320">
-        <v>1270</v>
+        <v>1276.5</v>
       </c>
       <c r="H320" t="str">
         <v>2025-09-01</v>
@@ -10648,7 +10648,7 @@
         <v>2026-09-31</v>
       </c>
       <c r="J320" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="321">
@@ -10671,7 +10671,7 @@
         <v>1993</v>
       </c>
       <c r="G321">
-        <v>1300</v>
+        <v>1307.25</v>
       </c>
       <c r="H321" t="str">
         <v>2025-10-01</v>
@@ -10680,7 +10680,7 @@
         <v>2026-10-31</v>
       </c>
       <c r="J321" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="322">
@@ -10703,7 +10703,7 @@
         <v>1995</v>
       </c>
       <c r="G322">
-        <v>1330</v>
+        <v>1338</v>
       </c>
       <c r="H322" t="str">
         <v>2025-11-01</v>
@@ -10712,7 +10712,7 @@
         <v>2026-11-31</v>
       </c>
       <c r="J322" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="323">
@@ -10735,7 +10735,7 @@
         <v>1997</v>
       </c>
       <c r="G323">
-        <v>1360</v>
+        <v>1368.75</v>
       </c>
       <c r="H323" t="str">
         <v>2025-12-01</v>
@@ -10744,7 +10744,7 @@
         <v>2026-12-31</v>
       </c>
       <c r="J323" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="324">
@@ -10767,7 +10767,7 @@
         <v>2001</v>
       </c>
       <c r="G324">
-        <v>1240</v>
+        <v>1245.75</v>
       </c>
       <c r="H324" t="str">
         <v>2025-08-01</v>
@@ -10776,7 +10776,7 @@
         <v>2026-08-31</v>
       </c>
       <c r="J324" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="325">
@@ -10799,7 +10799,7 @@
         <v>2003</v>
       </c>
       <c r="G325">
-        <v>1270</v>
+        <v>1276.5</v>
       </c>
       <c r="H325" t="str">
         <v>2025-09-01</v>
@@ -10808,7 +10808,7 @@
         <v>2026-09-31</v>
       </c>
       <c r="J325" t="str">
-        <v>Occupied</v>
+        <v>Notice</v>
       </c>
     </row>
     <row r="326">
@@ -10831,7 +10831,7 @@
         <v>1993</v>
       </c>
       <c r="G326">
-        <v>1300</v>
+        <v>1307.25</v>
       </c>
       <c r="H326" t="str">
         <v>2025-10-01</v>
@@ -10840,7 +10840,7 @@
         <v>2026-10-31</v>
       </c>
       <c r="J326" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="327">
@@ -10863,7 +10863,7 @@
         <v>1995</v>
       </c>
       <c r="G327">
-        <v>1330</v>
+        <v>1338</v>
       </c>
       <c r="H327" t="str">
         <v>2025-11-01</v>
@@ -10872,7 +10872,7 @@
         <v>2026-11-31</v>
       </c>
       <c r="J327" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="328">
@@ -10895,7 +10895,7 @@
         <v>2001</v>
       </c>
       <c r="G328">
-        <v>1240</v>
+        <v>1245.75</v>
       </c>
       <c r="H328" t="str">
         <v>2025-08-01</v>
@@ -10904,7 +10904,7 @@
         <v>2026-08-31</v>
       </c>
       <c r="J328" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="329">
@@ -10927,7 +10927,7 @@
         <v>2003</v>
       </c>
       <c r="G329">
-        <v>1270</v>
+        <v>1276.5</v>
       </c>
       <c r="H329" t="str">
         <v>2025-09-01</v>
@@ -10936,7 +10936,7 @@
         <v>2026-09-31</v>
       </c>
       <c r="J329" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="330">
@@ -10959,7 +10959,7 @@
         <v>2001</v>
       </c>
       <c r="G330">
-        <v>1240</v>
+        <v>1245.75</v>
       </c>
       <c r="H330" t="str">
         <v>2025-08-01</v>
@@ -10968,7 +10968,7 @@
         <v>2026-08-31</v>
       </c>
       <c r="J330" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="331">
@@ -10991,7 +10991,7 @@
         <v>2003</v>
       </c>
       <c r="G331">
-        <v>1270</v>
+        <v>1276.5</v>
       </c>
       <c r="H331" t="str">
         <v>2025-09-01</v>
@@ -11000,7 +11000,7 @@
         <v>2026-09-31</v>
       </c>
       <c r="J331" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="332">
@@ -11023,7 +11023,7 @@
         <v>1993</v>
       </c>
       <c r="G332">
-        <v>1300</v>
+        <v>1307.25</v>
       </c>
       <c r="H332" t="str">
         <v>2025-10-01</v>
@@ -11032,7 +11032,7 @@
         <v>2026-10-31</v>
       </c>
       <c r="J332" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="333">
@@ -11055,7 +11055,7 @@
         <v>2001</v>
       </c>
       <c r="G333">
-        <v>1240</v>
+        <v>1245.75</v>
       </c>
       <c r="H333" t="str">
         <v>2025-08-01</v>
@@ -11064,7 +11064,7 @@
         <v>2026-08-31</v>
       </c>
       <c r="J333" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="334">
@@ -11087,7 +11087,7 @@
         <v>2003</v>
       </c>
       <c r="G334">
-        <v>1270</v>
+        <v>1276.5</v>
       </c>
       <c r="H334" t="str">
         <v>2025-09-01</v>
@@ -11096,7 +11096,7 @@
         <v>2026-09-31</v>
       </c>
       <c r="J334" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="335">
@@ -11119,7 +11119,7 @@
         <v>1993</v>
       </c>
       <c r="G335">
-        <v>1300</v>
+        <v>1307.25</v>
       </c>
       <c r="H335" t="str">
         <v>2025-10-01</v>
@@ -11128,7 +11128,7 @@
         <v>2026-10-31</v>
       </c>
       <c r="J335" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="336">
@@ -11151,7 +11151,7 @@
         <v>1995</v>
       </c>
       <c r="G336">
-        <v>1330</v>
+        <v>1338</v>
       </c>
       <c r="H336" t="str">
         <v>2025-11-01</v>
@@ -11160,7 +11160,7 @@
         <v>2026-11-31</v>
       </c>
       <c r="J336" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="337">
@@ -11183,7 +11183,7 @@
         <v>2001</v>
       </c>
       <c r="G337">
-        <v>1240</v>
+        <v>1245.75</v>
       </c>
       <c r="H337" t="str">
         <v>2025-08-01</v>
@@ -11192,7 +11192,7 @@
         <v>2026-08-31</v>
       </c>
       <c r="J337" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="338">
@@ -11215,7 +11215,7 @@
         <v>2003</v>
       </c>
       <c r="G338">
-        <v>1270</v>
+        <v>1276.5</v>
       </c>
       <c r="H338" t="str">
         <v>2025-09-01</v>
@@ -11224,7 +11224,7 @@
         <v>2026-09-31</v>
       </c>
       <c r="J338" t="str">
-        <v>Occupied</v>
+        <v>Notice</v>
       </c>
     </row>
     <row r="339">
@@ -11247,7 +11247,7 @@
         <v>1995</v>
       </c>
       <c r="G339">
-        <v>1330</v>
+        <v>1338</v>
       </c>
       <c r="H339" t="str">
         <v>2025-11-01</v>
@@ -11256,7 +11256,7 @@
         <v>2026-11-31</v>
       </c>
       <c r="J339" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="340">
@@ -11279,7 +11279,7 @@
         <v>1997</v>
       </c>
       <c r="G340">
-        <v>1360</v>
+        <v>1368.75</v>
       </c>
       <c r="H340" t="str">
         <v>2025-12-01</v>
@@ -11288,7 +11288,7 @@
         <v>2026-12-31</v>
       </c>
       <c r="J340" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="341">
@@ -11311,7 +11311,7 @@
         <v>2002</v>
       </c>
       <c r="G341">
-        <v>1260</v>
+        <v>1266</v>
       </c>
       <c r="H341" t="str">
         <v>2025-09-01</v>
@@ -11320,7 +11320,7 @@
         <v>2026-09-31</v>
       </c>
       <c r="J341" t="str">
-        <v>Secured</v>
+        <v>Future</v>
       </c>
     </row>
     <row r="342">
@@ -11343,7 +11343,7 @@
         <v>2004</v>
       </c>
       <c r="G342">
-        <v>1290</v>
+        <v>1296.75</v>
       </c>
       <c r="H342" t="str">
         <v>2025-10-01</v>
@@ -11352,7 +11352,7 @@
         <v>2026-10-31</v>
       </c>
       <c r="J342" t="str">
-        <v>Secured</v>
+        <v>Future</v>
       </c>
     </row>
     <row r="343">
@@ -11375,7 +11375,7 @@
         <v>1994</v>
       </c>
       <c r="G343">
-        <v>1320</v>
+        <v>1327.5</v>
       </c>
       <c r="H343" t="str">
         <v>2025-11-01</v>
@@ -11384,7 +11384,7 @@
         <v>2026-11-31</v>
       </c>
       <c r="J343" t="str">
-        <v>Secured</v>
+        <v>Future</v>
       </c>
     </row>
     <row r="344">
@@ -11407,7 +11407,7 @@
         <v>1996</v>
       </c>
       <c r="G344">
-        <v>1350</v>
+        <v>1358.25</v>
       </c>
       <c r="H344" t="str">
         <v>2025-12-01</v>
@@ -11416,7 +11416,7 @@
         <v>2026-12-31</v>
       </c>
       <c r="J344" t="str">
-        <v>Secured</v>
+        <v>Future</v>
       </c>
     </row>
     <row r="345">
@@ -11439,7 +11439,7 @@
         <v>1998</v>
       </c>
       <c r="G345">
-        <v>1380</v>
+        <v>1389</v>
       </c>
       <c r="H345" t="str">
         <v>2025-01-01</v>
@@ -11448,7 +11448,7 @@
         <v>2026-01-31</v>
       </c>
       <c r="J345" t="str">
-        <v>Secured</v>
+        <v>Future</v>
       </c>
     </row>
     <row r="346">
@@ -11471,7 +11471,7 @@
         <v>2002</v>
       </c>
       <c r="G346">
-        <v>1260</v>
+        <v>1266</v>
       </c>
       <c r="H346" t="str">
         <v>2025-09-01</v>
@@ -11480,7 +11480,7 @@
         <v>2026-09-31</v>
       </c>
       <c r="J346" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="347">
@@ -11503,7 +11503,7 @@
         <v>2004</v>
       </c>
       <c r="G347">
-        <v>1290</v>
+        <v>1296.75</v>
       </c>
       <c r="H347" t="str">
         <v>2025-10-01</v>
@@ -11512,7 +11512,7 @@
         <v>2026-10-31</v>
       </c>
       <c r="J347" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="348">
@@ -11535,7 +11535,7 @@
         <v>1996</v>
       </c>
       <c r="G348">
-        <v>1350</v>
+        <v>1358.25</v>
       </c>
       <c r="H348" t="str">
         <v>2025-12-01</v>
@@ -11544,7 +11544,7 @@
         <v>2026-12-31</v>
       </c>
       <c r="J348" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="349">
@@ -11567,7 +11567,7 @@
         <v>2002</v>
       </c>
       <c r="G349">
-        <v>1260</v>
+        <v>1266</v>
       </c>
       <c r="H349" t="str">
         <v>2025-09-01</v>
@@ -11576,7 +11576,7 @@
         <v>2026-09-31</v>
       </c>
       <c r="J349" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="350">
@@ -11599,7 +11599,7 @@
         <v>2004</v>
       </c>
       <c r="G350">
-        <v>1290</v>
+        <v>1296.75</v>
       </c>
       <c r="H350" t="str">
         <v>2025-10-01</v>
@@ -11608,7 +11608,7 @@
         <v>2026-10-31</v>
       </c>
       <c r="J350" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="351">
@@ -11631,7 +11631,7 @@
         <v>1994</v>
       </c>
       <c r="G351">
-        <v>1320</v>
+        <v>1327.5</v>
       </c>
       <c r="H351" t="str">
         <v>2025-11-01</v>
@@ -11640,7 +11640,7 @@
         <v>2026-11-31</v>
       </c>
       <c r="J351" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="352">
@@ -11663,7 +11663,7 @@
         <v>2002</v>
       </c>
       <c r="G352">
-        <v>1260</v>
+        <v>1266</v>
       </c>
       <c r="H352" t="str">
         <v>2025-09-01</v>
@@ -11672,7 +11672,7 @@
         <v>2026-09-31</v>
       </c>
       <c r="J352" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="353">
@@ -11695,7 +11695,7 @@
         <v>2004</v>
       </c>
       <c r="G353">
-        <v>1290</v>
+        <v>1296.75</v>
       </c>
       <c r="H353" t="str">
         <v>2025-10-01</v>
@@ -11704,7 +11704,7 @@
         <v>2026-10-31</v>
       </c>
       <c r="J353" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="354">
@@ -11727,7 +11727,7 @@
         <v>1994</v>
       </c>
       <c r="G354">
-        <v>1320</v>
+        <v>1327.5</v>
       </c>
       <c r="H354" t="str">
         <v>2025-11-01</v>
@@ -11736,7 +11736,7 @@
         <v>2026-11-31</v>
       </c>
       <c r="J354" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="355">
@@ -11759,7 +11759,7 @@
         <v>2002</v>
       </c>
       <c r="G355">
-        <v>1260</v>
+        <v>1266</v>
       </c>
       <c r="H355" t="str">
         <v>2025-09-01</v>
@@ -11768,7 +11768,7 @@
         <v>2026-09-31</v>
       </c>
       <c r="J355" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="356">
@@ -11791,7 +11791,7 @@
         <v>2004</v>
       </c>
       <c r="G356">
-        <v>1290</v>
+        <v>1296.75</v>
       </c>
       <c r="H356" t="str">
         <v>2025-10-01</v>
@@ -11800,7 +11800,7 @@
         <v>2026-10-31</v>
       </c>
       <c r="J356" t="str">
-        <v>Occupied</v>
+        <v>Notice</v>
       </c>
     </row>
     <row r="357">
@@ -11823,7 +11823,7 @@
         <v>1996</v>
       </c>
       <c r="G357">
-        <v>1350</v>
+        <v>1358.25</v>
       </c>
       <c r="H357" t="str">
         <v>2025-12-01</v>
@@ -11832,7 +11832,7 @@
         <v>2026-12-31</v>
       </c>
       <c r="J357" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="358">
@@ -11855,7 +11855,7 @@
         <v>2002</v>
       </c>
       <c r="G358">
-        <v>1260</v>
+        <v>1266</v>
       </c>
       <c r="H358" t="str">
         <v>2025-09-01</v>
@@ -11864,7 +11864,7 @@
         <v>2026-09-31</v>
       </c>
       <c r="J358" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="359">
@@ -11887,7 +11887,7 @@
         <v>2004</v>
       </c>
       <c r="G359">
-        <v>1290</v>
+        <v>1296.75</v>
       </c>
       <c r="H359" t="str">
         <v>2025-10-01</v>
@@ -11896,7 +11896,7 @@
         <v>2026-10-31</v>
       </c>
       <c r="J359" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="360">
@@ -11919,7 +11919,7 @@
         <v>1994</v>
       </c>
       <c r="G360">
-        <v>1320</v>
+        <v>1327.5</v>
       </c>
       <c r="H360" t="str">
         <v>2025-11-01</v>
@@ -11928,7 +11928,7 @@
         <v>2026-11-31</v>
       </c>
       <c r="J360" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="361">
@@ -11951,7 +11951,7 @@
         <v>1996</v>
       </c>
       <c r="G361">
-        <v>1350</v>
+        <v>1358.25</v>
       </c>
       <c r="H361" t="str">
         <v>2025-12-01</v>
@@ -11960,7 +11960,7 @@
         <v>2026-12-31</v>
       </c>
       <c r="J361" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="362">
@@ -11983,7 +11983,7 @@
         <v>1998</v>
       </c>
       <c r="G362">
-        <v>1380</v>
+        <v>1389</v>
       </c>
       <c r="H362" t="str">
         <v>2025-01-01</v>
@@ -11992,7 +11992,7 @@
         <v>2026-01-31</v>
       </c>
       <c r="J362" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="363">
@@ -12015,7 +12015,7 @@
         <v>2003</v>
       </c>
       <c r="G363">
-        <v>1280</v>
+        <v>1286.25</v>
       </c>
       <c r="H363" t="str">
         <v>2025-10-01</v>
@@ -12024,7 +12024,7 @@
         <v>2026-10-31</v>
       </c>
       <c r="J363" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="364">
@@ -12047,7 +12047,7 @@
         <v>1993</v>
       </c>
       <c r="G364">
-        <v>1310</v>
+        <v>1317</v>
       </c>
       <c r="H364" t="str">
         <v>2025-11-01</v>
@@ -12056,7 +12056,7 @@
         <v>2026-11-31</v>
       </c>
       <c r="J364" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="365">
@@ -12079,7 +12079,7 @@
         <v>1997</v>
       </c>
       <c r="G365">
-        <v>1370</v>
+        <v>1378.5</v>
       </c>
       <c r="H365" t="str">
         <v>2025-01-01</v>
@@ -12088,7 +12088,7 @@
         <v>2026-01-31</v>
       </c>
       <c r="J365" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="366">
@@ -12111,7 +12111,7 @@
         <v>1999</v>
       </c>
       <c r="G366">
-        <v>1400</v>
+        <v>1409.25</v>
       </c>
       <c r="H366" t="str">
         <v>2025-02-01</v>
@@ -12120,7 +12120,7 @@
         <v>2026-02-31</v>
       </c>
       <c r="J366" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="367">
@@ -12143,7 +12143,7 @@
         <v>2003</v>
       </c>
       <c r="G367">
-        <v>1280</v>
+        <v>1286.25</v>
       </c>
       <c r="H367" t="str">
         <v>2025-10-01</v>
@@ -12152,7 +12152,7 @@
         <v>2026-10-31</v>
       </c>
       <c r="J367" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="368">
@@ -12175,7 +12175,7 @@
         <v>1993</v>
       </c>
       <c r="G368">
-        <v>1310</v>
+        <v>1317</v>
       </c>
       <c r="H368" t="str">
         <v>2025-11-01</v>
@@ -12184,7 +12184,7 @@
         <v>2026-11-31</v>
       </c>
       <c r="J368" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="369">
@@ -12207,7 +12207,7 @@
         <v>1995</v>
       </c>
       <c r="G369">
-        <v>1340</v>
+        <v>1347.75</v>
       </c>
       <c r="H369" t="str">
         <v>2025-12-01</v>
@@ -12216,7 +12216,7 @@
         <v>2026-12-31</v>
       </c>
       <c r="J369" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="370">
@@ -12239,7 +12239,7 @@
         <v>1997</v>
       </c>
       <c r="G370">
-        <v>1370</v>
+        <v>1378.5</v>
       </c>
       <c r="H370" t="str">
         <v>2025-01-01</v>
@@ -12248,7 +12248,7 @@
         <v>2026-01-31</v>
       </c>
       <c r="J370" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="371">
@@ -12271,7 +12271,7 @@
         <v>2003</v>
       </c>
       <c r="G371">
-        <v>1280</v>
+        <v>1286.25</v>
       </c>
       <c r="H371" t="str">
         <v>2025-10-01</v>
@@ -12280,7 +12280,7 @@
         <v>2026-10-31</v>
       </c>
       <c r="J371" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="372">
@@ -12303,7 +12303,7 @@
         <v>1993</v>
       </c>
       <c r="G372">
-        <v>1310</v>
+        <v>1317</v>
       </c>
       <c r="H372" t="str">
         <v>2025-11-01</v>
@@ -12312,7 +12312,7 @@
         <v>2026-11-31</v>
       </c>
       <c r="J372" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="373">
@@ -12335,7 +12335,7 @@
         <v>1995</v>
       </c>
       <c r="G373">
-        <v>1340</v>
+        <v>1347.75</v>
       </c>
       <c r="H373" t="str">
         <v>2025-12-01</v>
@@ -12344,7 +12344,7 @@
         <v>2026-12-31</v>
       </c>
       <c r="J373" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="374">
@@ -12367,7 +12367,7 @@
         <v>2003</v>
       </c>
       <c r="G374">
-        <v>1280</v>
+        <v>1286.25</v>
       </c>
       <c r="H374" t="str">
         <v>2025-10-01</v>
@@ -12376,7 +12376,7 @@
         <v>2026-10-31</v>
       </c>
       <c r="J374" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="375">
@@ -12399,7 +12399,7 @@
         <v>1993</v>
       </c>
       <c r="G375">
-        <v>1310</v>
+        <v>1317</v>
       </c>
       <c r="H375" t="str">
         <v>2025-11-01</v>
@@ -12408,7 +12408,7 @@
         <v>2026-11-31</v>
       </c>
       <c r="J375" t="str">
-        <v>Occupied</v>
+        <v>Notice</v>
       </c>
     </row>
     <row r="376">
@@ -12431,7 +12431,7 @@
         <v>2003</v>
       </c>
       <c r="G376">
-        <v>1280</v>
+        <v>1286.25</v>
       </c>
       <c r="H376" t="str">
         <v>2025-10-01</v>
@@ -12440,7 +12440,7 @@
         <v>2026-10-31</v>
       </c>
       <c r="J376" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="377">
@@ -12463,7 +12463,7 @@
         <v>1993</v>
       </c>
       <c r="G377">
-        <v>1310</v>
+        <v>1317</v>
       </c>
       <c r="H377" t="str">
         <v>2025-11-01</v>
@@ -12472,7 +12472,7 @@
         <v>2026-11-31</v>
       </c>
       <c r="J377" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="378">
@@ -12495,7 +12495,7 @@
         <v>1995</v>
       </c>
       <c r="G378">
-        <v>1340</v>
+        <v>1347.75</v>
       </c>
       <c r="H378" t="str">
         <v>2025-12-01</v>
@@ -12504,7 +12504,7 @@
         <v>2026-12-31</v>
       </c>
       <c r="J378" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="379">
@@ -12527,7 +12527,7 @@
         <v>1997</v>
       </c>
       <c r="G379">
-        <v>1370</v>
+        <v>1378.5</v>
       </c>
       <c r="H379" t="str">
         <v>2025-01-01</v>
@@ -12536,7 +12536,7 @@
         <v>2026-01-31</v>
       </c>
       <c r="J379" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="380">
@@ -12559,7 +12559,7 @@
         <v>2004</v>
       </c>
       <c r="G380">
-        <v>1300</v>
+        <v>1306.5</v>
       </c>
       <c r="H380" t="str">
         <v>2025-11-01</v>
@@ -12568,7 +12568,7 @@
         <v>2026-11-31</v>
       </c>
       <c r="J380" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="381">
@@ -12591,7 +12591,7 @@
         <v>1994</v>
       </c>
       <c r="G381">
-        <v>1330</v>
+        <v>1337.25</v>
       </c>
       <c r="H381" t="str">
         <v>2025-12-01</v>
@@ -12600,7 +12600,7 @@
         <v>2026-12-31</v>
       </c>
       <c r="J381" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="382">
@@ -12623,7 +12623,7 @@
         <v>1996</v>
       </c>
       <c r="G382">
-        <v>1360</v>
+        <v>1368</v>
       </c>
       <c r="H382" t="str">
         <v>2025-01-01</v>
@@ -12632,7 +12632,7 @@
         <v>2026-01-31</v>
       </c>
       <c r="J382" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="383">
@@ -12655,7 +12655,7 @@
         <v>1998</v>
       </c>
       <c r="G383">
-        <v>1390</v>
+        <v>1398.75</v>
       </c>
       <c r="H383" t="str">
         <v>2025-02-01</v>
@@ -12664,7 +12664,7 @@
         <v>2026-02-31</v>
       </c>
       <c r="J383" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="384">
@@ -12687,7 +12687,7 @@
         <v>2000</v>
       </c>
       <c r="G384">
-        <v>1420</v>
+        <v>1429.5</v>
       </c>
       <c r="H384" t="str">
         <v>2025-03-01</v>
@@ -12696,7 +12696,7 @@
         <v>2026-03-31</v>
       </c>
       <c r="J384" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="385">
@@ -12719,7 +12719,7 @@
         <v>2004</v>
       </c>
       <c r="G385">
-        <v>1300</v>
+        <v>1306.5</v>
       </c>
       <c r="H385" t="str">
         <v>2025-11-01</v>
@@ -12728,7 +12728,7 @@
         <v>2026-11-31</v>
       </c>
       <c r="J385" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="386">
@@ -12751,7 +12751,7 @@
         <v>1994</v>
       </c>
       <c r="G386">
-        <v>1330</v>
+        <v>1337.25</v>
       </c>
       <c r="H386" t="str">
         <v>2025-12-01</v>
@@ -12760,7 +12760,7 @@
         <v>2026-12-31</v>
       </c>
       <c r="J386" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="387">
@@ -12783,7 +12783,7 @@
         <v>1996</v>
       </c>
       <c r="G387">
-        <v>1360</v>
+        <v>1368</v>
       </c>
       <c r="H387" t="str">
         <v>2025-01-01</v>
@@ -12792,7 +12792,7 @@
         <v>2026-01-31</v>
       </c>
       <c r="J387" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="388">
@@ -12815,7 +12815,7 @@
         <v>1998</v>
       </c>
       <c r="G388">
-        <v>1390</v>
+        <v>1398.75</v>
       </c>
       <c r="H388" t="str">
         <v>2025-02-01</v>
@@ -12824,7 +12824,7 @@
         <v>2026-02-31</v>
       </c>
       <c r="J388" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="389">
@@ -12847,7 +12847,7 @@
         <v>2004</v>
       </c>
       <c r="G389">
-        <v>1300</v>
+        <v>1306.5</v>
       </c>
       <c r="H389" t="str">
         <v>2025-11-01</v>
@@ -12856,7 +12856,7 @@
         <v>2026-11-31</v>
       </c>
       <c r="J389" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="390">
@@ -12879,7 +12879,7 @@
         <v>1994</v>
       </c>
       <c r="G390">
-        <v>1330</v>
+        <v>1337.25</v>
       </c>
       <c r="H390" t="str">
         <v>2025-12-01</v>
@@ -12888,7 +12888,7 @@
         <v>2026-12-31</v>
       </c>
       <c r="J390" t="str">
-        <v>Occupied</v>
+        <v>Notice</v>
       </c>
     </row>
     <row r="391">
@@ -12911,7 +12911,7 @@
         <v>2004</v>
       </c>
       <c r="G391">
-        <v>1300</v>
+        <v>1306.5</v>
       </c>
       <c r="H391" t="str">
         <v>2025-11-01</v>
@@ -12920,7 +12920,7 @@
         <v>2026-11-31</v>
       </c>
       <c r="J391" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="392">
@@ -12943,7 +12943,7 @@
         <v>1994</v>
       </c>
       <c r="G392">
-        <v>1330</v>
+        <v>1337.25</v>
       </c>
       <c r="H392" t="str">
         <v>2025-12-01</v>
@@ -12952,7 +12952,7 @@
         <v>2026-12-31</v>
       </c>
       <c r="J392" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="393">
@@ -12975,7 +12975,7 @@
         <v>1996</v>
       </c>
       <c r="G393">
-        <v>1360</v>
+        <v>1368</v>
       </c>
       <c r="H393" t="str">
         <v>2025-01-01</v>
@@ -12984,7 +12984,7 @@
         <v>2026-01-31</v>
       </c>
       <c r="J393" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="394">
@@ -13007,7 +13007,7 @@
         <v>2004</v>
       </c>
       <c r="G394">
-        <v>1300</v>
+        <v>1306.5</v>
       </c>
       <c r="H394" t="str">
         <v>2025-11-01</v>
@@ -13016,7 +13016,7 @@
         <v>2026-11-31</v>
       </c>
       <c r="J394" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="395">
@@ -13039,7 +13039,7 @@
         <v>1994</v>
       </c>
       <c r="G395">
-        <v>1330</v>
+        <v>1337.25</v>
       </c>
       <c r="H395" t="str">
         <v>2025-12-01</v>
@@ -13048,7 +13048,7 @@
         <v>2026-12-31</v>
       </c>
       <c r="J395" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="396">
@@ -13071,7 +13071,7 @@
         <v>1996</v>
       </c>
       <c r="G396">
-        <v>1360</v>
+        <v>1368</v>
       </c>
       <c r="H396" t="str">
         <v>2025-01-01</v>
@@ -13080,7 +13080,7 @@
         <v>2026-01-31</v>
       </c>
       <c r="J396" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="397">
@@ -13103,7 +13103,7 @@
         <v>1998</v>
       </c>
       <c r="G397">
-        <v>1390</v>
+        <v>1398.75</v>
       </c>
       <c r="H397" t="str">
         <v>2025-02-01</v>
@@ -13112,7 +13112,7 @@
         <v>2026-02-31</v>
       </c>
       <c r="J397" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="398">
@@ -13135,7 +13135,7 @@
         <v>2004</v>
       </c>
       <c r="G398">
-        <v>1300</v>
+        <v>1306.5</v>
       </c>
       <c r="H398" t="str">
         <v>2025-11-01</v>
@@ -13144,7 +13144,7 @@
         <v>2026-11-31</v>
       </c>
       <c r="J398" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="399">
@@ -13167,7 +13167,7 @@
         <v>1994</v>
       </c>
       <c r="G399">
-        <v>1330</v>
+        <v>1337.25</v>
       </c>
       <c r="H399" t="str">
         <v>2025-12-01</v>
@@ -13176,7 +13176,7 @@
         <v>2026-12-31</v>
       </c>
       <c r="J399" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="400">
@@ -13199,7 +13199,7 @@
         <v>1998</v>
       </c>
       <c r="G400">
-        <v>1390</v>
+        <v>1398.75</v>
       </c>
       <c r="H400" t="str">
         <v>2025-02-01</v>
@@ -13208,7 +13208,7 @@
         <v>2026-02-31</v>
       </c>
       <c r="J400" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
       </c>
     </row>
     <row r="401">
@@ -13231,7 +13231,7 @@
         <v>2000</v>
       </c>
       <c r="G401">
-        <v>1420</v>
+        <v>1429.5</v>
       </c>
       <c r="H401" t="str">
         <v>2025-03-01</v>
@@ -13240,12 +13240,44 @@
         <v>2026-03-31</v>
       </c>
       <c r="J401" t="str">
-        <v>Occupied</v>
+        <v>Current</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="str">
+        <v>0503-1</v>
+      </c>
+      <c r="B402" t="str">
+        <v/>
+      </c>
+      <c r="C402" t="str">
+        <v/>
+      </c>
+      <c r="D402" t="str">
+        <v/>
+      </c>
+      <c r="E402" t="str">
+        <v/>
+      </c>
+      <c r="F402" t="str">
+        <v/>
+      </c>
+      <c r="G402">
+        <v>0</v>
+      </c>
+      <c r="H402" t="str">
+        <v/>
+      </c>
+      <c r="I402" t="str">
+        <v/>
+      </c>
+      <c r="J402" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J401"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J402"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/building_tenants_test_data.xlsx
+++ b/building_tenants_test_data.xlsx
@@ -466,10 +466,10 @@
         <v>942</v>
       </c>
       <c r="H2" t="str">
-        <v>2025-05-01</v>
+        <v>2025</v>
       </c>
       <c r="I2" t="str">
-        <v>2026-05-31</v>
+        <v>2026</v>
       </c>
       <c r="J2" t="str">
         <v>Current</v>
@@ -498,10 +498,10 @@
         <v>972.75</v>
       </c>
       <c r="H3" t="str">
-        <v>2025-06-01</v>
+        <v>2025</v>
       </c>
       <c r="I3" t="str">
-        <v>2026-06-31</v>
+        <v>2026</v>
       </c>
       <c r="J3" t="str">
         <v>Notice</v>
@@ -530,10 +530,10 @@
         <v>1003.5</v>
       </c>
       <c r="H4" t="str">
-        <v>2025-07-01</v>
+        <v>2025</v>
       </c>
       <c r="I4" t="str">
-        <v>2026-07-31</v>
+        <v>2026</v>
       </c>
       <c r="J4" t="str">
         <v>Current</v>
@@ -562,10 +562,10 @@
         <v>1034.25</v>
       </c>
       <c r="H5" t="str">
-        <v>2025-08-01</v>
+        <v>2025</v>
       </c>
       <c r="I5" t="str">
-        <v>2026-08-31</v>
+        <v>2026</v>
       </c>
       <c r="J5" t="str">
         <v>Current</v>
@@ -594,10 +594,10 @@
         <v>942</v>
       </c>
       <c r="H6" t="str">
-        <v>2025-05-01</v>
+        <v>2025</v>
       </c>
       <c r="I6" t="str">
-        <v>2026-05-31</v>
+        <v>2026</v>
       </c>
       <c r="J6" t="str">
         <v>Current</v>
@@ -626,10 +626,10 @@
         <v>972.75</v>
       </c>
       <c r="H7" t="str">
-        <v>2025-06-01</v>
+        <v>2025</v>
       </c>
       <c r="I7" t="str">
-        <v>2026-06-31</v>
+        <v>2026</v>
       </c>
       <c r="J7" t="str">
         <v>Current</v>
@@ -658,10 +658,10 @@
         <v>1003.5</v>
       </c>
       <c r="H8" t="str">
-        <v>2025-07-01</v>
+        <v>2025</v>
       </c>
       <c r="I8" t="str">
-        <v>2026-07-31</v>
+        <v>2026</v>
       </c>
       <c r="J8" t="str">
         <v>Current</v>
@@ -690,10 +690,10 @@
         <v>1034.25</v>
       </c>
       <c r="H9" t="str">
-        <v>2025-08-01</v>
+        <v>2025</v>
       </c>
       <c r="I9" t="str">
-        <v>2026-08-31</v>
+        <v>2026</v>
       </c>
       <c r="J9" t="str">
         <v>Current</v>
@@ -722,10 +722,10 @@
         <v>1065</v>
       </c>
       <c r="H10" t="str">
-        <v>2025-09-01</v>
+        <v>2025</v>
       </c>
       <c r="I10" t="str">
-        <v>2026-09-31</v>
+        <v>2026</v>
       </c>
       <c r="J10" t="str">
         <v>Current</v>
@@ -754,10 +754,10 @@
         <v>942</v>
       </c>
       <c r="H11" t="str">
-        <v>2025-05-01</v>
+        <v>2025</v>
       </c>
       <c r="I11" t="str">
-        <v>2026-05-31</v>
+        <v>2026</v>
       </c>
       <c r="J11" t="str">
         <v>Current</v>
@@ -786,10 +786,10 @@
         <v>972.75</v>
       </c>
       <c r="H12" t="str">
-        <v>2025-06-01</v>
+        <v>2025</v>
       </c>
       <c r="I12" t="str">
-        <v>2026-06-31</v>
+        <v>2026</v>
       </c>
       <c r="J12" t="str">
         <v>Current</v>
@@ -818,10 +818,10 @@
         <v>942</v>
       </c>
       <c r="H13" t="str">
-        <v>2025-05-01</v>
+        <v>2025</v>
       </c>
       <c r="I13" t="str">
-        <v>2026-05-31</v>
+        <v>2026</v>
       </c>
       <c r="J13" t="str">
         <v>Current</v>
@@ -850,10 +850,10 @@
         <v>972.75</v>
       </c>
       <c r="H14" t="str">
-        <v>2025-06-01</v>
+        <v>2025</v>
       </c>
       <c r="I14" t="str">
-        <v>2026-06-31</v>
+        <v>2026</v>
       </c>
       <c r="J14" t="str">
         <v>Notice</v>
@@ -882,10 +882,10 @@
         <v>1003.5</v>
       </c>
       <c r="H15" t="str">
-        <v>2025-07-01</v>
+        <v>2025</v>
       </c>
       <c r="I15" t="str">
-        <v>2026-07-31</v>
+        <v>2026</v>
       </c>
       <c r="J15" t="str">
         <v>Current</v>
@@ -914,10 +914,10 @@
         <v>1034.25</v>
       </c>
       <c r="H16" t="str">
-        <v>2025-08-01</v>
+        <v>2025</v>
       </c>
       <c r="I16" t="str">
-        <v>2026-08-31</v>
+        <v>2026</v>
       </c>
       <c r="J16" t="str">
         <v>Current</v>
@@ -946,10 +946,10 @@
         <v>1065</v>
       </c>
       <c r="H17" t="str">
-        <v>2025-09-01</v>
+        <v>2025</v>
       </c>
       <c r="I17" t="str">
-        <v>2026-09-31</v>
+        <v>2026</v>
       </c>
       <c r="J17" t="str">
         <v>Current</v>
@@ -978,10 +978,10 @@
         <v>942</v>
       </c>
       <c r="H18" t="str">
-        <v>2025-05-01</v>
+        <v>2025</v>
       </c>
       <c r="I18" t="str">
-        <v>2026-05-31</v>
+        <v>2026</v>
       </c>
       <c r="J18" t="str">
         <v>Current</v>
@@ -1010,10 +1010,10 @@
         <v>972.75</v>
       </c>
       <c r="H19" t="str">
-        <v>2025-06-01</v>
+        <v>2025</v>
       </c>
       <c r="I19" t="str">
-        <v>2026-06-31</v>
+        <v>2026</v>
       </c>
       <c r="J19" t="str">
         <v>Current</v>
@@ -1042,10 +1042,10 @@
         <v>1034.25</v>
       </c>
       <c r="H20" t="str">
-        <v>2025-08-01</v>
+        <v>2025</v>
       </c>
       <c r="I20" t="str">
-        <v>2026-08-31</v>
+        <v>2026</v>
       </c>
       <c r="J20" t="str">
         <v>Current</v>
@@ -1074,10 +1074,10 @@
         <v>962.25</v>
       </c>
       <c r="H21" t="str">
-        <v>2025-06-01</v>
+        <v>2025</v>
       </c>
       <c r="I21" t="str">
-        <v>2026-06-31</v>
+        <v>2026</v>
       </c>
       <c r="J21" t="str">
         <v>Current</v>
@@ -1106,10 +1106,10 @@
         <v>993</v>
       </c>
       <c r="H22" t="str">
-        <v>2025-07-01</v>
+        <v>2025</v>
       </c>
       <c r="I22" t="str">
-        <v>2026-07-31</v>
+        <v>2026</v>
       </c>
       <c r="J22" t="str">
         <v>Current</v>
@@ -1138,10 +1138,10 @@
         <v>1023.75</v>
       </c>
       <c r="H23" t="str">
-        <v>2025-08-01</v>
+        <v>2025</v>
       </c>
       <c r="I23" t="str">
-        <v>2026-08-31</v>
+        <v>2026</v>
       </c>
       <c r="J23" t="str">
         <v>Current</v>
@@ -1170,10 +1170,10 @@
         <v>1054.5</v>
       </c>
       <c r="H24" t="str">
-        <v>2025-09-01</v>
+        <v>2025</v>
       </c>
       <c r="I24" t="str">
-        <v>2026-09-31</v>
+        <v>2026</v>
       </c>
       <c r="J24" t="str">
         <v>Current</v>
@@ -1202,10 +1202,10 @@
         <v>962.25</v>
       </c>
       <c r="H25" t="str">
-        <v>2025-06-01</v>
+        <v>2025</v>
       </c>
       <c r="I25" t="str">
-        <v>2026-06-31</v>
+        <v>2026</v>
       </c>
       <c r="J25" t="str">
         <v>Current</v>
@@ -1234,10 +1234,10 @@
         <v>993</v>
       </c>
       <c r="H26" t="str">
-        <v>2025-07-01</v>
+        <v>2025</v>
       </c>
       <c r="I26" t="str">
-        <v>2026-07-31</v>
+        <v>2026</v>
       </c>
       <c r="J26" t="str">
         <v>Current</v>
@@ -1266,10 +1266,10 @@
         <v>1054.5</v>
       </c>
       <c r="H27" t="str">
-        <v>2025-09-01</v>
+        <v>2025</v>
       </c>
       <c r="I27" t="str">
-        <v>2026-09-31</v>
+        <v>2026</v>
       </c>
       <c r="J27" t="str">
         <v>Current</v>
@@ -1298,10 +1298,10 @@
         <v>1085.25</v>
       </c>
       <c r="H28" t="str">
-        <v>2025-10-01</v>
+        <v>2025</v>
       </c>
       <c r="I28" t="str">
-        <v>2026-10-31</v>
+        <v>2026</v>
       </c>
       <c r="J28" t="str">
         <v>Current</v>
@@ -1330,10 +1330,10 @@
         <v>962.25</v>
       </c>
       <c r="H29" t="str">
-        <v>2025-06-01</v>
+        <v>2025</v>
       </c>
       <c r="I29" t="str">
-        <v>2026-06-31</v>
+        <v>2026</v>
       </c>
       <c r="J29" t="str">
         <v>Current</v>
@@ -1362,10 +1362,10 @@
         <v>993</v>
       </c>
       <c r="H30" t="str">
-        <v>2025-07-01</v>
+        <v>2025</v>
       </c>
       <c r="I30" t="str">
-        <v>2026-07-31</v>
+        <v>2026</v>
       </c>
       <c r="J30" t="str">
         <v>Current</v>
@@ -1394,10 +1394,10 @@
         <v>1023.75</v>
       </c>
       <c r="H31" t="str">
-        <v>2025-08-01</v>
+        <v>2025</v>
       </c>
       <c r="I31" t="str">
-        <v>2026-08-31</v>
+        <v>2026</v>
       </c>
       <c r="J31" t="str">
         <v>Current</v>
@@ -1426,10 +1426,10 @@
         <v>962.25</v>
       </c>
       <c r="H32" t="str">
-        <v>2025-06-01</v>
+        <v>2025</v>
       </c>
       <c r="I32" t="str">
-        <v>2026-06-31</v>
+        <v>2026</v>
       </c>
       <c r="J32" t="str">
         <v>Current</v>
@@ -1458,10 +1458,10 @@
         <v>993</v>
       </c>
       <c r="H33" t="str">
-        <v>2025-07-01</v>
+        <v>2025</v>
       </c>
       <c r="I33" t="str">
-        <v>2026-07-31</v>
+        <v>2026</v>
       </c>
       <c r="J33" t="str">
         <v>Notice</v>
@@ -1490,10 +1490,10 @@
         <v>1023.75</v>
       </c>
       <c r="H34" t="str">
-        <v>2025-08-01</v>
+        <v>2025</v>
       </c>
       <c r="I34" t="str">
-        <v>2026-08-31</v>
+        <v>2026</v>
       </c>
       <c r="J34" t="str">
         <v>Current</v>
@@ -1522,10 +1522,10 @@
         <v>962.25</v>
       </c>
       <c r="H35" t="str">
-        <v>2025-06-01</v>
+        <v>2025</v>
       </c>
       <c r="I35" t="str">
-        <v>2026-06-31</v>
+        <v>2026</v>
       </c>
       <c r="J35" t="str">
         <v>Current</v>
@@ -1554,10 +1554,10 @@
         <v>993</v>
       </c>
       <c r="H36" t="str">
-        <v>2025-07-01</v>
+        <v>2025</v>
       </c>
       <c r="I36" t="str">
-        <v>2026-07-31</v>
+        <v>2026</v>
       </c>
       <c r="J36" t="str">
         <v>Current</v>
@@ -1586,10 +1586,10 @@
         <v>1054.5</v>
       </c>
       <c r="H37" t="str">
-        <v>2025-09-01</v>
+        <v>2025</v>
       </c>
       <c r="I37" t="str">
-        <v>2026-09-31</v>
+        <v>2026</v>
       </c>
       <c r="J37" t="str">
         <v>Current</v>
@@ -1618,10 +1618,10 @@
         <v>1085.25</v>
       </c>
       <c r="H38" t="str">
-        <v>2025-10-01</v>
+        <v>2025</v>
       </c>
       <c r="I38" t="str">
-        <v>2026-10-31</v>
+        <v>2026</v>
       </c>
       <c r="J38" t="str">
         <v>Current</v>
@@ -1650,10 +1650,10 @@
         <v>962.25</v>
       </c>
       <c r="H39" t="str">
-        <v>2025-06-01</v>
+        <v>2025</v>
       </c>
       <c r="I39" t="str">
-        <v>2026-06-31</v>
+        <v>2026</v>
       </c>
       <c r="J39" t="str">
         <v>Future</v>
@@ -1682,10 +1682,10 @@
         <v>993</v>
       </c>
       <c r="H40" t="str">
-        <v>2025-07-01</v>
+        <v>2025</v>
       </c>
       <c r="I40" t="str">
-        <v>2026-07-31</v>
+        <v>2026</v>
       </c>
       <c r="J40" t="str">
         <v>Future</v>
@@ -1714,10 +1714,10 @@
         <v>1023.75</v>
       </c>
       <c r="H41" t="str">
-        <v>2025-08-01</v>
+        <v>2025</v>
       </c>
       <c r="I41" t="str">
-        <v>2026-08-31</v>
+        <v>2026</v>
       </c>
       <c r="J41" t="str">
         <v>Future</v>
@@ -1746,10 +1746,10 @@
         <v>1054.5</v>
       </c>
       <c r="H42" t="str">
-        <v>2025-09-01</v>
+        <v>2025</v>
       </c>
       <c r="I42" t="str">
-        <v>2026-09-31</v>
+        <v>2026</v>
       </c>
       <c r="J42" t="str">
         <v>Future</v>
@@ -1778,10 +1778,10 @@
         <v>982.5</v>
       </c>
       <c r="H43" t="str">
-        <v>2025-07-01</v>
+        <v>2025</v>
       </c>
       <c r="I43" t="str">
-        <v>2026-07-31</v>
+        <v>2026</v>
       </c>
       <c r="J43" t="str">
         <v>Current</v>
@@ -1810,10 +1810,10 @@
         <v>1013.25</v>
       </c>
       <c r="H44" t="str">
-        <v>2025-08-01</v>
+        <v>2025</v>
       </c>
       <c r="I44" t="str">
-        <v>2026-08-31</v>
+        <v>2026</v>
       </c>
       <c r="J44" t="str">
         <v>Current</v>
@@ -1842,10 +1842,10 @@
         <v>1074.75</v>
       </c>
       <c r="H45" t="str">
-        <v>2025-10-01</v>
+        <v>2025</v>
       </c>
       <c r="I45" t="str">
-        <v>2026-10-31</v>
+        <v>2026</v>
       </c>
       <c r="J45" t="str">
         <v>Current</v>
@@ -1874,10 +1874,10 @@
         <v>982.5</v>
       </c>
       <c r="H46" t="str">
-        <v>2025-07-01</v>
+        <v>2025</v>
       </c>
       <c r="I46" t="str">
-        <v>2026-07-31</v>
+        <v>2026</v>
       </c>
       <c r="J46" t="str">
         <v>Current</v>
@@ -1906,10 +1906,10 @@
         <v>1013.25</v>
       </c>
       <c r="H47" t="str">
-        <v>2025-08-01</v>
+        <v>2025</v>
       </c>
       <c r="I47" t="str">
-        <v>2026-08-31</v>
+        <v>2026</v>
       </c>
       <c r="J47" t="str">
         <v>Current</v>
@@ -1938,10 +1938,10 @@
         <v>1044</v>
       </c>
       <c r="H48" t="str">
-        <v>2025-09-01</v>
+        <v>2025</v>
       </c>
       <c r="I48" t="str">
-        <v>2026-09-31</v>
+        <v>2026</v>
       </c>
       <c r="J48" t="str">
         <v>Current</v>
@@ -1970,10 +1970,10 @@
         <v>1074.75</v>
       </c>
       <c r="H49" t="str">
-        <v>2025-10-01</v>
+        <v>2025</v>
       </c>
       <c r="I49" t="str">
-        <v>2026-10-31</v>
+        <v>2026</v>
       </c>
       <c r="J49" t="str">
         <v>Current</v>
@@ -2002,10 +2002,10 @@
         <v>1105.5</v>
       </c>
       <c r="H50" t="str">
-        <v>2025-11-01</v>
+        <v>2025</v>
       </c>
       <c r="I50" t="str">
-        <v>2026-11-31</v>
+        <v>2026</v>
       </c>
       <c r="J50" t="str">
         <v>Current</v>
@@ -2034,10 +2034,10 @@
         <v>982.5</v>
       </c>
       <c r="H51" t="str">
-        <v>2025-07-01</v>
+        <v>2025</v>
       </c>
       <c r="I51" t="str">
-        <v>2026-07-31</v>
+        <v>2026</v>
       </c>
       <c r="J51" t="str">
         <v>Current</v>
@@ -2066,10 +2066,10 @@
         <v>1013.25</v>
       </c>
       <c r="H52" t="str">
-        <v>2025-08-01</v>
+        <v>2025</v>
       </c>
       <c r="I52" t="str">
-        <v>2026-08-31</v>
+        <v>2026</v>
       </c>
       <c r="J52" t="str">
         <v>Current</v>
@@ -2098,10 +2098,10 @@
         <v>982.5</v>
       </c>
       <c r="H53" t="str">
-        <v>2025-07-01</v>
+        <v>2025</v>
       </c>
       <c r="I53" t="str">
-        <v>2026-07-31</v>
+        <v>2026</v>
       </c>
       <c r="J53" t="str">
         <v>Current</v>
@@ -2130,10 +2130,10 @@
         <v>1013.25</v>
       </c>
       <c r="H54" t="str">
-        <v>2025-08-01</v>
+        <v>2025</v>
       </c>
       <c r="I54" t="str">
-        <v>2026-08-31</v>
+        <v>2026</v>
       </c>
       <c r="J54" t="str">
         <v>Current</v>
@@ -2162,10 +2162,10 @@
         <v>1044</v>
       </c>
       <c r="H55" t="str">
-        <v>2025-09-01</v>
+        <v>2025</v>
       </c>
       <c r="I55" t="str">
-        <v>2026-09-31</v>
+        <v>2026</v>
       </c>
       <c r="J55" t="str">
         <v>Current</v>
@@ -2194,10 +2194,10 @@
         <v>1074.75</v>
       </c>
       <c r="H56" t="str">
-        <v>2025-10-01</v>
+        <v>2025</v>
       </c>
       <c r="I56" t="str">
-        <v>2026-10-31</v>
+        <v>2026</v>
       </c>
       <c r="J56" t="str">
         <v>Current</v>
@@ -2226,10 +2226,10 @@
         <v>1105.5</v>
       </c>
       <c r="H57" t="str">
-        <v>2025-11-01</v>
+        <v>2025</v>
       </c>
       <c r="I57" t="str">
-        <v>2026-11-31</v>
+        <v>2026</v>
       </c>
       <c r="J57" t="str">
         <v>Current</v>
@@ -2258,10 +2258,10 @@
         <v>982.5</v>
       </c>
       <c r="H58" t="str">
-        <v>2025-07-01</v>
+        <v>2025</v>
       </c>
       <c r="I58" t="str">
-        <v>2026-07-31</v>
+        <v>2026</v>
       </c>
       <c r="J58" t="str">
         <v>Current</v>
@@ -2290,10 +2290,10 @@
         <v>1013.25</v>
       </c>
       <c r="H59" t="str">
-        <v>2025-08-01</v>
+        <v>2025</v>
       </c>
       <c r="I59" t="str">
-        <v>2026-08-31</v>
+        <v>2026</v>
       </c>
       <c r="J59" t="str">
         <v>Current</v>
@@ -2322,10 +2322,10 @@
         <v>1044</v>
       </c>
       <c r="H60" t="str">
-        <v>2025-09-01</v>
+        <v>2025</v>
       </c>
       <c r="I60" t="str">
-        <v>2026-09-31</v>
+        <v>2026</v>
       </c>
       <c r="J60" t="str">
         <v>Current</v>
@@ -2354,10 +2354,10 @@
         <v>1074.75</v>
       </c>
       <c r="H61" t="str">
-        <v>2025-10-01</v>
+        <v>2025</v>
       </c>
       <c r="I61" t="str">
-        <v>2026-10-31</v>
+        <v>2026</v>
       </c>
       <c r="J61" t="str">
         <v>Current</v>
@@ -2386,10 +2386,10 @@
         <v>1002.75</v>
       </c>
       <c r="H62" t="str">
-        <v>2025-08-01</v>
+        <v>2025</v>
       </c>
       <c r="I62" t="str">
-        <v>2026-08-31</v>
+        <v>2026</v>
       </c>
       <c r="J62" t="str">
         <v>Current</v>
@@ -2418,10 +2418,10 @@
         <v>1033.5</v>
       </c>
       <c r="H63" t="str">
-        <v>2025-09-01</v>
+        <v>2025</v>
       </c>
       <c r="I63" t="str">
-        <v>2026-09-31</v>
+        <v>2026</v>
       </c>
       <c r="J63" t="str">
         <v>Current</v>
@@ -2450,10 +2450,10 @@
         <v>1064.25</v>
       </c>
       <c r="H64" t="str">
-        <v>2025-10-01</v>
+        <v>2025</v>
       </c>
       <c r="I64" t="str">
-        <v>2026-10-31</v>
+        <v>2026</v>
       </c>
       <c r="J64" t="str">
         <v>Current</v>
@@ -2482,10 +2482,10 @@
         <v>1095</v>
       </c>
       <c r="H65" t="str">
-        <v>2025-11-01</v>
+        <v>2025</v>
       </c>
       <c r="I65" t="str">
-        <v>2026-11-31</v>
+        <v>2026</v>
       </c>
       <c r="J65" t="str">
         <v>Current</v>
@@ -2514,10 +2514,10 @@
         <v>1002.75</v>
       </c>
       <c r="H66" t="str">
-        <v>2025-08-01</v>
+        <v>2025</v>
       </c>
       <c r="I66" t="str">
-        <v>2026-08-31</v>
+        <v>2026</v>
       </c>
       <c r="J66" t="str">
         <v>Current</v>
@@ -2546,10 +2546,10 @@
         <v>1033.5</v>
       </c>
       <c r="H67" t="str">
-        <v>2025-09-01</v>
+        <v>2025</v>
       </c>
       <c r="I67" t="str">
-        <v>2026-09-31</v>
+        <v>2026</v>
       </c>
       <c r="J67" t="str">
         <v>Notice</v>
@@ -2578,10 +2578,10 @@
         <v>1064.25</v>
       </c>
       <c r="H68" t="str">
-        <v>2025-10-01</v>
+        <v>2025</v>
       </c>
       <c r="I68" t="str">
-        <v>2026-10-31</v>
+        <v>2026</v>
       </c>
       <c r="J68" t="str">
         <v>Current</v>
@@ -2610,10 +2610,10 @@
         <v>1095</v>
       </c>
       <c r="H69" t="str">
-        <v>2025-11-01</v>
+        <v>2025</v>
       </c>
       <c r="I69" t="str">
-        <v>2026-11-31</v>
+        <v>2026</v>
       </c>
       <c r="J69" t="str">
         <v>Current</v>
@@ -2642,10 +2642,10 @@
         <v>1125.75</v>
       </c>
       <c r="H70" t="str">
-        <v>2025-12-01</v>
+        <v>2025</v>
       </c>
       <c r="I70" t="str">
-        <v>2026-12-31</v>
+        <v>2026</v>
       </c>
       <c r="J70" t="str">
         <v>Current</v>
@@ -2674,10 +2674,10 @@
         <v>1002.75</v>
       </c>
       <c r="H71" t="str">
-        <v>2025-08-01</v>
+        <v>2025</v>
       </c>
       <c r="I71" t="str">
-        <v>2026-08-31</v>
+        <v>2026</v>
       </c>
       <c r="J71" t="str">
         <v>Current</v>
@@ -2706,10 +2706,10 @@
         <v>1033.5</v>
       </c>
       <c r="H72" t="str">
-        <v>2025-09-01</v>
+        <v>2025</v>
       </c>
       <c r="I72" t="str">
-        <v>2026-09-31</v>
+        <v>2026</v>
       </c>
       <c r="J72" t="str">
         <v>Current</v>
@@ -2738,10 +2738,10 @@
         <v>1002.75</v>
       </c>
       <c r="H73" t="str">
-        <v>2025-08-01</v>
+        <v>2025</v>
       </c>
       <c r="I73" t="str">
-        <v>2026-08-31</v>
+        <v>2026</v>
       </c>
       <c r="J73" t="str">
         <v>Current</v>
@@ -2770,10 +2770,10 @@
         <v>1033.5</v>
       </c>
       <c r="H74" t="str">
-        <v>2025-09-01</v>
+        <v>2025</v>
       </c>
       <c r="I74" t="str">
-        <v>2026-09-31</v>
+        <v>2026</v>
       </c>
       <c r="J74" t="str">
         <v>Current</v>
@@ -2802,10 +2802,10 @@
         <v>1064.25</v>
       </c>
       <c r="H75" t="str">
-        <v>2025-10-01</v>
+        <v>2025</v>
       </c>
       <c r="I75" t="str">
-        <v>2026-10-31</v>
+        <v>2026</v>
       </c>
       <c r="J75" t="str">
         <v>Current</v>
@@ -2834,10 +2834,10 @@
         <v>1002.75</v>
       </c>
       <c r="H76" t="str">
-        <v>2025-08-01</v>
+        <v>2025</v>
       </c>
       <c r="I76" t="str">
-        <v>2026-08-31</v>
+        <v>2026</v>
       </c>
       <c r="J76" t="str">
         <v>Current</v>
@@ -2866,10 +2866,10 @@
         <v>1033.5</v>
       </c>
       <c r="H77" t="str">
-        <v>2025-09-01</v>
+        <v>2025</v>
       </c>
       <c r="I77" t="str">
-        <v>2026-09-31</v>
+        <v>2026</v>
       </c>
       <c r="J77" t="str">
         <v>Current</v>
@@ -2898,10 +2898,10 @@
         <v>1064.25</v>
       </c>
       <c r="H78" t="str">
-        <v>2025-10-01</v>
+        <v>2025</v>
       </c>
       <c r="I78" t="str">
-        <v>2026-10-31</v>
+        <v>2026</v>
       </c>
       <c r="J78" t="str">
         <v>Current</v>
@@ -2930,10 +2930,10 @@
         <v>1095</v>
       </c>
       <c r="H79" t="str">
-        <v>2025-11-01</v>
+        <v>2025</v>
       </c>
       <c r="I79" t="str">
-        <v>2026-11-31</v>
+        <v>2026</v>
       </c>
       <c r="J79" t="str">
         <v>Current</v>
@@ -2962,10 +2962,10 @@
         <v>1125.75</v>
       </c>
       <c r="H80" t="str">
-        <v>2025-12-01</v>
+        <v>2025</v>
       </c>
       <c r="I80" t="str">
-        <v>2026-12-31</v>
+        <v>2026</v>
       </c>
       <c r="J80" t="str">
         <v>Current</v>
@@ -2994,10 +2994,10 @@
         <v>1002.75</v>
       </c>
       <c r="H81" t="str">
-        <v>2025-08-01</v>
+        <v>2025</v>
       </c>
       <c r="I81" t="str">
-        <v>2026-08-31</v>
+        <v>2026</v>
       </c>
       <c r="J81" t="str">
         <v>Current</v>
@@ -3026,10 +3026,10 @@
         <v>1033.5</v>
       </c>
       <c r="H82" t="str">
-        <v>2025-09-01</v>
+        <v>2025</v>
       </c>
       <c r="I82" t="str">
-        <v>2026-09-31</v>
+        <v>2026</v>
       </c>
       <c r="J82" t="str">
         <v>Notice</v>
@@ -3058,10 +3058,10 @@
         <v>1095</v>
       </c>
       <c r="H83" t="str">
-        <v>2025-11-01</v>
+        <v>2025</v>
       </c>
       <c r="I83" t="str">
-        <v>2026-11-31</v>
+        <v>2026</v>
       </c>
       <c r="J83" t="str">
         <v>Current</v>
@@ -3090,10 +3090,10 @@
         <v>1023</v>
       </c>
       <c r="H84" t="str">
-        <v>2025-09-01</v>
+        <v>2025</v>
       </c>
       <c r="I84" t="str">
-        <v>2026-09-31</v>
+        <v>2026</v>
       </c>
       <c r="J84" t="str">
         <v>Current</v>
@@ -3122,10 +3122,10 @@
         <v>1053.75</v>
       </c>
       <c r="H85" t="str">
-        <v>2025-10-01</v>
+        <v>2025</v>
       </c>
       <c r="I85" t="str">
-        <v>2026-10-31</v>
+        <v>2026</v>
       </c>
       <c r="J85" t="str">
         <v>Notice</v>
@@ -3154,10 +3154,10 @@
         <v>1084.5</v>
       </c>
       <c r="H86" t="str">
-        <v>2025-11-01</v>
+        <v>2025</v>
       </c>
       <c r="I86" t="str">
-        <v>2026-11-31</v>
+        <v>2026</v>
       </c>
       <c r="J86" t="str">
         <v>Current</v>
@@ -3186,10 +3186,10 @@
         <v>1115.25</v>
       </c>
       <c r="H87" t="str">
-        <v>2025-12-01</v>
+        <v>2025</v>
       </c>
       <c r="I87" t="str">
-        <v>2026-12-31</v>
+        <v>2026</v>
       </c>
       <c r="J87" t="str">
         <v>Current</v>
@@ -3218,10 +3218,10 @@
         <v>1023</v>
       </c>
       <c r="H88" t="str">
-        <v>2025-09-01</v>
+        <v>2025</v>
       </c>
       <c r="I88" t="str">
-        <v>2026-09-31</v>
+        <v>2026</v>
       </c>
       <c r="J88" t="str">
         <v>Current</v>
@@ -3250,10 +3250,10 @@
         <v>1053.75</v>
       </c>
       <c r="H89" t="str">
-        <v>2025-10-01</v>
+        <v>2025</v>
       </c>
       <c r="I89" t="str">
-        <v>2026-10-31</v>
+        <v>2026</v>
       </c>
       <c r="J89" t="str">
         <v>Current</v>
@@ -3282,10 +3282,10 @@
         <v>1115.25</v>
       </c>
       <c r="H90" t="str">
-        <v>2025-12-01</v>
+        <v>2025</v>
       </c>
       <c r="I90" t="str">
-        <v>2026-12-31</v>
+        <v>2026</v>
       </c>
       <c r="J90" t="str">
         <v>Current</v>
@@ -3314,10 +3314,10 @@
         <v>1146</v>
       </c>
       <c r="H91" t="str">
-        <v>2025-01-01</v>
+        <v>2025</v>
       </c>
       <c r="I91" t="str">
-        <v>2026-01-31</v>
+        <v>2026</v>
       </c>
       <c r="J91" t="str">
         <v>Current</v>
@@ -3346,10 +3346,10 @@
         <v>1023</v>
       </c>
       <c r="H92" t="str">
-        <v>2025-09-01</v>
+        <v>2025</v>
       </c>
       <c r="I92" t="str">
-        <v>2026-09-31</v>
+        <v>2026</v>
       </c>
       <c r="J92" t="str">
         <v>Current</v>
@@ -3378,10 +3378,10 @@
         <v>1053.75</v>
       </c>
       <c r="H93" t="str">
-        <v>2025-10-01</v>
+        <v>2025</v>
       </c>
       <c r="I93" t="str">
-        <v>2026-10-31</v>
+        <v>2026</v>
       </c>
       <c r="J93" t="str">
         <v>Current</v>
@@ -3410,10 +3410,10 @@
         <v>1084.5</v>
       </c>
       <c r="H94" t="str">
-        <v>2025-11-01</v>
+        <v>2025</v>
       </c>
       <c r="I94" t="str">
-        <v>2026-11-31</v>
+        <v>2026</v>
       </c>
       <c r="J94" t="str">
         <v>Current</v>
@@ -3442,10 +3442,10 @@
         <v>1023</v>
       </c>
       <c r="H95" t="str">
-        <v>2025-09-01</v>
+        <v>2025</v>
       </c>
       <c r="I95" t="str">
-        <v>2026-09-31</v>
+        <v>2026</v>
       </c>
       <c r="J95" t="str">
         <v>Current</v>
@@ -3474,10 +3474,10 @@
         <v>1053.75</v>
       </c>
       <c r="H96" t="str">
-        <v>2025-10-01</v>
+        <v>2025</v>
       </c>
       <c r="I96" t="str">
-        <v>2026-10-31</v>
+        <v>2026</v>
       </c>
       <c r="J96" t="str">
         <v>Current</v>
@@ -3506,10 +3506,10 @@
         <v>1084.5</v>
       </c>
       <c r="H97" t="str">
-        <v>2025-11-01</v>
+        <v>2025</v>
       </c>
       <c r="I97" t="str">
-        <v>2026-11-31</v>
+        <v>2026</v>
       </c>
       <c r="J97" t="str">
         <v>Current</v>
@@ -3538,10 +3538,10 @@
         <v>1023</v>
       </c>
       <c r="H98" t="str">
-        <v>2025-09-01</v>
+        <v>2025</v>
       </c>
       <c r="I98" t="str">
-        <v>2026-09-31</v>
+        <v>2026</v>
       </c>
       <c r="J98" t="str">
         <v>Current</v>
@@ -3570,10 +3570,10 @@
         <v>1053.75</v>
       </c>
       <c r="H99" t="str">
-        <v>2025-10-01</v>
+        <v>2025</v>
       </c>
       <c r="I99" t="str">
-        <v>2026-10-31</v>
+        <v>2026</v>
       </c>
       <c r="J99" t="str">
         <v>Notice</v>
@@ -3602,10 +3602,10 @@
         <v>1115.25</v>
       </c>
       <c r="H100" t="str">
-        <v>2025-12-01</v>
+        <v>2025</v>
       </c>
       <c r="I100" t="str">
-        <v>2026-12-31</v>
+        <v>2026</v>
       </c>
       <c r="J100" t="str">
         <v>Current</v>
@@ -3634,10 +3634,10 @@
         <v>1146</v>
       </c>
       <c r="H101" t="str">
-        <v>2025-01-01</v>
+        <v>2025</v>
       </c>
       <c r="I101" t="str">
-        <v>2026-01-31</v>
+        <v>2026</v>
       </c>
       <c r="J101" t="str">
         <v>Current</v>
@@ -3666,10 +3666,10 @@
         <v>1023</v>
       </c>
       <c r="H102" t="str">
-        <v>2025-09-01</v>
+        <v>2025</v>
       </c>
       <c r="I102" t="str">
-        <v>2026-09-31</v>
+        <v>2026</v>
       </c>
       <c r="J102" t="str">
         <v>Current</v>
@@ -3698,10 +3698,10 @@
         <v>1053.75</v>
       </c>
       <c r="H103" t="str">
-        <v>2025-10-01</v>
+        <v>2025</v>
       </c>
       <c r="I103" t="str">
-        <v>2026-10-31</v>
+        <v>2026</v>
       </c>
       <c r="J103" t="str">
         <v>Current</v>
@@ -3730,10 +3730,10 @@
         <v>1084.5</v>
       </c>
       <c r="H104" t="str">
-        <v>2025-11-01</v>
+        <v>2025</v>
       </c>
       <c r="I104" t="str">
-        <v>2026-11-31</v>
+        <v>2026</v>
       </c>
       <c r="J104" t="str">
         <v>Current</v>
@@ -3762,10 +3762,10 @@
         <v>1115.25</v>
       </c>
       <c r="H105" t="str">
-        <v>2025-12-01</v>
+        <v>2025</v>
       </c>
       <c r="I105" t="str">
-        <v>2026-12-31</v>
+        <v>2026</v>
       </c>
       <c r="J105" t="str">
         <v>Current</v>
@@ -3794,10 +3794,10 @@
         <v>1043.25</v>
       </c>
       <c r="H106" t="str">
-        <v>2025-10-01</v>
+        <v>2025</v>
       </c>
       <c r="I106" t="str">
-        <v>2026-10-31</v>
+        <v>2026</v>
       </c>
       <c r="J106" t="str">
         <v>Current</v>
@@ -3826,10 +3826,10 @@
         <v>1074</v>
       </c>
       <c r="H107" t="str">
-        <v>2025-11-01</v>
+        <v>2025</v>
       </c>
       <c r="I107" t="str">
-        <v>2026-11-31</v>
+        <v>2026</v>
       </c>
       <c r="J107" t="str">
         <v>Current</v>
@@ -3858,10 +3858,10 @@
         <v>1104.75</v>
       </c>
       <c r="H108" t="str">
-        <v>2025-12-01</v>
+        <v>2025</v>
       </c>
       <c r="I108" t="str">
-        <v>2026-12-31</v>
+        <v>2026</v>
       </c>
       <c r="J108" t="str">
         <v>Current</v>
@@ -3890,10 +3890,10 @@
         <v>1135.5</v>
       </c>
       <c r="H109" t="str">
-        <v>2025-01-01</v>
+        <v>2025</v>
       </c>
       <c r="I109" t="str">
-        <v>2026-01-31</v>
+        <v>2026</v>
       </c>
       <c r="J109" t="str">
         <v>Current</v>
@@ -3922,10 +3922,10 @@
         <v>1166.25</v>
       </c>
       <c r="H110" t="str">
-        <v>2025-02-01</v>
+        <v>2025</v>
       </c>
       <c r="I110" t="str">
-        <v>2026-02-31</v>
+        <v>2026</v>
       </c>
       <c r="J110" t="str">
         <v>Current</v>
@@ -3954,10 +3954,10 @@
         <v>1043.25</v>
       </c>
       <c r="H111" t="str">
-        <v>2025-10-01</v>
+        <v>2025</v>
       </c>
       <c r="I111" t="str">
-        <v>2026-10-31</v>
+        <v>2026</v>
       </c>
       <c r="J111" t="str">
         <v>Current</v>
@@ -3986,10 +3986,10 @@
         <v>1074</v>
       </c>
       <c r="H112" t="str">
-        <v>2025-11-01</v>
+        <v>2025</v>
       </c>
       <c r="I112" t="str">
-        <v>2026-11-31</v>
+        <v>2026</v>
       </c>
       <c r="J112" t="str">
         <v>Current</v>
@@ -4018,10 +4018,10 @@
         <v>1104.75</v>
       </c>
       <c r="H113" t="str">
-        <v>2025-12-01</v>
+        <v>2025</v>
       </c>
       <c r="I113" t="str">
-        <v>2026-12-31</v>
+        <v>2026</v>
       </c>
       <c r="J113" t="str">
         <v>Current</v>
@@ -4050,10 +4050,10 @@
         <v>1043.25</v>
       </c>
       <c r="H114" t="str">
-        <v>2025-10-01</v>
+        <v>2025</v>
       </c>
       <c r="I114" t="str">
-        <v>2026-10-31</v>
+        <v>2026</v>
       </c>
       <c r="J114" t="str">
         <v>Current</v>
@@ -4082,10 +4082,10 @@
         <v>1074</v>
       </c>
       <c r="H115" t="str">
-        <v>2025-11-01</v>
+        <v>2025</v>
       </c>
       <c r="I115" t="str">
-        <v>2026-11-31</v>
+        <v>2026</v>
       </c>
       <c r="J115" t="str">
         <v>Notice</v>
@@ -4114,10 +4114,10 @@
         <v>1043.25</v>
       </c>
       <c r="H116" t="str">
-        <v>2025-10-01</v>
+        <v>2025</v>
       </c>
       <c r="I116" t="str">
-        <v>2026-10-31</v>
+        <v>2026</v>
       </c>
       <c r="J116" t="str">
         <v>Current</v>
@@ -4146,10 +4146,10 @@
         <v>1074</v>
       </c>
       <c r="H117" t="str">
-        <v>2025-11-01</v>
+        <v>2025</v>
       </c>
       <c r="I117" t="str">
-        <v>2026-11-31</v>
+        <v>2026</v>
       </c>
       <c r="J117" t="str">
         <v>Current</v>
@@ -4178,10 +4178,10 @@
         <v>1104.75</v>
       </c>
       <c r="H118" t="str">
-        <v>2025-12-01</v>
+        <v>2025</v>
       </c>
       <c r="I118" t="str">
-        <v>2026-12-31</v>
+        <v>2026</v>
       </c>
       <c r="J118" t="str">
         <v>Current</v>
@@ -4210,10 +4210,10 @@
         <v>1135.5</v>
       </c>
       <c r="H119" t="str">
-        <v>2025-01-01</v>
+        <v>2025</v>
       </c>
       <c r="I119" t="str">
-        <v>2026-01-31</v>
+        <v>2026</v>
       </c>
       <c r="J119" t="str">
         <v>Current</v>
@@ -4242,10 +4242,10 @@
         <v>1166.25</v>
       </c>
       <c r="H120" t="str">
-        <v>2025-02-01</v>
+        <v>2025</v>
       </c>
       <c r="I120" t="str">
-        <v>2026-02-31</v>
+        <v>2026</v>
       </c>
       <c r="J120" t="str">
         <v>Current</v>
@@ -4274,10 +4274,10 @@
         <v>1043.25</v>
       </c>
       <c r="H121" t="str">
-        <v>2025-10-01</v>
+        <v>2025</v>
       </c>
       <c r="I121" t="str">
-        <v>2026-10-31</v>
+        <v>2026</v>
       </c>
       <c r="J121" t="str">
         <v>Current</v>
@@ -4306,10 +4306,10 @@
         <v>1074</v>
       </c>
       <c r="H122" t="str">
-        <v>2025-11-01</v>
+        <v>2025</v>
       </c>
       <c r="I122" t="str">
-        <v>2026-11-31</v>
+        <v>2026</v>
       </c>
       <c r="J122" t="str">
         <v>Current</v>
@@ -4338,10 +4338,10 @@
         <v>1104.75</v>
       </c>
       <c r="H123" t="str">
-        <v>2025-12-01</v>
+        <v>2025</v>
       </c>
       <c r="I123" t="str">
-        <v>2026-12-31</v>
+        <v>2026</v>
       </c>
       <c r="J123" t="str">
         <v>Current</v>
@@ -4370,10 +4370,10 @@
         <v>1135.5</v>
       </c>
       <c r="H124" t="str">
-        <v>2025-01-01</v>
+        <v>2025</v>
       </c>
       <c r="I124" t="str">
-        <v>2026-01-31</v>
+        <v>2026</v>
       </c>
       <c r="J124" t="str">
         <v>Current</v>
@@ -4402,10 +4402,10 @@
         <v>1063.5</v>
       </c>
       <c r="H125" t="str">
-        <v>2025-11-01</v>
+        <v>2025</v>
       </c>
       <c r="I125" t="str">
-        <v>2026-11-31</v>
+        <v>2026</v>
       </c>
       <c r="J125" t="str">
         <v>Current</v>
@@ -4434,10 +4434,10 @@
         <v>1094.25</v>
       </c>
       <c r="H126" t="str">
-        <v>2025-12-01</v>
+        <v>2025</v>
       </c>
       <c r="I126" t="str">
-        <v>2026-12-31</v>
+        <v>2026</v>
       </c>
       <c r="J126" t="str">
         <v>Current</v>
@@ -4466,10 +4466,10 @@
         <v>1125</v>
       </c>
       <c r="H127" t="str">
-        <v>2025-01-01</v>
+        <v>2025</v>
       </c>
       <c r="I127" t="str">
-        <v>2026-01-31</v>
+        <v>2026</v>
       </c>
       <c r="J127" t="str">
         <v>Current</v>
@@ -4498,10 +4498,10 @@
         <v>1155.75</v>
       </c>
       <c r="H128" t="str">
-        <v>2025-02-01</v>
+        <v>2025</v>
       </c>
       <c r="I128" t="str">
-        <v>2026-02-31</v>
+        <v>2026</v>
       </c>
       <c r="J128" t="str">
         <v>Current</v>
@@ -4530,10 +4530,10 @@
         <v>1063.5</v>
       </c>
       <c r="H129" t="str">
-        <v>2025-11-01</v>
+        <v>2025</v>
       </c>
       <c r="I129" t="str">
-        <v>2026-11-31</v>
+        <v>2026</v>
       </c>
       <c r="J129" t="str">
         <v>Future</v>
@@ -4562,10 +4562,10 @@
         <v>1094.25</v>
       </c>
       <c r="H130" t="str">
-        <v>2025-12-01</v>
+        <v>2025</v>
       </c>
       <c r="I130" t="str">
-        <v>2026-12-31</v>
+        <v>2026</v>
       </c>
       <c r="J130" t="str">
         <v>Future</v>
@@ -4594,10 +4594,10 @@
         <v>1125</v>
       </c>
       <c r="H131" t="str">
-        <v>2025-01-01</v>
+        <v>2025</v>
       </c>
       <c r="I131" t="str">
-        <v>2026-01-31</v>
+        <v>2026</v>
       </c>
       <c r="J131" t="str">
         <v>Future</v>
@@ -4626,10 +4626,10 @@
         <v>1155.75</v>
       </c>
       <c r="H132" t="str">
-        <v>2025-02-01</v>
+        <v>2025</v>
       </c>
       <c r="I132" t="str">
-        <v>2026-02-31</v>
+        <v>2026</v>
       </c>
       <c r="J132" t="str">
         <v>Future</v>
@@ -4658,10 +4658,10 @@
         <v>1186.5</v>
       </c>
       <c r="H133" t="str">
-        <v>2025-03-01</v>
+        <v>2025</v>
       </c>
       <c r="I133" t="str">
-        <v>2026-03-31</v>
+        <v>2026</v>
       </c>
       <c r="J133" t="str">
         <v>Future</v>
@@ -4690,10 +4690,10 @@
         <v>1063.5</v>
       </c>
       <c r="H134" t="str">
-        <v>2025-11-01</v>
+        <v>2025</v>
       </c>
       <c r="I134" t="str">
-        <v>2026-11-31</v>
+        <v>2026</v>
       </c>
       <c r="J134" t="str">
         <v>Current</v>
@@ -4722,10 +4722,10 @@
         <v>1094.25</v>
       </c>
       <c r="H135" t="str">
-        <v>2025-12-01</v>
+        <v>2025</v>
       </c>
       <c r="I135" t="str">
-        <v>2026-12-31</v>
+        <v>2026</v>
       </c>
       <c r="J135" t="str">
         <v>Notice</v>
@@ -4754,10 +4754,10 @@
         <v>1063.5</v>
       </c>
       <c r="H136" t="str">
-        <v>2025-11-01</v>
+        <v>2025</v>
       </c>
       <c r="I136" t="str">
-        <v>2026-11-31</v>
+        <v>2026</v>
       </c>
       <c r="J136" t="str">
         <v>Current</v>
@@ -4786,10 +4786,10 @@
         <v>1094.25</v>
       </c>
       <c r="H137" t="str">
-        <v>2025-12-01</v>
+        <v>2025</v>
       </c>
       <c r="I137" t="str">
-        <v>2026-12-31</v>
+        <v>2026</v>
       </c>
       <c r="J137" t="str">
         <v>Current</v>
@@ -4818,10 +4818,10 @@
         <v>1125</v>
       </c>
       <c r="H138" t="str">
-        <v>2025-01-01</v>
+        <v>2025</v>
       </c>
       <c r="I138" t="str">
-        <v>2026-01-31</v>
+        <v>2026</v>
       </c>
       <c r="J138" t="str">
         <v>Current</v>
@@ -4850,10 +4850,10 @@
         <v>1063.5</v>
       </c>
       <c r="H139" t="str">
-        <v>2025-11-01</v>
+        <v>2025</v>
       </c>
       <c r="I139" t="str">
-        <v>2026-11-31</v>
+        <v>2026</v>
       </c>
       <c r="J139" t="str">
         <v>Current</v>
@@ -4882,10 +4882,10 @@
         <v>1094.25</v>
       </c>
       <c r="H140" t="str">
-        <v>2025-12-01</v>
+        <v>2025</v>
       </c>
       <c r="I140" t="str">
-        <v>2026-12-31</v>
+        <v>2026</v>
       </c>
       <c r="J140" t="str">
         <v>Current</v>
@@ -4914,10 +4914,10 @@
         <v>1125</v>
       </c>
       <c r="H141" t="str">
-        <v>2025-01-01</v>
+        <v>2025</v>
       </c>
       <c r="I141" t="str">
-        <v>2026-01-31</v>
+        <v>2026</v>
       </c>
       <c r="J141" t="str">
         <v>Current</v>
@@ -4946,10 +4946,10 @@
         <v>1155.75</v>
       </c>
       <c r="H142" t="str">
-        <v>2025-02-01</v>
+        <v>2025</v>
       </c>
       <c r="I142" t="str">
-        <v>2026-02-31</v>
+        <v>2026</v>
       </c>
       <c r="J142" t="str">
         <v>Current</v>
@@ -4978,10 +4978,10 @@
         <v>1186.5</v>
       </c>
       <c r="H143" t="str">
-        <v>2025-03-01</v>
+        <v>2025</v>
       </c>
       <c r="I143" t="str">
-        <v>2026-03-31</v>
+        <v>2026</v>
       </c>
       <c r="J143" t="str">
         <v>Current</v>
@@ -5010,10 +5010,10 @@
         <v>1063.5</v>
       </c>
       <c r="H144" t="str">
-        <v>2025-11-01</v>
+        <v>2025</v>
       </c>
       <c r="I144" t="str">
-        <v>2026-11-31</v>
+        <v>2026</v>
       </c>
       <c r="J144" t="str">
         <v>Current</v>
@@ -5042,10 +5042,10 @@
         <v>1094.25</v>
       </c>
       <c r="H145" t="str">
-        <v>2025-12-01</v>
+        <v>2025</v>
       </c>
       <c r="I145" t="str">
-        <v>2026-12-31</v>
+        <v>2026</v>
       </c>
       <c r="J145" t="str">
         <v>Current</v>
@@ -5074,10 +5074,10 @@
         <v>1155.75</v>
       </c>
       <c r="H146" t="str">
-        <v>2025-02-01</v>
+        <v>2025</v>
       </c>
       <c r="I146" t="str">
-        <v>2026-02-31</v>
+        <v>2026</v>
       </c>
       <c r="J146" t="str">
         <v>Current</v>
@@ -5106,10 +5106,10 @@
         <v>1083.75</v>
       </c>
       <c r="H147" t="str">
-        <v>2025-12-01</v>
+        <v>2025</v>
       </c>
       <c r="I147" t="str">
-        <v>2026-12-31</v>
+        <v>2026</v>
       </c>
       <c r="J147" t="str">
         <v>Current</v>
@@ -5138,10 +5138,10 @@
         <v>1114.5</v>
       </c>
       <c r="H148" t="str">
-        <v>2025-01-01</v>
+        <v>2025</v>
       </c>
       <c r="I148" t="str">
-        <v>2026-01-31</v>
+        <v>2026</v>
       </c>
       <c r="J148" t="str">
         <v>Current</v>
@@ -5170,10 +5170,10 @@
         <v>1145.25</v>
       </c>
       <c r="H149" t="str">
-        <v>2025-02-01</v>
+        <v>2025</v>
       </c>
       <c r="I149" t="str">
-        <v>2026-02-31</v>
+        <v>2026</v>
       </c>
       <c r="J149" t="str">
         <v>Current</v>
@@ -5202,10 +5202,10 @@
         <v>1176</v>
       </c>
       <c r="H150" t="str">
-        <v>2025-03-01</v>
+        <v>2025</v>
       </c>
       <c r="I150" t="str">
-        <v>2026-03-31</v>
+        <v>2026</v>
       </c>
       <c r="J150" t="str">
         <v>Current</v>
@@ -5234,10 +5234,10 @@
         <v>1083.75</v>
       </c>
       <c r="H151" t="str">
-        <v>2025-12-01</v>
+        <v>2025</v>
       </c>
       <c r="I151" t="str">
-        <v>2026-12-31</v>
+        <v>2026</v>
       </c>
       <c r="J151" t="str">
         <v>Current</v>
@@ -5266,10 +5266,10 @@
         <v>1114.5</v>
       </c>
       <c r="H152" t="str">
-        <v>2025-01-01</v>
+        <v>2025</v>
       </c>
       <c r="I152" t="str">
-        <v>2026-01-31</v>
+        <v>2026</v>
       </c>
       <c r="J152" t="str">
         <v>Notice</v>
@@ -5298,10 +5298,10 @@
         <v>1176</v>
       </c>
       <c r="H153" t="str">
-        <v>2025-03-01</v>
+        <v>2025</v>
       </c>
       <c r="I153" t="str">
-        <v>2026-03-31</v>
+        <v>2026</v>
       </c>
       <c r="J153" t="str">
         <v>Current</v>
@@ -5330,10 +5330,10 @@
         <v>1206.75</v>
       </c>
       <c r="H154" t="str">
-        <v>2025-04-01</v>
+        <v>2025</v>
       </c>
       <c r="I154" t="str">
-        <v>2026-04-31</v>
+        <v>2026</v>
       </c>
       <c r="J154" t="str">
         <v>Current</v>
@@ -5362,10 +5362,10 @@
         <v>1083.75</v>
       </c>
       <c r="H155" t="str">
-        <v>2025-12-01</v>
+        <v>2025</v>
       </c>
       <c r="I155" t="str">
-        <v>2026-12-31</v>
+        <v>2026</v>
       </c>
       <c r="J155" t="str">
         <v>Current</v>
@@ -5394,10 +5394,10 @@
         <v>1114.5</v>
       </c>
       <c r="H156" t="str">
-        <v>2025-01-01</v>
+        <v>2025</v>
       </c>
       <c r="I156" t="str">
-        <v>2026-01-31</v>
+        <v>2026</v>
       </c>
       <c r="J156" t="str">
         <v>Current</v>
@@ -5426,10 +5426,10 @@
         <v>1145.25</v>
       </c>
       <c r="H157" t="str">
-        <v>2025-02-01</v>
+        <v>2025</v>
       </c>
       <c r="I157" t="str">
-        <v>2026-02-31</v>
+        <v>2026</v>
       </c>
       <c r="J157" t="str">
         <v>Current</v>
@@ -5458,10 +5458,10 @@
         <v>1083.75</v>
       </c>
       <c r="H158" t="str">
-        <v>2025-12-01</v>
+        <v>2025</v>
       </c>
       <c r="I158" t="str">
-        <v>2026-12-31</v>
+        <v>2026</v>
       </c>
       <c r="J158" t="str">
         <v>Current</v>
@@ -5490,10 +5490,10 @@
         <v>1114.5</v>
       </c>
       <c r="H159" t="str">
-        <v>2025-01-01</v>
+        <v>2025</v>
       </c>
       <c r="I159" t="str">
-        <v>2026-01-31</v>
+        <v>2026</v>
       </c>
       <c r="J159" t="str">
         <v>Current</v>
@@ -5522,10 +5522,10 @@
         <v>1145.25</v>
       </c>
       <c r="H160" t="str">
-        <v>2025-02-01</v>
+        <v>2025</v>
       </c>
       <c r="I160" t="str">
-        <v>2026-02-31</v>
+        <v>2026</v>
       </c>
       <c r="J160" t="str">
         <v>Current</v>
@@ -5554,10 +5554,10 @@
         <v>1083.75</v>
       </c>
       <c r="H161" t="str">
-        <v>2025-12-01</v>
+        <v>2025</v>
       </c>
       <c r="I161" t="str">
-        <v>2026-12-31</v>
+        <v>2026</v>
       </c>
       <c r="J161" t="str">
         <v>Current</v>
@@ -5586,10 +5586,10 @@
         <v>1114.5</v>
       </c>
       <c r="H162" t="str">
-        <v>2025-01-01</v>
+        <v>2025</v>
       </c>
       <c r="I162" t="str">
-        <v>2026-01-31</v>
+        <v>2026</v>
       </c>
       <c r="J162" t="str">
         <v>Current</v>
@@ -5618,10 +5618,10 @@
         <v>1176</v>
       </c>
       <c r="H163" t="str">
-        <v>2025-03-01</v>
+        <v>2025</v>
       </c>
       <c r="I163" t="str">
-        <v>2026-03-31</v>
+        <v>2026</v>
       </c>
       <c r="J163" t="str">
         <v>Current</v>
@@ -5650,10 +5650,10 @@
         <v>1206.75</v>
       </c>
       <c r="H164" t="str">
-        <v>2025-04-01</v>
+        <v>2025</v>
       </c>
       <c r="I164" t="str">
-        <v>2026-04-31</v>
+        <v>2026</v>
       </c>
       <c r="J164" t="str">
         <v>Current</v>
@@ -5682,10 +5682,10 @@
         <v>1083.75</v>
       </c>
       <c r="H165" t="str">
-        <v>2025-12-01</v>
+        <v>2025</v>
       </c>
       <c r="I165" t="str">
-        <v>2026-12-31</v>
+        <v>2026</v>
       </c>
       <c r="J165" t="str">
         <v>Current</v>
@@ -5714,10 +5714,10 @@
         <v>1114.5</v>
       </c>
       <c r="H166" t="str">
-        <v>2025-01-01</v>
+        <v>2025</v>
       </c>
       <c r="I166" t="str">
-        <v>2026-01-31</v>
+        <v>2026</v>
       </c>
       <c r="J166" t="str">
         <v>Notice</v>
@@ -5746,10 +5746,10 @@
         <v>1145.25</v>
       </c>
       <c r="H167" t="str">
-        <v>2025-02-01</v>
+        <v>2025</v>
       </c>
       <c r="I167" t="str">
-        <v>2026-02-31</v>
+        <v>2026</v>
       </c>
       <c r="J167" t="str">
         <v>Current</v>
@@ -5778,10 +5778,10 @@
         <v>1176</v>
       </c>
       <c r="H168" t="str">
-        <v>2025-03-01</v>
+        <v>2025</v>
       </c>
       <c r="I168" t="str">
-        <v>2026-03-31</v>
+        <v>2026</v>
       </c>
       <c r="J168" t="str">
         <v>Current</v>
@@ -5810,10 +5810,10 @@
         <v>1104</v>
       </c>
       <c r="H169" t="str">
-        <v>2025-01-01</v>
+        <v>2025</v>
       </c>
       <c r="I169" t="str">
-        <v>2026-01-31</v>
+        <v>2026</v>
       </c>
       <c r="J169" t="str">
         <v>Current</v>
@@ -5842,10 +5842,10 @@
         <v>1134.75</v>
       </c>
       <c r="H170" t="str">
-        <v>2025-02-01</v>
+        <v>2025</v>
       </c>
       <c r="I170" t="str">
-        <v>2026-02-31</v>
+        <v>2026</v>
       </c>
       <c r="J170" t="str">
         <v>Notice</v>
@@ -5874,10 +5874,10 @@
         <v>1196.25</v>
       </c>
       <c r="H171" t="str">
-        <v>2025-04-01</v>
+        <v>2025</v>
       </c>
       <c r="I171" t="str">
-        <v>2026-04-31</v>
+        <v>2026</v>
       </c>
       <c r="J171" t="str">
         <v>Current</v>
@@ -5906,10 +5906,10 @@
         <v>1104</v>
       </c>
       <c r="H172" t="str">
-        <v>2025-01-01</v>
+        <v>2025</v>
       </c>
       <c r="I172" t="str">
-        <v>2026-01-31</v>
+        <v>2026</v>
       </c>
       <c r="J172" t="str">
         <v>Current</v>
@@ -5938,10 +5938,10 @@
         <v>1134.75</v>
       </c>
       <c r="H173" t="str">
-        <v>2025-02-01</v>
+        <v>2025</v>
       </c>
       <c r="I173" t="str">
-        <v>2026-02-31</v>
+        <v>2026</v>
       </c>
       <c r="J173" t="str">
         <v>Current</v>
@@ -5970,10 +5970,10 @@
         <v>1165.5</v>
       </c>
       <c r="H174" t="str">
-        <v>2025-03-01</v>
+        <v>2025</v>
       </c>
       <c r="I174" t="str">
-        <v>2026-03-31</v>
+        <v>2026</v>
       </c>
       <c r="J174" t="str">
         <v>Current</v>
@@ -6002,10 +6002,10 @@
         <v>1196.25</v>
       </c>
       <c r="H175" t="str">
-        <v>2025-04-01</v>
+        <v>2025</v>
       </c>
       <c r="I175" t="str">
-        <v>2026-04-31</v>
+        <v>2026</v>
       </c>
       <c r="J175" t="str">
         <v>Current</v>
@@ -6034,10 +6034,10 @@
         <v>1227</v>
       </c>
       <c r="H176" t="str">
-        <v>2025-05-01</v>
+        <v>2025</v>
       </c>
       <c r="I176" t="str">
-        <v>2026-05-31</v>
+        <v>2026</v>
       </c>
       <c r="J176" t="str">
         <v>Current</v>
@@ -6066,10 +6066,10 @@
         <v>1104</v>
       </c>
       <c r="H177" t="str">
-        <v>2025-01-01</v>
+        <v>2025</v>
       </c>
       <c r="I177" t="str">
-        <v>2026-01-31</v>
+        <v>2026</v>
       </c>
       <c r="J177" t="str">
         <v>Current</v>
@@ -6098,10 +6098,10 @@
         <v>1134.75</v>
       </c>
       <c r="H178" t="str">
-        <v>2025-02-01</v>
+        <v>2025</v>
       </c>
       <c r="I178" t="str">
-        <v>2026-02-31</v>
+        <v>2026</v>
       </c>
       <c r="J178" t="str">
         <v>Current</v>
@@ -6130,10 +6130,10 @@
         <v>1165.5</v>
       </c>
       <c r="H179" t="str">
-        <v>2025-03-01</v>
+        <v>2025</v>
       </c>
       <c r="I179" t="str">
-        <v>2026-03-31</v>
+        <v>2026</v>
       </c>
       <c r="J179" t="str">
         <v>Current</v>
@@ -6162,10 +6162,10 @@
         <v>1104</v>
       </c>
       <c r="H180" t="str">
-        <v>2025-01-01</v>
+        <v>2025</v>
       </c>
       <c r="I180" t="str">
-        <v>2026-01-31</v>
+        <v>2026</v>
       </c>
       <c r="J180" t="str">
         <v>Current</v>
@@ -6194,10 +6194,10 @@
         <v>1134.75</v>
       </c>
       <c r="H181" t="str">
-        <v>2025-02-01</v>
+        <v>2025</v>
       </c>
       <c r="I181" t="str">
-        <v>2026-02-31</v>
+        <v>2026</v>
       </c>
       <c r="J181" t="str">
         <v>Current</v>
@@ -6226,10 +6226,10 @@
         <v>1104</v>
       </c>
       <c r="H182" t="str">
-        <v>2025-01-01</v>
+        <v>2025</v>
       </c>
       <c r="I182" t="str">
-        <v>2026-01-31</v>
+        <v>2026</v>
       </c>
       <c r="J182" t="str">
         <v>Current</v>
@@ -6258,10 +6258,10 @@
         <v>1134.75</v>
       </c>
       <c r="H183" t="str">
-        <v>2025-02-01</v>
+        <v>2025</v>
       </c>
       <c r="I183" t="str">
-        <v>2026-02-31</v>
+        <v>2026</v>
       </c>
       <c r="J183" t="str">
         <v>Notice</v>
@@ -6290,10 +6290,10 @@
         <v>1165.5</v>
       </c>
       <c r="H184" t="str">
-        <v>2025-03-01</v>
+        <v>2025</v>
       </c>
       <c r="I184" t="str">
-        <v>2026-03-31</v>
+        <v>2026</v>
       </c>
       <c r="J184" t="str">
         <v>Current</v>
@@ -6322,10 +6322,10 @@
         <v>1196.25</v>
       </c>
       <c r="H185" t="str">
-        <v>2025-04-01</v>
+        <v>2025</v>
       </c>
       <c r="I185" t="str">
-        <v>2026-04-31</v>
+        <v>2026</v>
       </c>
       <c r="J185" t="str">
         <v>Current</v>
@@ -6354,10 +6354,10 @@
         <v>1227</v>
       </c>
       <c r="H186" t="str">
-        <v>2025-05-01</v>
+        <v>2025</v>
       </c>
       <c r="I186" t="str">
-        <v>2026-05-31</v>
+        <v>2026</v>
       </c>
       <c r="J186" t="str">
         <v>Current</v>
@@ -6386,10 +6386,10 @@
         <v>1104</v>
       </c>
       <c r="H187" t="str">
-        <v>2025-01-01</v>
+        <v>2025</v>
       </c>
       <c r="I187" t="str">
-        <v>2026-01-31</v>
+        <v>2026</v>
       </c>
       <c r="J187" t="str">
         <v>Current</v>
@@ -6418,10 +6418,10 @@
         <v>1134.75</v>
       </c>
       <c r="H188" t="str">
-        <v>2025-02-01</v>
+        <v>2025</v>
       </c>
       <c r="I188" t="str">
-        <v>2026-02-31</v>
+        <v>2026</v>
       </c>
       <c r="J188" t="str">
         <v>Current</v>
@@ -6450,10 +6450,10 @@
         <v>1165.5</v>
       </c>
       <c r="H189" t="str">
-        <v>2025-03-01</v>
+        <v>2025</v>
       </c>
       <c r="I189" t="str">
-        <v>2026-03-31</v>
+        <v>2026</v>
       </c>
       <c r="J189" t="str">
         <v>Current</v>
@@ -6482,10 +6482,10 @@
         <v>1196.25</v>
       </c>
       <c r="H190" t="str">
-        <v>2025-04-01</v>
+        <v>2025</v>
       </c>
       <c r="I190" t="str">
-        <v>2026-04-31</v>
+        <v>2026</v>
       </c>
       <c r="J190" t="str">
         <v>Current</v>
@@ -6514,10 +6514,10 @@
         <v>1124.25</v>
       </c>
       <c r="H191" t="str">
-        <v>2025-02-01</v>
+        <v>2025</v>
       </c>
       <c r="I191" t="str">
-        <v>2026-02-31</v>
+        <v>2026</v>
       </c>
       <c r="J191" t="str">
         <v>Current</v>
@@ -6546,10 +6546,10 @@
         <v>1155</v>
       </c>
       <c r="H192" t="str">
-        <v>2025-03-01</v>
+        <v>2025</v>
       </c>
       <c r="I192" t="str">
-        <v>2026-03-31</v>
+        <v>2026</v>
       </c>
       <c r="J192" t="str">
         <v>Current</v>
@@ -6578,10 +6578,10 @@
         <v>1185.75</v>
       </c>
       <c r="H193" t="str">
-        <v>2025-04-01</v>
+        <v>2025</v>
       </c>
       <c r="I193" t="str">
-        <v>2026-04-31</v>
+        <v>2026</v>
       </c>
       <c r="J193" t="str">
         <v>Current</v>
@@ -6610,10 +6610,10 @@
         <v>1216.5</v>
       </c>
       <c r="H194" t="str">
-        <v>2025-05-01</v>
+        <v>2025</v>
       </c>
       <c r="I194" t="str">
-        <v>2026-05-31</v>
+        <v>2026</v>
       </c>
       <c r="J194" t="str">
         <v>Current</v>
@@ -6642,10 +6642,10 @@
         <v>1124.25</v>
       </c>
       <c r="H195" t="str">
-        <v>2025-02-01</v>
+        <v>2025</v>
       </c>
       <c r="I195" t="str">
-        <v>2026-02-31</v>
+        <v>2026</v>
       </c>
       <c r="J195" t="str">
         <v>Current</v>
@@ -6674,10 +6674,10 @@
         <v>1155</v>
       </c>
       <c r="H196" t="str">
-        <v>2025-03-01</v>
+        <v>2025</v>
       </c>
       <c r="I196" t="str">
-        <v>2026-03-31</v>
+        <v>2026</v>
       </c>
       <c r="J196" t="str">
         <v>Current</v>
@@ -6706,10 +6706,10 @@
         <v>1185.75</v>
       </c>
       <c r="H197" t="str">
-        <v>2025-04-01</v>
+        <v>2025</v>
       </c>
       <c r="I197" t="str">
-        <v>2026-04-31</v>
+        <v>2026</v>
       </c>
       <c r="J197" t="str">
         <v>Current</v>
@@ -6738,10 +6738,10 @@
         <v>1216.5</v>
       </c>
       <c r="H198" t="str">
-        <v>2025-05-01</v>
+        <v>2025</v>
       </c>
       <c r="I198" t="str">
-        <v>2026-05-31</v>
+        <v>2026</v>
       </c>
       <c r="J198" t="str">
         <v>Current</v>
@@ -6770,10 +6770,10 @@
         <v>1247.25</v>
       </c>
       <c r="H199" t="str">
-        <v>2025-06-01</v>
+        <v>2025</v>
       </c>
       <c r="I199" t="str">
-        <v>2026-06-31</v>
+        <v>2026</v>
       </c>
       <c r="J199" t="str">
         <v>Current</v>
@@ -6802,10 +6802,10 @@
         <v>1124.25</v>
       </c>
       <c r="H200" t="str">
-        <v>2025-02-01</v>
+        <v>2025</v>
       </c>
       <c r="I200" t="str">
-        <v>2026-02-31</v>
+        <v>2026</v>
       </c>
       <c r="J200" t="str">
         <v>Current</v>
@@ -6834,10 +6834,10 @@
         <v>1155</v>
       </c>
       <c r="H201" t="str">
-        <v>2025-03-01</v>
+        <v>2025</v>
       </c>
       <c r="I201" t="str">
-        <v>2026-03-31</v>
+        <v>2026</v>
       </c>
       <c r="J201" t="str">
         <v>Current</v>
@@ -6866,10 +6866,10 @@
         <v>1124.25</v>
       </c>
       <c r="H202" t="str">
-        <v>2025-02-01</v>
+        <v>2025</v>
       </c>
       <c r="I202" t="str">
-        <v>2026-02-31</v>
+        <v>2026</v>
       </c>
       <c r="J202" t="str">
         <v>Current</v>
@@ -6898,10 +6898,10 @@
         <v>1155</v>
       </c>
       <c r="H203" t="str">
-        <v>2025-03-01</v>
+        <v>2025</v>
       </c>
       <c r="I203" t="str">
-        <v>2026-03-31</v>
+        <v>2026</v>
       </c>
       <c r="J203" t="str">
         <v>Current</v>
@@ -6930,10 +6930,10 @@
         <v>1185.75</v>
       </c>
       <c r="H204" t="str">
-        <v>2025-04-01</v>
+        <v>2025</v>
       </c>
       <c r="I204" t="str">
-        <v>2026-04-31</v>
+        <v>2026</v>
       </c>
       <c r="J204" t="str">
         <v>Current</v>
@@ -6962,10 +6962,10 @@
         <v>1216.5</v>
       </c>
       <c r="H205" t="str">
-        <v>2025-05-01</v>
+        <v>2025</v>
       </c>
       <c r="I205" t="str">
-        <v>2026-05-31</v>
+        <v>2026</v>
       </c>
       <c r="J205" t="str">
         <v>Current</v>
@@ -6994,10 +6994,10 @@
         <v>1247.25</v>
       </c>
       <c r="H206" t="str">
-        <v>2025-06-01</v>
+        <v>2025</v>
       </c>
       <c r="I206" t="str">
-        <v>2026-06-31</v>
+        <v>2026</v>
       </c>
       <c r="J206" t="str">
         <v>Current</v>
@@ -7026,10 +7026,10 @@
         <v>1124.25</v>
       </c>
       <c r="H207" t="str">
-        <v>2025-02-01</v>
+        <v>2025</v>
       </c>
       <c r="I207" t="str">
-        <v>2026-02-31</v>
+        <v>2026</v>
       </c>
       <c r="J207" t="str">
         <v>Current</v>
@@ -7058,10 +7058,10 @@
         <v>1155</v>
       </c>
       <c r="H208" t="str">
-        <v>2025-03-01</v>
+        <v>2025</v>
       </c>
       <c r="I208" t="str">
-        <v>2026-03-31</v>
+        <v>2026</v>
       </c>
       <c r="J208" t="str">
         <v>Current</v>
@@ -7090,10 +7090,10 @@
         <v>1216.5</v>
       </c>
       <c r="H209" t="str">
-        <v>2025-05-01</v>
+        <v>2025</v>
       </c>
       <c r="I209" t="str">
-        <v>2026-05-31</v>
+        <v>2026</v>
       </c>
       <c r="J209" t="str">
         <v>Current</v>
@@ -7122,10 +7122,10 @@
         <v>1164.75</v>
       </c>
       <c r="H210" t="str">
-        <v>2025-04-01</v>
+        <v>2025</v>
       </c>
       <c r="I210" t="str">
-        <v>2026-04-31</v>
+        <v>2026</v>
       </c>
       <c r="J210" t="str">
         <v>Current</v>
@@ -7154,10 +7154,10 @@
         <v>1195.5</v>
       </c>
       <c r="H211" t="str">
-        <v>2025-05-01</v>
+        <v>2025</v>
       </c>
       <c r="I211" t="str">
-        <v>2026-05-31</v>
+        <v>2026</v>
       </c>
       <c r="J211" t="str">
         <v>Current</v>
@@ -7186,10 +7186,10 @@
         <v>1257</v>
       </c>
       <c r="H212" t="str">
-        <v>2025-07-01</v>
+        <v>2025</v>
       </c>
       <c r="I212" t="str">
-        <v>2026-07-31</v>
+        <v>2026</v>
       </c>
       <c r="J212" t="str">
         <v>Current</v>
@@ -7218,10 +7218,10 @@
         <v>1164.75</v>
       </c>
       <c r="H213" t="str">
-        <v>2025-04-01</v>
+        <v>2025</v>
       </c>
       <c r="I213" t="str">
-        <v>2026-04-31</v>
+        <v>2026</v>
       </c>
       <c r="J213" t="str">
         <v>Current</v>
@@ -7250,10 +7250,10 @@
         <v>1195.5</v>
       </c>
       <c r="H214" t="str">
-        <v>2025-05-01</v>
+        <v>2025</v>
       </c>
       <c r="I214" t="str">
-        <v>2026-05-31</v>
+        <v>2026</v>
       </c>
       <c r="J214" t="str">
         <v>Notice</v>
@@ -7282,10 +7282,10 @@
         <v>1226.25</v>
       </c>
       <c r="H215" t="str">
-        <v>2025-06-01</v>
+        <v>2025</v>
       </c>
       <c r="I215" t="str">
-        <v>2026-06-31</v>
+        <v>2026</v>
       </c>
       <c r="J215" t="str">
         <v>Current</v>
@@ -7314,10 +7314,10 @@
         <v>1257</v>
       </c>
       <c r="H216" t="str">
-        <v>2025-07-01</v>
+        <v>2025</v>
       </c>
       <c r="I216" t="str">
-        <v>2026-07-31</v>
+        <v>2026</v>
       </c>
       <c r="J216" t="str">
         <v>Current</v>
@@ -7346,10 +7346,10 @@
         <v>1287.75</v>
       </c>
       <c r="H217" t="str">
-        <v>2025-08-01</v>
+        <v>2025</v>
       </c>
       <c r="I217" t="str">
-        <v>2026-08-31</v>
+        <v>2026</v>
       </c>
       <c r="J217" t="str">
         <v>Current</v>
@@ -7378,10 +7378,10 @@
         <v>1164.75</v>
       </c>
       <c r="H218" t="str">
-        <v>2025-04-01</v>
+        <v>2025</v>
       </c>
       <c r="I218" t="str">
-        <v>2026-04-31</v>
+        <v>2026</v>
       </c>
       <c r="J218" t="str">
         <v>Current</v>
@@ -7410,10 +7410,10 @@
         <v>1195.5</v>
       </c>
       <c r="H219" t="str">
-        <v>2025-05-01</v>
+        <v>2025</v>
       </c>
       <c r="I219" t="str">
-        <v>2026-05-31</v>
+        <v>2026</v>
       </c>
       <c r="J219" t="str">
         <v>Current</v>
@@ -7442,10 +7442,10 @@
         <v>1226.25</v>
       </c>
       <c r="H220" t="str">
-        <v>2025-06-01</v>
+        <v>2025</v>
       </c>
       <c r="I220" t="str">
-        <v>2026-06-31</v>
+        <v>2026</v>
       </c>
       <c r="J220" t="str">
         <v>Current</v>
@@ -7474,10 +7474,10 @@
         <v>1164.75</v>
       </c>
       <c r="H221" t="str">
-        <v>2025-04-01</v>
+        <v>2025</v>
       </c>
       <c r="I221" t="str">
-        <v>2026-04-31</v>
+        <v>2026</v>
       </c>
       <c r="J221" t="str">
         <v>Current</v>
@@ -7506,10 +7506,10 @@
         <v>1195.5</v>
       </c>
       <c r="H222" t="str">
-        <v>2025-05-01</v>
+        <v>2025</v>
       </c>
       <c r="I222" t="str">
-        <v>2026-05-31</v>
+        <v>2026</v>
       </c>
       <c r="J222" t="str">
         <v>Current</v>
@@ -7538,10 +7538,10 @@
         <v>1164.75</v>
       </c>
       <c r="H223" t="str">
-        <v>2025-04-01</v>
+        <v>2025</v>
       </c>
       <c r="I223" t="str">
-        <v>2026-04-31</v>
+        <v>2026</v>
       </c>
       <c r="J223" t="str">
         <v>Future</v>
@@ -7570,10 +7570,10 @@
         <v>1195.5</v>
       </c>
       <c r="H224" t="str">
-        <v>2025-05-01</v>
+        <v>2025</v>
       </c>
       <c r="I224" t="str">
-        <v>2026-05-31</v>
+        <v>2026</v>
       </c>
       <c r="J224" t="str">
         <v>Future</v>
@@ -7602,10 +7602,10 @@
         <v>1226.25</v>
       </c>
       <c r="H225" t="str">
-        <v>2025-06-01</v>
+        <v>2025</v>
       </c>
       <c r="I225" t="str">
-        <v>2026-06-31</v>
+        <v>2026</v>
       </c>
       <c r="J225" t="str">
         <v>Future</v>
@@ -7634,10 +7634,10 @@
         <v>1257</v>
       </c>
       <c r="H226" t="str">
-        <v>2025-07-01</v>
+        <v>2025</v>
       </c>
       <c r="I226" t="str">
-        <v>2026-07-31</v>
+        <v>2026</v>
       </c>
       <c r="J226" t="str">
         <v>Future</v>
@@ -7666,10 +7666,10 @@
         <v>1287.75</v>
       </c>
       <c r="H227" t="str">
-        <v>2025-08-01</v>
+        <v>2025</v>
       </c>
       <c r="I227" t="str">
-        <v>2026-08-31</v>
+        <v>2026</v>
       </c>
       <c r="J227" t="str">
         <v>Future</v>
@@ -7698,10 +7698,10 @@
         <v>1164.75</v>
       </c>
       <c r="H228" t="str">
-        <v>2025-04-01</v>
+        <v>2025</v>
       </c>
       <c r="I228" t="str">
-        <v>2026-04-31</v>
+        <v>2026</v>
       </c>
       <c r="J228" t="str">
         <v>Current</v>
@@ -7730,10 +7730,10 @@
         <v>1195.5</v>
       </c>
       <c r="H229" t="str">
-        <v>2025-05-01</v>
+        <v>2025</v>
       </c>
       <c r="I229" t="str">
-        <v>2026-05-31</v>
+        <v>2026</v>
       </c>
       <c r="J229" t="str">
         <v>Notice</v>
@@ -7762,10 +7762,10 @@
         <v>1226.25</v>
       </c>
       <c r="H230" t="str">
-        <v>2025-06-01</v>
+        <v>2025</v>
       </c>
       <c r="I230" t="str">
-        <v>2026-06-31</v>
+        <v>2026</v>
       </c>
       <c r="J230" t="str">
         <v>Current</v>
@@ -7794,10 +7794,10 @@
         <v>1257</v>
       </c>
       <c r="H231" t="str">
-        <v>2025-07-01</v>
+        <v>2025</v>
       </c>
       <c r="I231" t="str">
-        <v>2026-07-31</v>
+        <v>2026</v>
       </c>
       <c r="J231" t="str">
         <v>Current</v>
@@ -7826,10 +7826,10 @@
         <v>1185</v>
       </c>
       <c r="H232" t="str">
-        <v>2025-05-01</v>
+        <v>2025</v>
       </c>
       <c r="I232" t="str">
-        <v>2026-05-31</v>
+        <v>2026</v>
       </c>
       <c r="J232" t="str">
         <v>Current</v>
@@ -7858,10 +7858,10 @@
         <v>1215.75</v>
       </c>
       <c r="H233" t="str">
-        <v>2025-06-01</v>
+        <v>2025</v>
       </c>
       <c r="I233" t="str">
-        <v>2026-06-31</v>
+        <v>2026</v>
       </c>
       <c r="J233" t="str">
         <v>Notice</v>
@@ -7890,10 +7890,10 @@
         <v>1246.5</v>
       </c>
       <c r="H234" t="str">
-        <v>2025-07-01</v>
+        <v>2025</v>
       </c>
       <c r="I234" t="str">
-        <v>2026-07-31</v>
+        <v>2026</v>
       </c>
       <c r="J234" t="str">
         <v>Current</v>
@@ -7922,10 +7922,10 @@
         <v>1277.25</v>
       </c>
       <c r="H235" t="str">
-        <v>2025-08-01</v>
+        <v>2025</v>
       </c>
       <c r="I235" t="str">
-        <v>2026-08-31</v>
+        <v>2026</v>
       </c>
       <c r="J235" t="str">
         <v>Current</v>
@@ -7954,10 +7954,10 @@
         <v>1185</v>
       </c>
       <c r="H236" t="str">
-        <v>2025-05-01</v>
+        <v>2025</v>
       </c>
       <c r="I236" t="str">
-        <v>2026-05-31</v>
+        <v>2026</v>
       </c>
       <c r="J236" t="str">
         <v>Current</v>
@@ -7986,10 +7986,10 @@
         <v>1215.75</v>
       </c>
       <c r="H237" t="str">
-        <v>2025-06-01</v>
+        <v>2025</v>
       </c>
       <c r="I237" t="str">
-        <v>2026-06-31</v>
+        <v>2026</v>
       </c>
       <c r="J237" t="str">
         <v>Current</v>
@@ -8018,10 +8018,10 @@
         <v>1246.5</v>
       </c>
       <c r="H238" t="str">
-        <v>2025-07-01</v>
+        <v>2025</v>
       </c>
       <c r="I238" t="str">
-        <v>2026-07-31</v>
+        <v>2026</v>
       </c>
       <c r="J238" t="str">
         <v>Current</v>
@@ -8050,10 +8050,10 @@
         <v>1277.25</v>
       </c>
       <c r="H239" t="str">
-        <v>2025-08-01</v>
+        <v>2025</v>
       </c>
       <c r="I239" t="str">
-        <v>2026-08-31</v>
+        <v>2026</v>
       </c>
       <c r="J239" t="str">
         <v>Current</v>
@@ -8082,10 +8082,10 @@
         <v>1308</v>
       </c>
       <c r="H240" t="str">
-        <v>2025-09-01</v>
+        <v>2025</v>
       </c>
       <c r="I240" t="str">
-        <v>2026-09-31</v>
+        <v>2026</v>
       </c>
       <c r="J240" t="str">
         <v>Current</v>
@@ -8114,10 +8114,10 @@
         <v>1185</v>
       </c>
       <c r="H241" t="str">
-        <v>2025-05-01</v>
+        <v>2025</v>
       </c>
       <c r="I241" t="str">
-        <v>2026-05-31</v>
+        <v>2026</v>
       </c>
       <c r="J241" t="str">
         <v>Current</v>
@@ -8146,10 +8146,10 @@
         <v>1215.75</v>
       </c>
       <c r="H242" t="str">
-        <v>2025-06-01</v>
+        <v>2025</v>
       </c>
       <c r="I242" t="str">
-        <v>2026-06-31</v>
+        <v>2026</v>
       </c>
       <c r="J242" t="str">
         <v>Current</v>
@@ -8178,10 +8178,10 @@
         <v>1185</v>
       </c>
       <c r="H243" t="str">
-        <v>2025-05-01</v>
+        <v>2025</v>
       </c>
       <c r="I243" t="str">
-        <v>2026-05-31</v>
+        <v>2026</v>
       </c>
       <c r="J243" t="str">
         <v>Current</v>
@@ -8210,10 +8210,10 @@
         <v>1215.75</v>
       </c>
       <c r="H244" t="str">
-        <v>2025-06-01</v>
+        <v>2025</v>
       </c>
       <c r="I244" t="str">
-        <v>2026-06-31</v>
+        <v>2026</v>
       </c>
       <c r="J244" t="str">
         <v>Current</v>
@@ -8242,10 +8242,10 @@
         <v>1246.5</v>
       </c>
       <c r="H245" t="str">
-        <v>2025-07-01</v>
+        <v>2025</v>
       </c>
       <c r="I245" t="str">
-        <v>2026-07-31</v>
+        <v>2026</v>
       </c>
       <c r="J245" t="str">
         <v>Current</v>
@@ -8274,10 +8274,10 @@
         <v>1185</v>
       </c>
       <c r="H246" t="str">
-        <v>2025-05-01</v>
+        <v>2025</v>
       </c>
       <c r="I246" t="str">
-        <v>2026-05-31</v>
+        <v>2026</v>
       </c>
       <c r="J246" t="str">
         <v>Current</v>
@@ -8306,10 +8306,10 @@
         <v>1215.75</v>
       </c>
       <c r="H247" t="str">
-        <v>2025-06-01</v>
+        <v>2025</v>
       </c>
       <c r="I247" t="str">
-        <v>2026-06-31</v>
+        <v>2026</v>
       </c>
       <c r="J247" t="str">
         <v>Notice</v>
@@ -8338,10 +8338,10 @@
         <v>1246.5</v>
       </c>
       <c r="H248" t="str">
-        <v>2025-07-01</v>
+        <v>2025</v>
       </c>
       <c r="I248" t="str">
-        <v>2026-07-31</v>
+        <v>2026</v>
       </c>
       <c r="J248" t="str">
         <v>Current</v>
@@ -8370,10 +8370,10 @@
         <v>1277.25</v>
       </c>
       <c r="H249" t="str">
-        <v>2025-08-01</v>
+        <v>2025</v>
       </c>
       <c r="I249" t="str">
-        <v>2026-08-31</v>
+        <v>2026</v>
       </c>
       <c r="J249" t="str">
         <v>Current</v>
@@ -8402,10 +8402,10 @@
         <v>1308</v>
       </c>
       <c r="H250" t="str">
-        <v>2025-09-01</v>
+        <v>2025</v>
       </c>
       <c r="I250" t="str">
-        <v>2026-09-31</v>
+        <v>2026</v>
       </c>
       <c r="J250" t="str">
         <v>Current</v>
@@ -8434,10 +8434,10 @@
         <v>1185</v>
       </c>
       <c r="H251" t="str">
-        <v>2025-05-01</v>
+        <v>2025</v>
       </c>
       <c r="I251" t="str">
-        <v>2026-05-31</v>
+        <v>2026</v>
       </c>
       <c r="J251" t="str">
         <v>Current</v>
@@ -8466,10 +8466,10 @@
         <v>1215.75</v>
       </c>
       <c r="H252" t="str">
-        <v>2025-06-01</v>
+        <v>2025</v>
       </c>
       <c r="I252" t="str">
-        <v>2026-06-31</v>
+        <v>2026</v>
       </c>
       <c r="J252" t="str">
         <v>Current</v>
@@ -8498,10 +8498,10 @@
         <v>1277.25</v>
       </c>
       <c r="H253" t="str">
-        <v>2025-08-01</v>
+        <v>2025</v>
       </c>
       <c r="I253" t="str">
-        <v>2026-08-31</v>
+        <v>2026</v>
       </c>
       <c r="J253" t="str">
         <v>Current</v>
@@ -8530,10 +8530,10 @@
         <v>1205.25</v>
       </c>
       <c r="H254" t="str">
-        <v>2025-06-01</v>
+        <v>2025</v>
       </c>
       <c r="I254" t="str">
-        <v>2026-06-31</v>
+        <v>2026</v>
       </c>
       <c r="J254" t="str">
         <v>Current</v>
@@ -8562,10 +8562,10 @@
         <v>1236</v>
       </c>
       <c r="H255" t="str">
-        <v>2025-07-01</v>
+        <v>2025</v>
       </c>
       <c r="I255" t="str">
-        <v>2026-07-31</v>
+        <v>2026</v>
       </c>
       <c r="J255" t="str">
         <v>Current</v>
@@ -8594,10 +8594,10 @@
         <v>1266.75</v>
       </c>
       <c r="H256" t="str">
-        <v>2025-08-01</v>
+        <v>2025</v>
       </c>
       <c r="I256" t="str">
-        <v>2026-08-31</v>
+        <v>2026</v>
       </c>
       <c r="J256" t="str">
         <v>Current</v>
@@ -8626,10 +8626,10 @@
         <v>1297.5</v>
       </c>
       <c r="H257" t="str">
-        <v>2025-09-01</v>
+        <v>2025</v>
       </c>
       <c r="I257" t="str">
-        <v>2026-09-31</v>
+        <v>2026</v>
       </c>
       <c r="J257" t="str">
         <v>Current</v>
@@ -8658,10 +8658,10 @@
         <v>1205.25</v>
       </c>
       <c r="H258" t="str">
-        <v>2025-06-01</v>
+        <v>2025</v>
       </c>
       <c r="I258" t="str">
-        <v>2026-06-31</v>
+        <v>2026</v>
       </c>
       <c r="J258" t="str">
         <v>Current</v>
@@ -8690,10 +8690,10 @@
         <v>1236</v>
       </c>
       <c r="H259" t="str">
-        <v>2025-07-01</v>
+        <v>2025</v>
       </c>
       <c r="I259" t="str">
-        <v>2026-07-31</v>
+        <v>2026</v>
       </c>
       <c r="J259" t="str">
         <v>Current</v>
@@ -8722,10 +8722,10 @@
         <v>1297.5</v>
       </c>
       <c r="H260" t="str">
-        <v>2025-09-01</v>
+        <v>2025</v>
       </c>
       <c r="I260" t="str">
-        <v>2026-09-31</v>
+        <v>2026</v>
       </c>
       <c r="J260" t="str">
         <v>Current</v>
@@ -8754,10 +8754,10 @@
         <v>1328.25</v>
       </c>
       <c r="H261" t="str">
-        <v>2025-10-01</v>
+        <v>2025</v>
       </c>
       <c r="I261" t="str">
-        <v>2026-10-31</v>
+        <v>2026</v>
       </c>
       <c r="J261" t="str">
         <v>Current</v>
@@ -8786,10 +8786,10 @@
         <v>1205.25</v>
       </c>
       <c r="H262" t="str">
-        <v>2025-06-01</v>
+        <v>2025</v>
       </c>
       <c r="I262" t="str">
-        <v>2026-06-31</v>
+        <v>2026</v>
       </c>
       <c r="J262" t="str">
         <v>Current</v>
@@ -8818,10 +8818,10 @@
         <v>1236</v>
       </c>
       <c r="H263" t="str">
-        <v>2025-07-01</v>
+        <v>2025</v>
       </c>
       <c r="I263" t="str">
-        <v>2026-07-31</v>
+        <v>2026</v>
       </c>
       <c r="J263" t="str">
         <v>Current</v>
@@ -8850,10 +8850,10 @@
         <v>1266.75</v>
       </c>
       <c r="H264" t="str">
-        <v>2025-08-01</v>
+        <v>2025</v>
       </c>
       <c r="I264" t="str">
-        <v>2026-08-31</v>
+        <v>2026</v>
       </c>
       <c r="J264" t="str">
         <v>Current</v>
@@ -8882,10 +8882,10 @@
         <v>1205.25</v>
       </c>
       <c r="H265" t="str">
-        <v>2025-06-01</v>
+        <v>2025</v>
       </c>
       <c r="I265" t="str">
-        <v>2026-06-31</v>
+        <v>2026</v>
       </c>
       <c r="J265" t="str">
         <v>Current</v>
@@ -8914,10 +8914,10 @@
         <v>1236</v>
       </c>
       <c r="H266" t="str">
-        <v>2025-07-01</v>
+        <v>2025</v>
       </c>
       <c r="I266" t="str">
-        <v>2026-07-31</v>
+        <v>2026</v>
       </c>
       <c r="J266" t="str">
         <v>Notice</v>
@@ -8946,10 +8946,10 @@
         <v>1266.75</v>
       </c>
       <c r="H267" t="str">
-        <v>2025-08-01</v>
+        <v>2025</v>
       </c>
       <c r="I267" t="str">
-        <v>2026-08-31</v>
+        <v>2026</v>
       </c>
       <c r="J267" t="str">
         <v>Current</v>
@@ -8978,10 +8978,10 @@
         <v>1205.25</v>
       </c>
       <c r="H268" t="str">
-        <v>2025-06-01</v>
+        <v>2025</v>
       </c>
       <c r="I268" t="str">
-        <v>2026-06-31</v>
+        <v>2026</v>
       </c>
       <c r="J268" t="str">
         <v>Current</v>
@@ -9010,10 +9010,10 @@
         <v>1236</v>
       </c>
       <c r="H269" t="str">
-        <v>2025-07-01</v>
+        <v>2025</v>
       </c>
       <c r="I269" t="str">
-        <v>2026-07-31</v>
+        <v>2026</v>
       </c>
       <c r="J269" t="str">
         <v>Current</v>
@@ -9042,10 +9042,10 @@
         <v>1297.5</v>
       </c>
       <c r="H270" t="str">
-        <v>2025-09-01</v>
+        <v>2025</v>
       </c>
       <c r="I270" t="str">
-        <v>2026-09-31</v>
+        <v>2026</v>
       </c>
       <c r="J270" t="str">
         <v>Current</v>
@@ -9074,10 +9074,10 @@
         <v>1328.25</v>
       </c>
       <c r="H271" t="str">
-        <v>2025-10-01</v>
+        <v>2025</v>
       </c>
       <c r="I271" t="str">
-        <v>2026-10-31</v>
+        <v>2026</v>
       </c>
       <c r="J271" t="str">
         <v>Current</v>
@@ -9106,10 +9106,10 @@
         <v>1205.25</v>
       </c>
       <c r="H272" t="str">
-        <v>2025-06-01</v>
+        <v>2025</v>
       </c>
       <c r="I272" t="str">
-        <v>2026-06-31</v>
+        <v>2026</v>
       </c>
       <c r="J272" t="str">
         <v>Current</v>
@@ -9138,10 +9138,10 @@
         <v>1236</v>
       </c>
       <c r="H273" t="str">
-        <v>2025-07-01</v>
+        <v>2025</v>
       </c>
       <c r="I273" t="str">
-        <v>2026-07-31</v>
+        <v>2026</v>
       </c>
       <c r="J273" t="str">
         <v>Current</v>
@@ -9170,10 +9170,10 @@
         <v>1266.75</v>
       </c>
       <c r="H274" t="str">
-        <v>2025-08-01</v>
+        <v>2025</v>
       </c>
       <c r="I274" t="str">
-        <v>2026-08-31</v>
+        <v>2026</v>
       </c>
       <c r="J274" t="str">
         <v>Current</v>
@@ -9202,10 +9202,10 @@
         <v>1297.5</v>
       </c>
       <c r="H275" t="str">
-        <v>2025-09-01</v>
+        <v>2025</v>
       </c>
       <c r="I275" t="str">
-        <v>2026-09-31</v>
+        <v>2026</v>
       </c>
       <c r="J275" t="str">
         <v>Current</v>
@@ -9234,10 +9234,10 @@
         <v>1225.5</v>
       </c>
       <c r="H276" t="str">
-        <v>2025-07-01</v>
+        <v>2025</v>
       </c>
       <c r="I276" t="str">
-        <v>2026-07-31</v>
+        <v>2026</v>
       </c>
       <c r="J276" t="str">
         <v>Current</v>
@@ -9266,10 +9266,10 @@
         <v>1256.25</v>
       </c>
       <c r="H277" t="str">
-        <v>2025-08-01</v>
+        <v>2025</v>
       </c>
       <c r="I277" t="str">
-        <v>2026-08-31</v>
+        <v>2026</v>
       </c>
       <c r="J277" t="str">
         <v>Current</v>
@@ -9298,10 +9298,10 @@
         <v>1317.75</v>
       </c>
       <c r="H278" t="str">
-        <v>2025-10-01</v>
+        <v>2025</v>
       </c>
       <c r="I278" t="str">
-        <v>2026-10-31</v>
+        <v>2026</v>
       </c>
       <c r="J278" t="str">
         <v>Current</v>
@@ -9330,10 +9330,10 @@
         <v>1225.5</v>
       </c>
       <c r="H279" t="str">
-        <v>2025-07-01</v>
+        <v>2025</v>
       </c>
       <c r="I279" t="str">
-        <v>2026-07-31</v>
+        <v>2026</v>
       </c>
       <c r="J279" t="str">
         <v>Current</v>
@@ -9362,10 +9362,10 @@
         <v>1256.25</v>
       </c>
       <c r="H280" t="str">
-        <v>2025-08-01</v>
+        <v>2025</v>
       </c>
       <c r="I280" t="str">
-        <v>2026-08-31</v>
+        <v>2026</v>
       </c>
       <c r="J280" t="str">
         <v>Current</v>
@@ -9394,10 +9394,10 @@
         <v>1287</v>
       </c>
       <c r="H281" t="str">
-        <v>2025-09-01</v>
+        <v>2025</v>
       </c>
       <c r="I281" t="str">
-        <v>2026-09-31</v>
+        <v>2026</v>
       </c>
       <c r="J281" t="str">
         <v>Current</v>
@@ -9426,10 +9426,10 @@
         <v>1317.75</v>
       </c>
       <c r="H282" t="str">
-        <v>2025-10-01</v>
+        <v>2025</v>
       </c>
       <c r="I282" t="str">
-        <v>2026-10-31</v>
+        <v>2026</v>
       </c>
       <c r="J282" t="str">
         <v>Current</v>
@@ -9458,10 +9458,10 @@
         <v>1348.5</v>
       </c>
       <c r="H283" t="str">
-        <v>2025-11-01</v>
+        <v>2025</v>
       </c>
       <c r="I283" t="str">
-        <v>2026-11-31</v>
+        <v>2026</v>
       </c>
       <c r="J283" t="str">
         <v>Current</v>
@@ -9490,10 +9490,10 @@
         <v>1225.5</v>
       </c>
       <c r="H284" t="str">
-        <v>2025-07-01</v>
+        <v>2025</v>
       </c>
       <c r="I284" t="str">
-        <v>2026-07-31</v>
+        <v>2026</v>
       </c>
       <c r="J284" t="str">
         <v>Current</v>
@@ -9522,10 +9522,10 @@
         <v>1256.25</v>
       </c>
       <c r="H285" t="str">
-        <v>2025-08-01</v>
+        <v>2025</v>
       </c>
       <c r="I285" t="str">
-        <v>2026-08-31</v>
+        <v>2026</v>
       </c>
       <c r="J285" t="str">
         <v>Current</v>
@@ -9554,10 +9554,10 @@
         <v>1225.5</v>
       </c>
       <c r="H286" t="str">
-        <v>2025-07-01</v>
+        <v>2025</v>
       </c>
       <c r="I286" t="str">
-        <v>2026-07-31</v>
+        <v>2026</v>
       </c>
       <c r="J286" t="str">
         <v>Current</v>
@@ -9586,10 +9586,10 @@
         <v>1256.25</v>
       </c>
       <c r="H287" t="str">
-        <v>2025-08-01</v>
+        <v>2025</v>
       </c>
       <c r="I287" t="str">
-        <v>2026-08-31</v>
+        <v>2026</v>
       </c>
       <c r="J287" t="str">
         <v>Current</v>
@@ -9618,10 +9618,10 @@
         <v>1287</v>
       </c>
       <c r="H288" t="str">
-        <v>2025-09-01</v>
+        <v>2025</v>
       </c>
       <c r="I288" t="str">
-        <v>2026-09-31</v>
+        <v>2026</v>
       </c>
       <c r="J288" t="str">
         <v>Current</v>
@@ -9650,10 +9650,10 @@
         <v>1317.75</v>
       </c>
       <c r="H289" t="str">
-        <v>2025-10-01</v>
+        <v>2025</v>
       </c>
       <c r="I289" t="str">
-        <v>2026-10-31</v>
+        <v>2026</v>
       </c>
       <c r="J289" t="str">
         <v>Current</v>
@@ -9682,10 +9682,10 @@
         <v>1348.5</v>
       </c>
       <c r="H290" t="str">
-        <v>2025-11-01</v>
+        <v>2025</v>
       </c>
       <c r="I290" t="str">
-        <v>2026-11-31</v>
+        <v>2026</v>
       </c>
       <c r="J290" t="str">
         <v>Current</v>
@@ -9714,10 +9714,10 @@
         <v>1225.5</v>
       </c>
       <c r="H291" t="str">
-        <v>2025-07-01</v>
+        <v>2025</v>
       </c>
       <c r="I291" t="str">
-        <v>2026-07-31</v>
+        <v>2026</v>
       </c>
       <c r="J291" t="str">
         <v>Current</v>
@@ -9746,10 +9746,10 @@
         <v>1256.25</v>
       </c>
       <c r="H292" t="str">
-        <v>2025-08-01</v>
+        <v>2025</v>
       </c>
       <c r="I292" t="str">
-        <v>2026-08-31</v>
+        <v>2026</v>
       </c>
       <c r="J292" t="str">
         <v>Current</v>
@@ -9778,10 +9778,10 @@
         <v>1287</v>
       </c>
       <c r="H293" t="str">
-        <v>2025-09-01</v>
+        <v>2025</v>
       </c>
       <c r="I293" t="str">
-        <v>2026-09-31</v>
+        <v>2026</v>
       </c>
       <c r="J293" t="str">
         <v>Current</v>
@@ -9810,10 +9810,10 @@
         <v>1317.75</v>
       </c>
       <c r="H294" t="str">
-        <v>2025-10-01</v>
+        <v>2025</v>
       </c>
       <c r="I294" t="str">
-        <v>2026-10-31</v>
+        <v>2026</v>
       </c>
       <c r="J294" t="str">
         <v>Current</v>
@@ -9842,10 +9842,10 @@
         <v>1245.75</v>
       </c>
       <c r="H295" t="str">
-        <v>2025-08-01</v>
+        <v>2025</v>
       </c>
       <c r="I295" t="str">
-        <v>2026-08-31</v>
+        <v>2026</v>
       </c>
       <c r="J295" t="str">
         <v>Current</v>
@@ -9874,10 +9874,10 @@
         <v>1276.5</v>
       </c>
       <c r="H296" t="str">
-        <v>2025-09-01</v>
+        <v>2025</v>
       </c>
       <c r="I296" t="str">
-        <v>2026-09-31</v>
+        <v>2026</v>
       </c>
       <c r="J296" t="str">
         <v>Current</v>
@@ -9906,10 +9906,10 @@
         <v>1307.25</v>
       </c>
       <c r="H297" t="str">
-        <v>2025-10-01</v>
+        <v>2025</v>
       </c>
       <c r="I297" t="str">
-        <v>2026-10-31</v>
+        <v>2026</v>
       </c>
       <c r="J297" t="str">
         <v>Current</v>
@@ -9938,10 +9938,10 @@
         <v>1338</v>
       </c>
       <c r="H298" t="str">
-        <v>2025-11-01</v>
+        <v>2025</v>
       </c>
       <c r="I298" t="str">
-        <v>2026-11-31</v>
+        <v>2026</v>
       </c>
       <c r="J298" t="str">
         <v>Current</v>
@@ -9970,10 +9970,10 @@
         <v>1245.75</v>
       </c>
       <c r="H299" t="str">
-        <v>2025-08-01</v>
+        <v>2025</v>
       </c>
       <c r="I299" t="str">
-        <v>2026-08-31</v>
+        <v>2026</v>
       </c>
       <c r="J299" t="str">
         <v>Current</v>
@@ -10002,10 +10002,10 @@
         <v>1276.5</v>
       </c>
       <c r="H300" t="str">
-        <v>2025-09-01</v>
+        <v>2025</v>
       </c>
       <c r="I300" t="str">
-        <v>2026-09-31</v>
+        <v>2026</v>
       </c>
       <c r="J300" t="str">
         <v>Notice</v>
@@ -10034,10 +10034,10 @@
         <v>1307.25</v>
       </c>
       <c r="H301" t="str">
-        <v>2025-10-01</v>
+        <v>2025</v>
       </c>
       <c r="I301" t="str">
-        <v>2026-10-31</v>
+        <v>2026</v>
       </c>
       <c r="J301" t="str">
         <v>Current</v>
@@ -10066,10 +10066,10 @@
         <v>1338</v>
       </c>
       <c r="H302" t="str">
-        <v>2025-11-01</v>
+        <v>2025</v>
       </c>
       <c r="I302" t="str">
-        <v>2026-11-31</v>
+        <v>2026</v>
       </c>
       <c r="J302" t="str">
         <v>Current</v>
@@ -10098,10 +10098,10 @@
         <v>1368.75</v>
       </c>
       <c r="H303" t="str">
-        <v>2025-12-01</v>
+        <v>2025</v>
       </c>
       <c r="I303" t="str">
-        <v>2026-12-31</v>
+        <v>2026</v>
       </c>
       <c r="J303" t="str">
         <v>Current</v>
@@ -10130,10 +10130,10 @@
         <v>1245.75</v>
       </c>
       <c r="H304" t="str">
-        <v>2025-08-01</v>
+        <v>2025</v>
       </c>
       <c r="I304" t="str">
-        <v>2026-08-31</v>
+        <v>2026</v>
       </c>
       <c r="J304" t="str">
         <v>Current</v>
@@ -10162,10 +10162,10 @@
         <v>1276.5</v>
       </c>
       <c r="H305" t="str">
-        <v>2025-09-01</v>
+        <v>2025</v>
       </c>
       <c r="I305" t="str">
-        <v>2026-09-31</v>
+        <v>2026</v>
       </c>
       <c r="J305" t="str">
         <v>Current</v>
@@ -10194,10 +10194,10 @@
         <v>1245.75</v>
       </c>
       <c r="H306" t="str">
-        <v>2025-08-01</v>
+        <v>2025</v>
       </c>
       <c r="I306" t="str">
-        <v>2026-08-31</v>
+        <v>2026</v>
       </c>
       <c r="J306" t="str">
         <v>Current</v>
@@ -10226,10 +10226,10 @@
         <v>1276.5</v>
       </c>
       <c r="H307" t="str">
-        <v>2025-09-01</v>
+        <v>2025</v>
       </c>
       <c r="I307" t="str">
-        <v>2026-09-31</v>
+        <v>2026</v>
       </c>
       <c r="J307" t="str">
         <v>Current</v>
@@ -10258,10 +10258,10 @@
         <v>1307.25</v>
       </c>
       <c r="H308" t="str">
-        <v>2025-10-01</v>
+        <v>2025</v>
       </c>
       <c r="I308" t="str">
-        <v>2026-10-31</v>
+        <v>2026</v>
       </c>
       <c r="J308" t="str">
         <v>Current</v>
@@ -10290,10 +10290,10 @@
         <v>1245.75</v>
       </c>
       <c r="H309" t="str">
-        <v>2025-08-01</v>
+        <v>2025</v>
       </c>
       <c r="I309" t="str">
-        <v>2026-08-31</v>
+        <v>2026</v>
       </c>
       <c r="J309" t="str">
         <v>Current</v>
@@ -10322,10 +10322,10 @@
         <v>1276.5</v>
       </c>
       <c r="H310" t="str">
-        <v>2025-09-01</v>
+        <v>2025</v>
       </c>
       <c r="I310" t="str">
-        <v>2026-09-31</v>
+        <v>2026</v>
       </c>
       <c r="J310" t="str">
         <v>Current</v>
@@ -10354,10 +10354,10 @@
         <v>1307.25</v>
       </c>
       <c r="H311" t="str">
-        <v>2025-10-01</v>
+        <v>2025</v>
       </c>
       <c r="I311" t="str">
-        <v>2026-10-31</v>
+        <v>2026</v>
       </c>
       <c r="J311" t="str">
         <v>Current</v>
@@ -10386,10 +10386,10 @@
         <v>1338</v>
       </c>
       <c r="H312" t="str">
-        <v>2025-11-01</v>
+        <v>2025</v>
       </c>
       <c r="I312" t="str">
-        <v>2026-11-31</v>
+        <v>2026</v>
       </c>
       <c r="J312" t="str">
         <v>Current</v>
@@ -10418,10 +10418,10 @@
         <v>1368.75</v>
       </c>
       <c r="H313" t="str">
-        <v>2025-12-01</v>
+        <v>2025</v>
       </c>
       <c r="I313" t="str">
-        <v>2026-12-31</v>
+        <v>2026</v>
       </c>
       <c r="J313" t="str">
         <v>Current</v>
@@ -10450,10 +10450,10 @@
         <v>1245.75</v>
       </c>
       <c r="H314" t="str">
-        <v>2025-08-01</v>
+        <v>2025</v>
       </c>
       <c r="I314" t="str">
-        <v>2026-08-31</v>
+        <v>2026</v>
       </c>
       <c r="J314" t="str">
         <v>Current</v>
@@ -10482,10 +10482,10 @@
         <v>1276.5</v>
       </c>
       <c r="H315" t="str">
-        <v>2025-09-01</v>
+        <v>2025</v>
       </c>
       <c r="I315" t="str">
-        <v>2026-09-31</v>
+        <v>2026</v>
       </c>
       <c r="J315" t="str">
         <v>Notice</v>
@@ -10514,10 +10514,10 @@
         <v>1338</v>
       </c>
       <c r="H316" t="str">
-        <v>2025-11-01</v>
+        <v>2025</v>
       </c>
       <c r="I316" t="str">
-        <v>2026-11-31</v>
+        <v>2026</v>
       </c>
       <c r="J316" t="str">
         <v>Current</v>
@@ -10546,10 +10546,10 @@
         <v>1266</v>
       </c>
       <c r="H317" t="str">
-        <v>2025-09-01</v>
+        <v>2025</v>
       </c>
       <c r="I317" t="str">
-        <v>2026-09-31</v>
+        <v>2026</v>
       </c>
       <c r="J317" t="str">
         <v>Future</v>
@@ -10578,10 +10578,10 @@
         <v>1296.75</v>
       </c>
       <c r="H318" t="str">
-        <v>2025-10-01</v>
+        <v>2025</v>
       </c>
       <c r="I318" t="str">
-        <v>2026-10-31</v>
+        <v>2026</v>
       </c>
       <c r="J318" t="str">
         <v>Future</v>
@@ -10610,10 +10610,10 @@
         <v>1327.5</v>
       </c>
       <c r="H319" t="str">
-        <v>2025-11-01</v>
+        <v>2025</v>
       </c>
       <c r="I319" t="str">
-        <v>2026-11-31</v>
+        <v>2026</v>
       </c>
       <c r="J319" t="str">
         <v>Future</v>
@@ -10642,10 +10642,10 @@
         <v>1358.25</v>
       </c>
       <c r="H320" t="str">
-        <v>2025-12-01</v>
+        <v>2025</v>
       </c>
       <c r="I320" t="str">
-        <v>2026-12-31</v>
+        <v>2026</v>
       </c>
       <c r="J320" t="str">
         <v>Future</v>
@@ -10674,10 +10674,10 @@
         <v>1266</v>
       </c>
       <c r="H321" t="str">
-        <v>2025-09-01</v>
+        <v>2025</v>
       </c>
       <c r="I321" t="str">
-        <v>2026-09-31</v>
+        <v>2026</v>
       </c>
       <c r="J321" t="str">
         <v>Current</v>
@@ -10706,10 +10706,10 @@
         <v>1296.75</v>
       </c>
       <c r="H322" t="str">
-        <v>2025-10-01</v>
+        <v>2025</v>
       </c>
       <c r="I322" t="str">
-        <v>2026-10-31</v>
+        <v>2026</v>
       </c>
       <c r="J322" t="str">
         <v>Current</v>
@@ -10738,10 +10738,10 @@
         <v>1358.25</v>
       </c>
       <c r="H323" t="str">
-        <v>2025-12-01</v>
+        <v>2025</v>
       </c>
       <c r="I323" t="str">
-        <v>2026-12-31</v>
+        <v>2026</v>
       </c>
       <c r="J323" t="str">
         <v>Current</v>
@@ -10770,10 +10770,10 @@
         <v>1389</v>
       </c>
       <c r="H324" t="str">
-        <v>2025-01-01</v>
+        <v>2025</v>
       </c>
       <c r="I324" t="str">
-        <v>2026-01-31</v>
+        <v>2026</v>
       </c>
       <c r="J324" t="str">
         <v>Current</v>
@@ -10802,10 +10802,10 @@
         <v>1266</v>
       </c>
       <c r="H325" t="str">
-        <v>2025-09-01</v>
+        <v>2025</v>
       </c>
       <c r="I325" t="str">
-        <v>2026-09-31</v>
+        <v>2026</v>
       </c>
       <c r="J325" t="str">
         <v>Current</v>
@@ -10834,10 +10834,10 @@
         <v>1296.75</v>
       </c>
       <c r="H326" t="str">
-        <v>2025-10-01</v>
+        <v>2025</v>
       </c>
       <c r="I326" t="str">
-        <v>2026-10-31</v>
+        <v>2026</v>
       </c>
       <c r="J326" t="str">
         <v>Current</v>
@@ -10866,10 +10866,10 @@
         <v>1327.5</v>
       </c>
       <c r="H327" t="str">
-        <v>2025-11-01</v>
+        <v>2025</v>
       </c>
       <c r="I327" t="str">
-        <v>2026-11-31</v>
+        <v>2026</v>
       </c>
       <c r="J327" t="str">
         <v>Current</v>
@@ -10898,10 +10898,10 @@
         <v>1266</v>
       </c>
       <c r="H328" t="str">
-        <v>2025-09-01</v>
+        <v>2025</v>
       </c>
       <c r="I328" t="str">
-        <v>2026-09-31</v>
+        <v>2026</v>
       </c>
       <c r="J328" t="str">
         <v>Current</v>
@@ -10930,10 +10930,10 @@
         <v>1296.75</v>
       </c>
       <c r="H329" t="str">
-        <v>2025-10-01</v>
+        <v>2025</v>
       </c>
       <c r="I329" t="str">
-        <v>2026-10-31</v>
+        <v>2026</v>
       </c>
       <c r="J329" t="str">
         <v>Current</v>
@@ -10962,10 +10962,10 @@
         <v>1327.5</v>
       </c>
       <c r="H330" t="str">
-        <v>2025-11-01</v>
+        <v>2025</v>
       </c>
       <c r="I330" t="str">
-        <v>2026-11-31</v>
+        <v>2026</v>
       </c>
       <c r="J330" t="str">
         <v>Current</v>
@@ -10994,10 +10994,10 @@
         <v>1266</v>
       </c>
       <c r="H331" t="str">
-        <v>2025-09-01</v>
+        <v>2025</v>
       </c>
       <c r="I331" t="str">
-        <v>2026-09-31</v>
+        <v>2026</v>
       </c>
       <c r="J331" t="str">
         <v>Current</v>
@@ -11026,10 +11026,10 @@
         <v>1296.75</v>
       </c>
       <c r="H332" t="str">
-        <v>2025-10-01</v>
+        <v>2025</v>
       </c>
       <c r="I332" t="str">
-        <v>2026-10-31</v>
+        <v>2026</v>
       </c>
       <c r="J332" t="str">
         <v>Notice</v>
@@ -11058,10 +11058,10 @@
         <v>1358.25</v>
       </c>
       <c r="H333" t="str">
-        <v>2025-12-01</v>
+        <v>2025</v>
       </c>
       <c r="I333" t="str">
-        <v>2026-12-31</v>
+        <v>2026</v>
       </c>
       <c r="J333" t="str">
         <v>Current</v>
@@ -11090,10 +11090,10 @@
         <v>1389</v>
       </c>
       <c r="H334" t="str">
-        <v>2025-01-01</v>
+        <v>2025</v>
       </c>
       <c r="I334" t="str">
-        <v>2026-01-31</v>
+        <v>2026</v>
       </c>
       <c r="J334" t="str">
         <v>Current</v>
@@ -11122,10 +11122,10 @@
         <v>1266</v>
       </c>
       <c r="H335" t="str">
-        <v>2025-09-01</v>
+        <v>2025</v>
       </c>
       <c r="I335" t="str">
-        <v>2026-09-31</v>
+        <v>2026</v>
       </c>
       <c r="J335" t="str">
         <v>Current</v>
@@ -11154,10 +11154,10 @@
         <v>1296.75</v>
       </c>
       <c r="H336" t="str">
-        <v>2025-10-01</v>
+        <v>2025</v>
       </c>
       <c r="I336" t="str">
-        <v>2026-10-31</v>
+        <v>2026</v>
       </c>
       <c r="J336" t="str">
         <v>Current</v>
@@ -11186,10 +11186,10 @@
         <v>1327.5</v>
       </c>
       <c r="H337" t="str">
-        <v>2025-11-01</v>
+        <v>2025</v>
       </c>
       <c r="I337" t="str">
-        <v>2026-11-31</v>
+        <v>2026</v>
       </c>
       <c r="J337" t="str">
         <v>Current</v>
@@ -11218,10 +11218,10 @@
         <v>1358.25</v>
       </c>
       <c r="H338" t="str">
-        <v>2025-12-01</v>
+        <v>2025</v>
       </c>
       <c r="I338" t="str">
-        <v>2026-12-31</v>
+        <v>2026</v>
       </c>
       <c r="J338" t="str">
         <v>Current</v>
@@ -11250,10 +11250,10 @@
         <v>1286.25</v>
       </c>
       <c r="H339" t="str">
-        <v>2025-10-01</v>
+        <v>2025</v>
       </c>
       <c r="I339" t="str">
-        <v>2026-10-31</v>
+        <v>2026</v>
       </c>
       <c r="J339" t="str">
         <v>Current</v>
@@ -11282,10 +11282,10 @@
         <v>1317</v>
       </c>
       <c r="H340" t="str">
-        <v>2025-11-01</v>
+        <v>2025</v>
       </c>
       <c r="I340" t="str">
-        <v>2026-11-31</v>
+        <v>2026</v>
       </c>
       <c r="J340" t="str">
         <v>Current</v>
@@ -11314,10 +11314,10 @@
         <v>1378.5</v>
       </c>
       <c r="H341" t="str">
-        <v>2025-01-01</v>
+        <v>2025</v>
       </c>
       <c r="I341" t="str">
-        <v>2026-01-31</v>
+        <v>2026</v>
       </c>
       <c r="J341" t="str">
         <v>Current</v>
@@ -11346,10 +11346,10 @@
         <v>1286.25</v>
       </c>
       <c r="H342" t="str">
-        <v>2025-10-01</v>
+        <v>2025</v>
       </c>
       <c r="I342" t="str">
-        <v>2026-10-31</v>
+        <v>2026</v>
       </c>
       <c r="J342" t="str">
         <v>Current</v>
@@ -11378,10 +11378,10 @@
         <v>1317</v>
       </c>
       <c r="H343" t="str">
-        <v>2025-11-01</v>
+        <v>2025</v>
       </c>
       <c r="I343" t="str">
-        <v>2026-11-31</v>
+        <v>2026</v>
       </c>
       <c r="J343" t="str">
         <v>Current</v>
@@ -11410,10 +11410,10 @@
         <v>1347.75</v>
       </c>
       <c r="H344" t="str">
-        <v>2025-12-01</v>
+        <v>2025</v>
       </c>
       <c r="I344" t="str">
-        <v>2026-12-31</v>
+        <v>2026</v>
       </c>
       <c r="J344" t="str">
         <v>Current</v>
@@ -11442,10 +11442,10 @@
         <v>1378.5</v>
       </c>
       <c r="H345" t="str">
-        <v>2025-01-01</v>
+        <v>2025</v>
       </c>
       <c r="I345" t="str">
-        <v>2026-01-31</v>
+        <v>2026</v>
       </c>
       <c r="J345" t="str">
         <v>Current</v>
@@ -11474,10 +11474,10 @@
         <v>1409.25</v>
       </c>
       <c r="H346" t="str">
-        <v>2025-02-01</v>
+        <v>2025</v>
       </c>
       <c r="I346" t="str">
-        <v>2026-02-31</v>
+        <v>2026</v>
       </c>
       <c r="J346" t="str">
         <v>Current</v>
@@ -11506,10 +11506,10 @@
         <v>1286.25</v>
       </c>
       <c r="H347" t="str">
-        <v>2025-10-01</v>
+        <v>2025</v>
       </c>
       <c r="I347" t="str">
-        <v>2026-10-31</v>
+        <v>2026</v>
       </c>
       <c r="J347" t="str">
         <v>Current</v>
@@ -11538,10 +11538,10 @@
         <v>1317</v>
       </c>
       <c r="H348" t="str">
-        <v>2025-11-01</v>
+        <v>2025</v>
       </c>
       <c r="I348" t="str">
-        <v>2026-11-31</v>
+        <v>2026</v>
       </c>
       <c r="J348" t="str">
         <v>Current</v>
@@ -11570,10 +11570,10 @@
         <v>1347.75</v>
       </c>
       <c r="H349" t="str">
-        <v>2025-12-01</v>
+        <v>2025</v>
       </c>
       <c r="I349" t="str">
-        <v>2026-12-31</v>
+        <v>2026</v>
       </c>
       <c r="J349" t="str">
         <v>Current</v>
@@ -11602,10 +11602,10 @@
         <v>1286.25</v>
       </c>
       <c r="H350" t="str">
-        <v>2025-10-01</v>
+        <v>2025</v>
       </c>
       <c r="I350" t="str">
-        <v>2026-10-31</v>
+        <v>2026</v>
       </c>
       <c r="J350" t="str">
         <v>Current</v>
@@ -11634,10 +11634,10 @@
         <v>1317</v>
       </c>
       <c r="H351" t="str">
-        <v>2025-11-01</v>
+        <v>2025</v>
       </c>
       <c r="I351" t="str">
-        <v>2026-11-31</v>
+        <v>2026</v>
       </c>
       <c r="J351" t="str">
         <v>Notice</v>
@@ -11666,10 +11666,10 @@
         <v>1286.25</v>
       </c>
       <c r="H352" t="str">
-        <v>2025-10-01</v>
+        <v>2025</v>
       </c>
       <c r="I352" t="str">
-        <v>2026-10-31</v>
+        <v>2026</v>
       </c>
       <c r="J352" t="str">
         <v>Current</v>
@@ -11698,10 +11698,10 @@
         <v>1317</v>
       </c>
       <c r="H353" t="str">
-        <v>2025-11-01</v>
+        <v>2025</v>
       </c>
       <c r="I353" t="str">
-        <v>2026-11-31</v>
+        <v>2026</v>
       </c>
       <c r="J353" t="str">
         <v>Current</v>
@@ -11730,10 +11730,10 @@
         <v>1347.75</v>
       </c>
       <c r="H354" t="str">
-        <v>2025-12-01</v>
+        <v>2025</v>
       </c>
       <c r="I354" t="str">
-        <v>2026-12-31</v>
+        <v>2026</v>
       </c>
       <c r="J354" t="str">
         <v>Current</v>
@@ -11762,10 +11762,10 @@
         <v>1378.5</v>
       </c>
       <c r="H355" t="str">
-        <v>2025-01-01</v>
+        <v>2025</v>
       </c>
       <c r="I355" t="str">
-        <v>2026-01-31</v>
+        <v>2026</v>
       </c>
       <c r="J355" t="str">
         <v>Current</v>
@@ -11794,10 +11794,10 @@
         <v>1409.25</v>
       </c>
       <c r="H356" t="str">
-        <v>2025-02-01</v>
+        <v>2025</v>
       </c>
       <c r="I356" t="str">
-        <v>2026-02-31</v>
+        <v>2026</v>
       </c>
       <c r="J356" t="str">
         <v>Current</v>
@@ -11826,10 +11826,10 @@
         <v>1306.5</v>
       </c>
       <c r="H357" t="str">
-        <v>2025-11-01</v>
+        <v>2025</v>
       </c>
       <c r="I357" t="str">
-        <v>2026-11-31</v>
+        <v>2026</v>
       </c>
       <c r="J357" t="str">
         <v>Current</v>
@@ -11858,10 +11858,10 @@
         <v>1337.25</v>
       </c>
       <c r="H358" t="str">
-        <v>2025-12-01</v>
+        <v>2025</v>
       </c>
       <c r="I358" t="str">
-        <v>2026-12-31</v>
+        <v>2026</v>
       </c>
       <c r="J358" t="str">
         <v>Current</v>
@@ -11890,10 +11890,10 @@
         <v>1368</v>
       </c>
       <c r="H359" t="str">
-        <v>2025-01-01</v>
+        <v>2025</v>
       </c>
       <c r="I359" t="str">
-        <v>2026-01-31</v>
+        <v>2026</v>
       </c>
       <c r="J359" t="str">
         <v>Current</v>
@@ -11922,10 +11922,10 @@
         <v>1398.75</v>
       </c>
       <c r="H360" t="str">
-        <v>2025-02-01</v>
+        <v>2025</v>
       </c>
       <c r="I360" t="str">
-        <v>2026-02-31</v>
+        <v>2026</v>
       </c>
       <c r="J360" t="str">
         <v>Current</v>
@@ -11954,10 +11954,10 @@
         <v>1306.5</v>
       </c>
       <c r="H361" t="str">
-        <v>2025-11-01</v>
+        <v>2025</v>
       </c>
       <c r="I361" t="str">
-        <v>2026-11-31</v>
+        <v>2026</v>
       </c>
       <c r="J361" t="str">
         <v>Current</v>
@@ -11986,10 +11986,10 @@
         <v>1337.25</v>
       </c>
       <c r="H362" t="str">
-        <v>2025-12-01</v>
+        <v>2025</v>
       </c>
       <c r="I362" t="str">
-        <v>2026-12-31</v>
+        <v>2026</v>
       </c>
       <c r="J362" t="str">
         <v>Current</v>
@@ -12018,10 +12018,10 @@
         <v>1368</v>
       </c>
       <c r="H363" t="str">
-        <v>2025-01-01</v>
+        <v>2025</v>
       </c>
       <c r="I363" t="str">
-        <v>2026-01-31</v>
+        <v>2026</v>
       </c>
       <c r="J363" t="str">
         <v>Current</v>
@@ -12050,10 +12050,10 @@
         <v>1398.75</v>
       </c>
       <c r="H364" t="str">
-        <v>2025-02-01</v>
+        <v>2025</v>
       </c>
       <c r="I364" t="str">
-        <v>2026-02-31</v>
+        <v>2026</v>
       </c>
       <c r="J364" t="str">
         <v>Current</v>
@@ -12082,10 +12082,10 @@
         <v>1429.5</v>
       </c>
       <c r="H365" t="str">
-        <v>2025-03-01</v>
+        <v>2025</v>
       </c>
       <c r="I365" t="str">
-        <v>2026-03-31</v>
+        <v>2026</v>
       </c>
       <c r="J365" t="str">
         <v>Current</v>
@@ -12114,10 +12114,10 @@
         <v>1306.5</v>
       </c>
       <c r="H366" t="str">
-        <v>2025-11-01</v>
+        <v>2025</v>
       </c>
       <c r="I366" t="str">
-        <v>2026-11-31</v>
+        <v>2026</v>
       </c>
       <c r="J366" t="str">
         <v>Current</v>
@@ -12146,10 +12146,10 @@
         <v>1337.25</v>
       </c>
       <c r="H367" t="str">
-        <v>2025-12-01</v>
+        <v>2025</v>
       </c>
       <c r="I367" t="str">
-        <v>2026-12-31</v>
+        <v>2026</v>
       </c>
       <c r="J367" t="str">
         <v>Notice</v>
@@ -12178,10 +12178,10 @@
         <v>1306.5</v>
       </c>
       <c r="H368" t="str">
-        <v>2025-11-01</v>
+        <v>2025</v>
       </c>
       <c r="I368" t="str">
-        <v>2026-11-31</v>
+        <v>2026</v>
       </c>
       <c r="J368" t="str">
         <v>Current</v>
@@ -12210,10 +12210,10 @@
         <v>1337.25</v>
       </c>
       <c r="H369" t="str">
-        <v>2025-12-01</v>
+        <v>2025</v>
       </c>
       <c r="I369" t="str">
-        <v>2026-12-31</v>
+        <v>2026</v>
       </c>
       <c r="J369" t="str">
         <v>Current</v>
@@ -12242,10 +12242,10 @@
         <v>1368</v>
       </c>
       <c r="H370" t="str">
-        <v>2025-01-01</v>
+        <v>2025</v>
       </c>
       <c r="I370" t="str">
-        <v>2026-01-31</v>
+        <v>2026</v>
       </c>
       <c r="J370" t="str">
         <v>Current</v>
@@ -12274,10 +12274,10 @@
         <v>1306.5</v>
       </c>
       <c r="H371" t="str">
-        <v>2025-11-01</v>
+        <v>2025</v>
       </c>
       <c r="I371" t="str">
-        <v>2026-11-31</v>
+        <v>2026</v>
       </c>
       <c r="J371" t="str">
         <v>Current</v>
@@ -12306,10 +12306,10 @@
         <v>1337.25</v>
       </c>
       <c r="H372" t="str">
-        <v>2025-12-01</v>
+        <v>2025</v>
       </c>
       <c r="I372" t="str">
-        <v>2026-12-31</v>
+        <v>2026</v>
       </c>
       <c r="J372" t="str">
         <v>Current</v>
@@ -12338,10 +12338,10 @@
         <v>1368</v>
       </c>
       <c r="H373" t="str">
-        <v>2025-01-01</v>
+        <v>2025</v>
       </c>
       <c r="I373" t="str">
-        <v>2026-01-31</v>
+        <v>2026</v>
       </c>
       <c r="J373" t="str">
         <v>Current</v>
@@ -12370,10 +12370,10 @@
         <v>1398.75</v>
       </c>
       <c r="H374" t="str">
-        <v>2025-02-01</v>
+        <v>2025</v>
       </c>
       <c r="I374" t="str">
-        <v>2026-02-31</v>
+        <v>2026</v>
       </c>
       <c r="J374" t="str">
         <v>Current</v>
@@ -12402,10 +12402,10 @@
         <v>1429.5</v>
       </c>
       <c r="H375" t="str">
-        <v>2025-03-01</v>
+        <v>2025</v>
       </c>
       <c r="I375" t="str">
-        <v>2026-03-31</v>
+        <v>2026</v>
       </c>
       <c r="J375" t="str">
         <v>Current</v>
@@ -12434,10 +12434,10 @@
         <v>1306.5</v>
       </c>
       <c r="H376" t="str">
-        <v>2025-11-01</v>
+        <v>2025</v>
       </c>
       <c r="I376" t="str">
-        <v>2026-11-31</v>
+        <v>2026</v>
       </c>
       <c r="J376" t="str">
         <v>Current</v>
@@ -12466,10 +12466,10 @@
         <v>1337.25</v>
       </c>
       <c r="H377" t="str">
-        <v>2025-12-01</v>
+        <v>2025</v>
       </c>
       <c r="I377" t="str">
-        <v>2026-12-31</v>
+        <v>2026</v>
       </c>
       <c r="J377" t="str">
         <v>Current</v>
@@ -12498,10 +12498,10 @@
         <v>1398.75</v>
       </c>
       <c r="H378" t="str">
-        <v>2025-02-01</v>
+        <v>2025</v>
       </c>
       <c r="I378" t="str">
-        <v>2026-02-31</v>
+        <v>2026</v>
       </c>
       <c r="J378" t="str">
         <v>Current</v>
